--- a/InputData/indst/EoIEPwEEI/Elasticity of Ind Eqpt Price wrt E Eff Improvements.xlsx
+++ b/InputData/indst/EoIEPwEEI/Elasticity of Ind Eqpt Price wrt E Eff Improvements.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanO'Brien\Models\EPS\US\eps-us\InputData\indst\EoIEPwEEI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A802A4A4-6048-4AB2-9E5A-8AE402970795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{138C8715-36E6-4D76-B3E3-4B17A9E8069F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9150" yWindow="0" windowWidth="10140" windowHeight="11370" tabRatio="763" firstSheet="7" activeTab="9" xr2:uid="{05F795DA-2DEA-4188-AD09-B14B246EEF5D}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="763" firstSheet="4" activeTab="15" xr2:uid="{05F795DA-2DEA-4188-AD09-B14B246EEF5D}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -26,8 +26,9 @@
     <sheet name="indst heat pumps" sheetId="11" r:id="rId11"/>
     <sheet name="fans-blowers" sheetId="14" r:id="rId12"/>
     <sheet name="solid fuel boilers" sheetId="16" r:id="rId13"/>
-    <sheet name="calcs" sheetId="13" r:id="rId14"/>
-    <sheet name="EoIEECwEC" sheetId="3" r:id="rId15"/>
+    <sheet name="Lighting" sheetId="17" r:id="rId14"/>
+    <sheet name="calcs" sheetId="13" r:id="rId15"/>
+    <sheet name="EoIEPwEEI" sheetId="3" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -50,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="520">
   <si>
     <t>Source:</t>
   </si>
@@ -1147,9 +1148,6 @@
     <t>Machine Drive</t>
   </si>
   <si>
-    <t>Electrochem</t>
-  </si>
-  <si>
     <t>Other process</t>
   </si>
   <si>
@@ -1400,19 +1398,293 @@
   </si>
   <si>
     <t>total</t>
+  </si>
+  <si>
+    <t>Facility HVAC</t>
+  </si>
+  <si>
+    <t>Facility Lighting</t>
+  </si>
+  <si>
+    <t>Other Nonprocess</t>
+  </si>
+  <si>
+    <t>https://www.bulkofficesupply.com/Categories/Janitorial-and-Facility-Supplies/Lighting/Light-Bulbs.aspx?srsltid=AfmBOorWkgJMp4H4zdZKPjbhWJ39KPaQWfcg1JIX1YpF1EunQjEtuY1Z</t>
+  </si>
+  <si>
+    <t>lightstoreusa.com</t>
+  </si>
+  <si>
+    <t>incand</t>
+  </si>
+  <si>
+    <t>LED</t>
+  </si>
+  <si>
+    <t>fluorescent</t>
+  </si>
+  <si>
+    <t>CFL</t>
+  </si>
+  <si>
+    <t>HID</t>
+  </si>
+  <si>
+    <t>bulb</t>
+  </si>
+  <si>
+    <t>parabolic</t>
+  </si>
+  <si>
+    <t>reflector</t>
+  </si>
+  <si>
+    <t>tube</t>
+  </si>
+  <si>
+    <t>twin tube</t>
+  </si>
+  <si>
+    <t>floodlight</t>
+  </si>
+  <si>
+    <t>Satco A15 Appliance Light Bulb</t>
+  </si>
+  <si>
+    <t>Satco 6.5W PAR 20/FL 3000K LED Bulb</t>
+  </si>
+  <si>
+    <t>Satco 7.5W BR30 3000K LED Bulb</t>
+  </si>
+  <si>
+    <t>Satco 12W PAR 30/LN/FL 3000K LED Bulb</t>
+  </si>
+  <si>
+    <t>Satco 15W PAR38 3000K LED Bulb</t>
+  </si>
+  <si>
+    <t>Satco 10W A19 LED 5000K Light Bulbs</t>
+  </si>
+  <si>
+    <t>Satco 40W T8 4000K LED Tube Light</t>
+  </si>
+  <si>
+    <t>Satco 11 Watt LED T8 Bulb</t>
+  </si>
+  <si>
+    <t>Satco 13W GX23 Pin-Based 2700K Compact Fluorescent Bulb</t>
+  </si>
+  <si>
+    <t>Satco 54W T5 3500K Fluorescent Tube</t>
+  </si>
+  <si>
+    <t>Satco Flourescent Light Bulbs 32W 6/box</t>
+  </si>
+  <si>
+    <t>Satco 23W T2 2700K Spiral CFL Bulb</t>
+  </si>
+  <si>
+    <t>Plusrite 1035</t>
+  </si>
+  <si>
+    <t>M47 BT37 Mogul</t>
+  </si>
+  <si>
+    <t>Plusrite 1056</t>
+  </si>
+  <si>
+    <t>Plusrite 1061</t>
+  </si>
+  <si>
+    <t>PLUSRITE Par 38</t>
+  </si>
+  <si>
+    <t>$</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>lm</t>
+  </si>
+  <si>
+    <t>hr life</t>
+  </si>
+  <si>
+    <t>W equiv. incandesc.</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>https://www.mordorintelligence.com/industry-reports/industrial-lighting-market</t>
+  </si>
+  <si>
+    <t>lifetime</t>
+  </si>
+  <si>
+    <t>BTU/yr</t>
+  </si>
+  <si>
+    <t>Industrial lighting market</t>
+  </si>
+  <si>
+    <t>Fluorescent</t>
+  </si>
+  <si>
+    <t>assumed lighting lifetime (IESD)</t>
+  </si>
+  <si>
+    <t>HID fixtures</t>
+  </si>
+  <si>
+    <t>years</t>
+  </si>
+  <si>
+    <t>OLED</t>
+  </si>
+  <si>
+    <t>hours/yr use</t>
+  </si>
+  <si>
+    <t>hour life</t>
+  </si>
+  <si>
+    <t>BTU/kWh</t>
+  </si>
+  <si>
+    <t>$/(BTU/yr)</t>
+  </si>
+  <si>
+    <t>Lighting is generally electric. Other fuels can be used to power a generator to power lighting.</t>
+  </si>
+  <si>
+    <t>So we apply an efficiency loss for using a generator to power lighting.</t>
+  </si>
+  <si>
+    <t>generator efficiency</t>
+  </si>
+  <si>
+    <t>lightbulb contribution to cost</t>
+  </si>
+  <si>
+    <t>And must account for the cost of a generator:</t>
+  </si>
+  <si>
+    <t>Generac</t>
+  </si>
+  <si>
+    <t>Westinghouse Wgen 5300c</t>
+  </si>
+  <si>
+    <t>Westinghouse Wgen7500c</t>
+  </si>
+  <si>
+    <t>Westinghouse WGen9500c</t>
+  </si>
+  <si>
+    <t>WEN DF5600X</t>
+  </si>
+  <si>
+    <t>DuroMax XP13000HX</t>
+  </si>
+  <si>
+    <t>Firman Tri Fuel</t>
+  </si>
+  <si>
+    <t>avg $</t>
+  </si>
+  <si>
+    <t>avg watts</t>
+  </si>
+  <si>
+    <t>generator upfront cost per lightbulb powered</t>
+  </si>
+  <si>
+    <t>generator contribution to cost</t>
+  </si>
+  <si>
+    <t>total cost per BTU</t>
+  </si>
+  <si>
+    <t>40 W</t>
+  </si>
+  <si>
+    <t>Incandescent</t>
+  </si>
+  <si>
+    <t>50 W</t>
+  </si>
+  <si>
+    <t>home depot</t>
+  </si>
+  <si>
+    <t>round</t>
+  </si>
+  <si>
+    <t>5-5.5k lumens</t>
+  </si>
+  <si>
+    <t>32-Watt 48 in. Alto Linear T8 Type A Fluorescent Tube Light Bulb Cool White</t>
+  </si>
+  <si>
+    <t>Home Depot</t>
+  </si>
+  <si>
+    <t>Philips 32W 48in T8 Long Life Cool White Fluorescent Tube (Case of 30)</t>
+  </si>
+  <si>
+    <t>blubs/com</t>
+  </si>
+  <si>
+    <t>32-Watt 48 in. Linear F32T8/841 T8 Tube Fluorescent Light Bulb 4100K Cool White</t>
+  </si>
+  <si>
+    <t>F25T8/830 - 25 Watt 36 Inch T8 Flourescent Light Bulb</t>
+  </si>
+  <si>
+    <t>goodbulb</t>
+  </si>
+  <si>
+    <t>25PK 4FT LED T8 Tube Light, Type A+B Double End or Single End Power</t>
+  </si>
+  <si>
+    <t>3'</t>
+  </si>
+  <si>
+    <t>warehouse-lighting</t>
+  </si>
+  <si>
+    <t>25PK 4FT LED Tube Light, 2100 Lumens, 15W, CCT Selectable, 120-277V</t>
+  </si>
+  <si>
+    <t>25Pk 17 Watt 4' T8 LED Tube, 5000K, 120</t>
+  </si>
+  <si>
+    <t>30PK 4FT LED T8 Tube Light, Type A+B Double End or Single End Power, Wattage and CCT Tunable, 120-277V</t>
+  </si>
+  <si>
+    <t>fluoro</t>
+  </si>
+  <si>
+    <t>wattage</t>
+  </si>
+  <si>
+    <t>lumens</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1477,8 +1749,15 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1509,6 +1788,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1519,10 +1804,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1557,14 +1843,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2862,6 +3155,421 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Lighting!$C$14</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>$</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:strRef>
+              <c:f>Lighting!$B$15:$B$18</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>incand</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>LED</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>fluorescent</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>CFL</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Lighting!$C$15:$C$18</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1.3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.9169999999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.056861111111111</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.5236111111111121</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B242-47A5-BFA0-3B8BDB3CCCB8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Lighting!$D$14</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>BTU/yr</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:strRef>
+              <c:f>Lighting!$B$15:$B$18</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>incand</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>LED</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>fluorescent</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>CFL</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Lighting!$D$15:$D$18</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>377565.42095238098</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>137541.68906122446</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>311491.47228571423</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>217100.11704761902</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-B242-47A5-BFA0-3B8BDB3CCCB8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1366896671"/>
+        <c:axId val="1366898111"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1366896671"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1366898111"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1366898111"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1366896671"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -2902,7 +3610,563 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -3821,6 +5085,47 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>95249</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>188291</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>567357</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>32578</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{471CA160-2724-92E4-7169-B4CECAF141D0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -4139,23 +5444,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6F6B216-0153-49F1-A327-FA35702ED267}">
   <dimension ref="A1:B68"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="60.453125" customWidth="1"/>
+    <col min="2" max="2" width="60.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B2" s="4"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -4163,272 +5468,272 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" s="2">
         <v>2022</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B9" s="15" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B10" s="2">
         <v>2023</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B15" s="15" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B16" s="2">
         <v>2016</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" s="2">
         <v>2024</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B28" s="2">
         <v>2023</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B33" s="15" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B34" s="2">
         <v>2023</v>
       </c>
     </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B39" s="15" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B40" s="2">
         <v>2014</v>
       </c>
     </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="43" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="45" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B45" s="15" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="46" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B46" s="2">
         <v>2022</v>
       </c>
     </row>
-    <row r="47" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="48" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B51" s="15" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B52" s="2">
         <v>2022</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>25</v>
       </c>
@@ -4442,14 +5747,14 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D39F440-FA8D-440E-B9E0-04BD2776E781}">
   <dimension ref="B2:O26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>186</v>
       </c>
@@ -4481,7 +5786,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B4">
         <v>1</v>
       </c>
@@ -4513,7 +5818,7 @@
         <v>138.1</v>
       </c>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>2</v>
       </c>
@@ -4545,7 +5850,7 @@
         <v>138.1</v>
       </c>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>3</v>
       </c>
@@ -4577,7 +5882,7 @@
         <v>326.38</v>
       </c>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>4</v>
       </c>
@@ -4609,7 +5914,7 @@
         <v>326.38</v>
       </c>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>5</v>
       </c>
@@ -4641,7 +5946,7 @@
         <v>463.95499999999998</v>
       </c>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>6</v>
       </c>
@@ -4673,7 +5978,7 @@
         <v>463.95499999999998</v>
       </c>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>7</v>
       </c>
@@ -4705,7 +6010,7 @@
         <v>523.48</v>
       </c>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>8</v>
       </c>
@@ -4737,12 +6042,12 @@
         <v>523.48</v>
       </c>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
       <c r="F14" t="s">
         <v>216</v>
       </c>
@@ -4753,7 +6058,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>186</v>
       </c>
@@ -4794,7 +6099,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B16">
         <v>1</v>
       </c>
@@ -4839,7 +6144,7 @@
         <v>11.776649746192895</v>
       </c>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B17">
         <v>2</v>
       </c>
@@ -4884,7 +6189,7 @@
         <v>13.052350920371223</v>
       </c>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B18">
         <v>3</v>
       </c>
@@ -4929,7 +6234,7 @@
         <v>12.502343017806936</v>
       </c>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B19">
         <v>4</v>
       </c>
@@ -4974,7 +6279,7 @@
         <v>11.821305841924397</v>
       </c>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B20">
         <v>5</v>
       </c>
@@ -5019,7 +6324,7 @@
         <v>16.020380799141865</v>
       </c>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B21">
         <v>6</v>
       </c>
@@ -5064,7 +6369,7 @@
         <v>18.526861535711095</v>
       </c>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B22">
         <v>7</v>
       </c>
@@ -5109,7 +6414,7 @@
         <v>15.460365498777794</v>
       </c>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B23">
         <v>8</v>
       </c>
@@ -5154,7 +6459,7 @@
         <v>13.480774453885848</v>
       </c>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B24">
         <v>9</v>
       </c>
@@ -5199,7 +6504,7 @@
         <v>20.513715904240872</v>
       </c>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B25">
         <v>10</v>
       </c>
@@ -5244,7 +6549,7 @@
         <v>22.814573390757772</v>
       </c>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.25">
       <c r="O26" s="8">
         <f>AVERAGE(O16:O25)</f>
         <v>15.59693211088107</v>
@@ -5258,13 +6563,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75FF9701-D73C-4593-9C81-F6045C33961E}">
   <dimension ref="A1:AD94"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.453125" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
         <v>275</v>
       </c>
@@ -5279,12 +6584,12 @@
       <c r="H1" s="18"/>
       <c r="I1" s="18"/>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="F4" t="s">
         <v>223</v>
       </c>
@@ -5361,7 +6666,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
         <v>224</v>
       </c>
@@ -5468,7 +6773,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>227</v>
       </c>
@@ -5497,7 +6802,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>229</v>
       </c>
@@ -5511,7 +6816,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>230</v>
       </c>
@@ -5528,7 +6833,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>230</v>
       </c>
@@ -5545,7 +6850,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>233</v>
       </c>
@@ -5559,7 +6864,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>235</v>
       </c>
@@ -5580,7 +6885,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>237</v>
       </c>
@@ -5610,7 +6915,7 @@
         <v>2.3250000000000002</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>239</v>
       </c>
@@ -5640,7 +6945,7 @@
         <v>1.95</v>
       </c>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>241</v>
       </c>
@@ -5671,7 +6976,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>243</v>
       </c>
@@ -5702,7 +7007,7 @@
         <v>3.15</v>
       </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>245</v>
       </c>
@@ -5726,7 +7031,7 @@
         <v>4.75</v>
       </c>
     </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>247</v>
       </c>
@@ -5743,7 +7048,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>248</v>
       </c>
@@ -5772,7 +7077,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>251</v>
       </c>
@@ -5803,7 +7108,7 @@
         <v>1.65</v>
       </c>
     </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>253</v>
       </c>
@@ -5817,7 +7122,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>255</v>
       </c>
@@ -5837,7 +7142,7 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>257</v>
       </c>
@@ -5851,7 +7156,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>259</v>
       </c>
@@ -5865,7 +7170,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>262</v>
       </c>
@@ -5888,7 +7193,7 @@
         <v>2.85</v>
       </c>
     </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>264</v>
       </c>
@@ -5908,7 +7213,7 @@
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="26" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>266</v>
       </c>
@@ -5938,7 +7243,7 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>268</v>
       </c>
@@ -5959,7 +7264,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="30" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
         <v>276</v>
       </c>
@@ -5972,22 +7277,22 @@
       <c r="H30" s="18"/>
       <c r="I30" s="18"/>
     </row>
-    <row r="31" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C36" t="s">
         <v>279</v>
       </c>
@@ -5999,7 +7304,7 @@
       </c>
       <c r="F36" s="20"/>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>280</v>
       </c>
@@ -6015,7 +7320,7 @@
       </c>
       <c r="G37" s="17"/>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
         <v>281</v>
       </c>
@@ -6030,7 +7335,7 @@
         <v>1.246122375645043</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
         <v>282</v>
       </c>
@@ -6045,10 +7350,10 @@
         <v>0.78294087514412647</v>
       </c>
     </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E40" s="1"/>
     </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>291</v>
       </c>
@@ -6059,7 +7364,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C42" t="s">
         <v>283</v>
       </c>
@@ -6070,7 +7375,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>284</v>
       </c>
@@ -6099,7 +7404,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
         <v>285</v>
       </c>
@@ -6128,7 +7433,7 @@
         <v>4.0579999999999998</v>
       </c>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
         <v>286</v>
       </c>
@@ -6157,7 +7462,7 @@
         <v>3.9049999999999998</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
         <v>289</v>
       </c>
@@ -6168,7 +7473,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C48" t="s">
         <v>283</v>
       </c>
@@ -6179,7 +7484,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="49" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>284</v>
       </c>
@@ -6208,7 +7513,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
         <v>285</v>
       </c>
@@ -6234,7 +7539,7 @@
         <v>169.7</v>
       </c>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
         <v>286</v>
       </c>
@@ -6260,7 +7565,7 @@
         <v>158.79</v>
       </c>
     </row>
-    <row r="53" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
         <v>290</v>
       </c>
@@ -6271,7 +7576,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B54">
         <f>((C50-D51)/(D51))/((C44-D45)/(D45))</f>
         <v>0.20976791128179526</v>
@@ -6285,39 +7590,39 @@
         <v>0.60701632452890952</v>
       </c>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B56" s="1">
         <f>AVERAGE(B54,F54,J54)</f>
         <v>0.60324082264004886</v>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="59" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B59" s="17" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B60" s="17" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="61" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:13" x14ac:dyDescent="0.25">
       <c r="M61">
         <f>75+40+35</f>
         <v>150</v>
       </c>
     </row>
-    <row r="62" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B62" s="1" t="s">
         <v>299</v>
       </c>
@@ -6326,13 +7631,13 @@
         <v>624</v>
       </c>
     </row>
-    <row r="63" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B63" s="21">
         <f>AVERAGE(B56,F39)</f>
         <v>0.69309084889208772</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="19" t="s">
         <v>300</v>
       </c>
@@ -6345,12 +7650,12 @@
       <c r="H67" s="18"/>
       <c r="I67" s="18"/>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
         <v>302</v>
       </c>
@@ -6361,7 +7666,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B71">
         <v>4.59475218658892</v>
       </c>
@@ -6369,7 +7674,7 @@
         <v>0.61180308422301299</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B72">
         <v>4.5510204081632599</v>
       </c>
@@ -6382,7 +7687,7 @@
       </c>
       <c r="G72" s="1"/>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B73">
         <v>4.5014577259475201</v>
       </c>
@@ -6395,7 +7700,7 @@
       </c>
       <c r="G73" s="21"/>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B74">
         <v>4.4504373177842496</v>
       </c>
@@ -6407,7 +7712,7 @@
         <v>5.473122080544905</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B75">
         <v>4.4008746355685098</v>
       </c>
@@ -6419,7 +7724,7 @@
         <v>5.2350542623469831</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B76">
         <v>4.3498542274052401</v>
       </c>
@@ -6431,7 +7736,7 @@
         <v>5.251433437410828</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B77">
         <v>4.3002915451895003</v>
       </c>
@@ -6443,7 +7748,7 @@
         <v>3.8719312780711839</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B78">
         <v>4.2507288629737596</v>
       </c>
@@ -6455,7 +7760,7 @@
         <v>2.0972232149240635</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B79">
         <v>4.2011661807580101</v>
       </c>
@@ -6467,7 +7772,7 @@
         <v>1.935748293413651</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B80">
         <v>4.1516034985422703</v>
       </c>
@@ -6479,7 +7784,7 @@
         <v>1.5777144666035297</v>
       </c>
     </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B81">
         <v>4.1005830903789997</v>
       </c>
@@ -6491,7 +7796,7 @@
         <v>1.1745302713985946</v>
       </c>
     </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B82">
         <v>4.0510204081632599</v>
       </c>
@@ -6503,7 +7808,7 @@
         <v>1.0233524629365194</v>
       </c>
     </row>
-    <row r="83" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B83">
         <v>4</v>
       </c>
@@ -6515,7 +7820,7 @@
         <v>1.2695307336418431</v>
       </c>
     </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B84">
         <v>3.95043731778425</v>
       </c>
@@ -6527,7 +7832,7 @@
         <v>1.3119208045999733</v>
       </c>
     </row>
-    <row r="85" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B85">
         <v>3.8994169096209901</v>
       </c>
@@ -6539,7 +7844,7 @@
         <v>1.186252771618723</v>
       </c>
     </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B86">
         <v>3.8498542274052401</v>
       </c>
@@ -6551,7 +7856,7 @@
         <v>0.74907565919410624</v>
       </c>
     </row>
-    <row r="87" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B87">
         <v>3.8002915451894999</v>
       </c>
@@ -6563,7 +7868,7 @@
         <v>0.55861435641043156</v>
       </c>
     </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B88">
         <v>3.7580174927113701</v>
       </c>
@@ -6575,7 +7880,7 @@
         <v>0.54299813444073886</v>
       </c>
     </row>
-    <row r="89" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B89">
         <v>3.6997084548104899</v>
       </c>
@@ -6587,7 +7892,7 @@
         <v>0.2333946400419315</v>
       </c>
     </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B90">
         <v>3.6501457725947501</v>
       </c>
@@ -6599,7 +7904,7 @@
         <v>9.0412032929801656E-2</v>
       </c>
     </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="91" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B91">
         <v>3.5801749271137</v>
       </c>
@@ -6611,7 +7916,7 @@
         <v>6.2891425226783801E-2</v>
       </c>
     </row>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:8" x14ac:dyDescent="0.25">
       <c r="E92" s="1">
         <f>AVERAGE(E73:E91)</f>
         <v>2.1722720213347571</v>
@@ -6621,7 +7926,7 @@
       </c>
       <c r="H92" s="20"/>
     </row>
-    <row r="93" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="93" spans="2:8" x14ac:dyDescent="0.25">
       <c r="E93" s="1">
         <f>((C71-C91)/(C71+C91))/((B71-B91)/(B71+B91))</f>
         <v>2.3251416140774124</v>
@@ -6630,7 +7935,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="94" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:8" x14ac:dyDescent="0.25">
       <c r="E94" s="1"/>
     </row>
   </sheetData>
@@ -6642,46 +7947,46 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1011C56E-59CC-41D7-BD37-B8D3833EEA91}">
   <dimension ref="B2:G36"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="23.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.35">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="D3" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.35">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
+        <v>346</v>
+      </c>
+      <c r="C4" t="s">
         <v>347</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>348</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>349</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>350</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>351</v>
       </c>
-      <c r="G4" t="s">
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
         <v>352</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B5" t="s">
-        <v>353</v>
       </c>
       <c r="C5" t="s">
         <v>138</v>
@@ -6699,12 +8004,12 @@
         <v>1.33</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>172</v>
       </c>
       <c r="C6" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D6">
         <v>2.98</v>
@@ -6719,12 +8024,12 @@
         <v>1.33</v>
       </c>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>90</v>
       </c>
       <c r="C7" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D7">
         <v>3.18</v>
@@ -6739,12 +8044,12 @@
         <v>1.44</v>
       </c>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>91</v>
       </c>
       <c r="C8" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D8">
         <v>6.14</v>
@@ -6759,12 +8064,12 @@
         <v>2.17</v>
       </c>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>92</v>
       </c>
       <c r="C9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D9">
         <v>12.2</v>
@@ -6779,12 +8084,12 @@
         <v>3.65</v>
       </c>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
+        <v>357</v>
+      </c>
+      <c r="C10" t="s">
         <v>358</v>
-      </c>
-      <c r="C10" t="s">
-        <v>359</v>
       </c>
       <c r="D10">
         <v>20</v>
@@ -6799,12 +8104,12 @@
         <v>5.87</v>
       </c>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
+        <v>359</v>
+      </c>
+      <c r="C11" t="s">
         <v>360</v>
-      </c>
-      <c r="C11" t="s">
-        <v>361</v>
       </c>
       <c r="D11">
         <v>24.3</v>
@@ -6819,37 +8124,37 @@
         <v>7.02</v>
       </c>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B14" s="29"/>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="28"/>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
         <v>364</v>
       </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B17" t="s">
+      <c r="C17" t="s">
+        <v>347</v>
+      </c>
+      <c r="D17" t="s">
+        <v>372</v>
+      </c>
+      <c r="E17" t="s">
+        <v>373</v>
+      </c>
+      <c r="F17" t="s">
+        <v>374</v>
+      </c>
+      <c r="G17" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
         <v>365</v>
-      </c>
-      <c r="C17" t="s">
-        <v>348</v>
-      </c>
-      <c r="D17" t="s">
-        <v>373</v>
-      </c>
-      <c r="E17" t="s">
-        <v>374</v>
-      </c>
-      <c r="F17" t="s">
-        <v>375</v>
-      </c>
-      <c r="G17" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B18" t="s">
-        <v>366</v>
       </c>
       <c r="C18" t="s">
         <v>138</v>
@@ -6867,12 +8172,12 @@
         <v>62.88</v>
       </c>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D19" s="5">
         <v>111.11</v>
@@ -6887,12 +8192,12 @@
         <v>62.88</v>
       </c>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C20" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D20" s="5">
         <v>129.29</v>
@@ -6907,12 +8212,12 @@
         <v>90.44</v>
       </c>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C21" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D21" s="5">
         <v>129.29</v>
@@ -6927,12 +8232,12 @@
         <v>90.44</v>
       </c>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C22" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D22" s="5">
         <v>129.29</v>
@@ -6947,12 +8252,12 @@
         <v>90.44</v>
       </c>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C23" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D23" s="5">
         <v>129.29</v>
@@ -6967,12 +8272,12 @@
         <v>90.44</v>
       </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C24" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D24" s="5">
         <v>159.99</v>
@@ -6987,34 +8292,34 @@
         <v>116.11</v>
       </c>
     </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.35">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
+        <v>364</v>
+      </c>
+      <c r="C27" t="s">
+        <v>347</v>
+      </c>
+      <c r="D27" t="s">
+        <v>372</v>
+      </c>
+      <c r="E27" t="s">
+        <v>373</v>
+      </c>
+      <c r="F27" t="s">
+        <v>374</v>
+      </c>
+      <c r="G27" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
         <v>365</v>
-      </c>
-      <c r="C27" t="s">
-        <v>348</v>
-      </c>
-      <c r="D27" t="s">
-        <v>373</v>
-      </c>
-      <c r="E27" t="s">
-        <v>374</v>
-      </c>
-      <c r="F27" t="s">
-        <v>375</v>
-      </c>
-      <c r="G27" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B28" t="s">
-        <v>366</v>
       </c>
       <c r="C28" t="s">
         <v>138</v>
@@ -7024,22 +8329,22 @@
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
     </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C29" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D29" t="e">
         <f>((D19-D$18)/(D19+D$18))/((D6-D$5)/(D6+D$5))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E29" s="28">
+      <c r="E29" s="27">
         <f t="shared" ref="E29:F29" si="0">((E19-E$18)/(E$18))/((E6-E$5)/(E$5))</f>
         <v>-1.6807674122567731</v>
       </c>
-      <c r="F29" s="28">
+      <c r="F29" s="27">
         <f t="shared" si="0"/>
         <v>-1.4204128064217787</v>
       </c>
@@ -7048,128 +8353,128 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C30" t="s">
-        <v>355</v>
-      </c>
-      <c r="D30" s="28">
+        <v>354</v>
+      </c>
+      <c r="D30" s="27">
         <f>((D20-D$18)/(D$18))/((D7-D$5)/(D$5))</f>
         <v>2.4379623796237935</v>
       </c>
-      <c r="E30" s="28">
+      <c r="E30" s="27">
         <f t="shared" ref="E30:G30" si="2">((E20-E$18)/(E$18))/((E7-E$5)/(E$5))</f>
         <v>-0.653960849001894</v>
       </c>
-      <c r="F30" s="28">
+      <c r="F30" s="27">
         <f t="shared" si="2"/>
         <v>-0.32226330074820764</v>
       </c>
-      <c r="G30" s="28">
+      <c r="G30" s="27">
         <f t="shared" si="2"/>
         <v>5.2993869997686849</v>
       </c>
     </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C31" t="s">
-        <v>356</v>
-      </c>
-      <c r="D31" s="28">
+        <v>355</v>
+      </c>
+      <c r="D31" s="27">
         <f t="shared" ref="D31:G31" si="3">((D21-D$18)/(D$18))/((D8-D$5)/(D$5))</f>
         <v>0.15430141643188583</v>
       </c>
-      <c r="E31" s="28">
+      <c r="E31" s="27">
         <f t="shared" si="3"/>
         <v>-0.16984259268556354</v>
       </c>
-      <c r="F31" s="28">
+      <c r="F31" s="27">
         <f t="shared" si="3"/>
         <v>-0.12258208169596191</v>
       </c>
-      <c r="G31" s="28">
+      <c r="G31" s="27">
         <f t="shared" si="3"/>
         <v>0.69396734520780323</v>
       </c>
     </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C32" t="s">
-        <v>357</v>
-      </c>
-      <c r="D32" s="28">
+        <v>356</v>
+      </c>
+      <c r="D32" s="27">
         <f t="shared" ref="D32:G32" si="4">((D22-D$18)/(D$18))/((D9-D$5)/(D$5))</f>
         <v>5.2884216477739603E-2</v>
       </c>
-      <c r="E32" s="28">
+      <c r="E32" s="27">
         <f t="shared" si="4"/>
         <v>-6.8695639225178309E-2</v>
       </c>
-      <c r="F32" s="28">
+      <c r="F32" s="27">
         <f t="shared" si="4"/>
         <v>-5.432508731148273E-2</v>
       </c>
-      <c r="G32" s="28">
+      <c r="G32" s="27">
         <f t="shared" si="4"/>
         <v>0.25126403878213566</v>
       </c>
     </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C33" t="s">
-        <v>359</v>
-      </c>
-      <c r="D33" s="28">
+        <v>358</v>
+      </c>
+      <c r="D33" s="27">
         <f t="shared" ref="D33:G33" si="5">((D23-D$18)/(D$18))/((D10-D$5)/(D$5))</f>
         <v>2.8648206576072803E-2</v>
       </c>
-      <c r="E33" s="28">
+      <c r="E33" s="27">
         <f t="shared" si="5"/>
         <v>-4.1547287555397987E-2</v>
       </c>
-      <c r="F33" s="28">
+      <c r="F33" s="27">
         <f t="shared" si="5"/>
         <v>-3.7862939641336447E-2</v>
       </c>
-      <c r="G33" s="28">
+      <c r="G33" s="27">
         <f t="shared" si="5"/>
         <v>0.12839924448778736</v>
       </c>
     </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C34" t="s">
-        <v>361</v>
-      </c>
-      <c r="D34" s="28">
+        <v>360</v>
+      </c>
+      <c r="D34" s="27">
         <f t="shared" ref="D34:G34" si="6">((D24-D$18)/(D$18))/((D11-D$5)/(D$5))</f>
         <v>6.1490371001270992E-2</v>
       </c>
-      <c r="E34" s="28">
+      <c r="E34" s="27">
         <f t="shared" si="6"/>
         <v>-7.9987629086467026E-3</v>
       </c>
-      <c r="F34" s="28">
+      <c r="F34" s="27">
         <f t="shared" si="6"/>
         <v>3.7035177877858712E-3</v>
       </c>
-      <c r="G34" s="28">
+      <c r="G34" s="27">
         <f t="shared" si="6"/>
         <v>0.19787152810385616</v>
       </c>
     </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="D36" s="30">
+    <row r="36" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="D36" s="29">
         <f>AVERAGE(D30:D34,G30:G34)</f>
         <v>0.93061757464610295</v>
       </c>
@@ -7182,50 +8487,50 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFF80A1E-9380-4D67-8452-F9501E3A0DC6}">
   <dimension ref="A2:J19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="29.08984375" customWidth="1"/>
-    <col min="3" max="3" width="14.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.140625" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B4" t="s">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>419</v>
+      </c>
+      <c r="D5" t="s">
+        <v>382</v>
+      </c>
+      <c r="E5" t="s">
+        <v>420</v>
+      </c>
+      <c r="F5" t="s">
+        <v>425</v>
+      </c>
+      <c r="G5" t="s">
+        <v>426</v>
+      </c>
+      <c r="H5" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
         <v>414</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C5" t="s">
-        <v>420</v>
-      </c>
-      <c r="D5" t="s">
-        <v>383</v>
-      </c>
-      <c r="E5" t="s">
-        <v>421</v>
-      </c>
-      <c r="F5" t="s">
-        <v>426</v>
-      </c>
-      <c r="G5" t="s">
-        <v>427</v>
-      </c>
-      <c r="H5" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B6" t="s">
-        <v>415</v>
       </c>
       <c r="C6">
         <v>18</v>
@@ -7234,7 +8539,7 @@
         <v>0.66</v>
       </c>
       <c r="E6" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="F6">
         <v>3000</v>
@@ -7247,9 +8552,9 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C7">
         <v>20</v>
@@ -7258,7 +8563,7 @@
         <v>0.88</v>
       </c>
       <c r="E7" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="F7">
         <v>5000</v>
@@ -7271,9 +8576,9 @@
         <v>6500</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C8">
         <v>25</v>
@@ -7282,7 +8587,7 @@
         <v>0.82</v>
       </c>
       <c r="E8" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F8">
         <v>4000</v>
@@ -7295,9 +8600,9 @@
         <v>5500</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C9">
         <v>25</v>
@@ -7306,7 +8611,7 @@
         <v>0.88</v>
       </c>
       <c r="E9" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="F9">
         <v>6000</v>
@@ -7319,9 +8624,9 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C10">
         <v>160</v>
@@ -7330,7 +8635,7 @@
         <v>0.88</v>
       </c>
       <c r="E10" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="F10">
         <v>30000</v>
@@ -7343,37 +8648,37 @@
         <v>33500</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C13" t="s">
+        <v>419</v>
+      </c>
+      <c r="D13" t="s">
+        <v>382</v>
+      </c>
+      <c r="E13" t="s">
+        <v>420</v>
+      </c>
+      <c r="F13" t="s">
+        <v>425</v>
+      </c>
+      <c r="G13" t="s">
+        <v>426</v>
+      </c>
+      <c r="H13" t="s">
         <v>428</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C13" t="s">
-        <v>420</v>
-      </c>
-      <c r="D13" t="s">
-        <v>383</v>
-      </c>
-      <c r="E13" t="s">
-        <v>421</v>
-      </c>
-      <c r="F13" t="s">
-        <v>426</v>
-      </c>
-      <c r="G13" t="s">
-        <v>427</v>
-      </c>
-      <c r="H13" t="s">
-        <v>429</v>
       </c>
       <c r="J13" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C14">
         <v>18</v>
@@ -7382,7 +8687,7 @@
         <v>0.91</v>
       </c>
       <c r="E14" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="F14">
         <v>6305</v>
@@ -7399,9 +8704,9 @@
         <v>1.9389333333333334</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C15">
         <v>20</v>
@@ -7410,7 +8715,7 @@
         <v>0.91</v>
       </c>
       <c r="E15" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="F15">
         <v>6305</v>
@@ -7427,9 +8732,9 @@
         <v>5.8892307692307631</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C16">
         <v>25</v>
@@ -7438,7 +8743,7 @@
         <v>0.88</v>
       </c>
       <c r="E16" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F16">
         <v>4000</v>
@@ -7455,9 +8760,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C17">
         <v>25</v>
@@ -7466,7 +8771,7 @@
         <v>0.93</v>
       </c>
       <c r="E17" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="F17">
         <v>6990</v>
@@ -7483,9 +8788,9 @@
         <v>2.1779999999999977</v>
       </c>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C18">
         <v>160</v>
@@ -7494,7 +8799,7 @@
         <v>0.92</v>
       </c>
       <c r="E18" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="F18">
         <v>35000</v>
@@ -7511,7 +8816,7 @@
         <v>3.2835820895522354</v>
       </c>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="J19" s="13">
         <f>AVERAGE(J14:J18)</f>
         <v>2.6579492384232659</v>
@@ -7523,15 +8828,1306 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1D5271D-8741-40B6-92F2-97D4F5B6382F}">
-  <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D8718AA-AC7D-4D9E-9BAB-C38A4CE85A96}">
+  <dimension ref="A1:W63"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.54296875" customWidth="1"/>
-    <col min="2" max="9" width="13.54296875" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" customWidth="1"/>
+    <col min="4" max="7" width="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="10.5703125" customWidth="1"/>
+    <col min="10" max="11" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>432</v>
+      </c>
+      <c r="P1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>434</v>
+      </c>
+      <c r="D3" t="s">
+        <v>435</v>
+      </c>
+      <c r="E3" t="s">
+        <v>435</v>
+      </c>
+      <c r="F3" t="s">
+        <v>435</v>
+      </c>
+      <c r="G3" t="s">
+        <v>435</v>
+      </c>
+      <c r="H3" t="s">
+        <v>435</v>
+      </c>
+      <c r="I3" t="s">
+        <v>435</v>
+      </c>
+      <c r="J3" t="s">
+        <v>435</v>
+      </c>
+      <c r="K3" t="s">
+        <v>436</v>
+      </c>
+      <c r="L3" t="s">
+        <v>436</v>
+      </c>
+      <c r="M3" t="s">
+        <v>436</v>
+      </c>
+      <c r="N3" t="s">
+        <v>437</v>
+      </c>
+      <c r="O3" t="s">
+        <v>437</v>
+      </c>
+      <c r="P3" t="s">
+        <v>438</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>438</v>
+      </c>
+      <c r="R3" t="s">
+        <v>438</v>
+      </c>
+      <c r="S3" t="s">
+        <v>438</v>
+      </c>
+      <c r="T3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
+        <v>439</v>
+      </c>
+      <c r="D4" t="s">
+        <v>440</v>
+      </c>
+      <c r="E4" t="s">
+        <v>441</v>
+      </c>
+      <c r="F4" t="s">
+        <v>440</v>
+      </c>
+      <c r="G4" t="s">
+        <v>440</v>
+      </c>
+      <c r="H4" t="s">
+        <v>439</v>
+      </c>
+      <c r="I4" t="s">
+        <v>442</v>
+      </c>
+      <c r="J4" t="s">
+        <v>442</v>
+      </c>
+      <c r="K4" t="s">
+        <v>443</v>
+      </c>
+      <c r="L4" t="s">
+        <v>442</v>
+      </c>
+      <c r="M4" t="s">
+        <v>442</v>
+      </c>
+      <c r="N4" t="s">
+        <v>439</v>
+      </c>
+      <c r="O4" t="s">
+        <v>439</v>
+      </c>
+      <c r="P4" t="s">
+        <v>439</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>439</v>
+      </c>
+      <c r="R4" t="s">
+        <v>439</v>
+      </c>
+      <c r="S4" t="s">
+        <v>444</v>
+      </c>
+      <c r="T4" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>445</v>
+      </c>
+      <c r="D5" t="s">
+        <v>446</v>
+      </c>
+      <c r="E5" t="s">
+        <v>447</v>
+      </c>
+      <c r="F5" t="s">
+        <v>448</v>
+      </c>
+      <c r="G5" t="s">
+        <v>449</v>
+      </c>
+      <c r="H5" t="s">
+        <v>450</v>
+      </c>
+      <c r="I5" t="s">
+        <v>451</v>
+      </c>
+      <c r="J5" t="s">
+        <v>452</v>
+      </c>
+      <c r="K5" t="s">
+        <v>453</v>
+      </c>
+      <c r="L5" t="s">
+        <v>454</v>
+      </c>
+      <c r="M5" t="s">
+        <v>455</v>
+      </c>
+      <c r="N5" t="s">
+        <v>456</v>
+      </c>
+      <c r="O5" t="s">
+        <v>456</v>
+      </c>
+      <c r="P5" t="s">
+        <v>457</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>458</v>
+      </c>
+      <c r="R5" t="s">
+        <v>459</v>
+      </c>
+      <c r="S5" t="s">
+        <v>460</v>
+      </c>
+      <c r="T5" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B6" s="30" t="s">
+        <v>462</v>
+      </c>
+      <c r="C6">
+        <v>1.3</v>
+      </c>
+      <c r="D6">
+        <v>5.15</v>
+      </c>
+      <c r="E6">
+        <v>7.48</v>
+      </c>
+      <c r="F6">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="G6">
+        <v>11.84</v>
+      </c>
+      <c r="H6">
+        <f>12.98/4</f>
+        <v>3.2450000000000001</v>
+      </c>
+      <c r="I6">
+        <f>124.94/10</f>
+        <v>12.494</v>
+      </c>
+      <c r="J6">
+        <f>172.75/25</f>
+        <v>6.91</v>
+      </c>
+      <c r="K6">
+        <f>5.21</f>
+        <v>5.21</v>
+      </c>
+      <c r="L6">
+        <f>206.09/40</f>
+        <v>5.1522500000000004</v>
+      </c>
+      <c r="M6">
+        <f>28.85/6</f>
+        <v>4.8083333333333336</v>
+      </c>
+      <c r="N6">
+        <f>16.57/3</f>
+        <v>5.5233333333333334</v>
+      </c>
+      <c r="O6">
+        <f>198.86/12/3</f>
+        <v>5.52388888888889</v>
+      </c>
+      <c r="P6">
+        <v>15.99</v>
+      </c>
+      <c r="Q6">
+        <v>27.95</v>
+      </c>
+      <c r="R6">
+        <v>39.950000000000003</v>
+      </c>
+      <c r="S6">
+        <v>17</v>
+      </c>
+      <c r="T6">
+        <v>12</v>
+      </c>
+      <c r="W6" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B7" s="30" t="s">
+        <v>463</v>
+      </c>
+      <c r="C7">
+        <v>40</v>
+      </c>
+      <c r="D7">
+        <v>6.5</v>
+      </c>
+      <c r="E7">
+        <v>7.5</v>
+      </c>
+      <c r="F7">
+        <v>12</v>
+      </c>
+      <c r="G7">
+        <v>15</v>
+      </c>
+      <c r="H7">
+        <v>10</v>
+      </c>
+      <c r="I7">
+        <v>40</v>
+      </c>
+      <c r="J7">
+        <v>11</v>
+      </c>
+      <c r="K7">
+        <v>13</v>
+      </c>
+      <c r="L7">
+        <v>54</v>
+      </c>
+      <c r="M7">
+        <v>32</v>
+      </c>
+      <c r="N7">
+        <v>23</v>
+      </c>
+      <c r="O7">
+        <v>23</v>
+      </c>
+      <c r="P7">
+        <v>100</v>
+      </c>
+      <c r="Q7">
+        <v>1000</v>
+      </c>
+      <c r="R7">
+        <v>1000</v>
+      </c>
+      <c r="S7">
+        <v>70</v>
+      </c>
+      <c r="T7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B8" s="30" t="s">
+        <v>464</v>
+      </c>
+      <c r="C8">
+        <v>225</v>
+      </c>
+      <c r="D8">
+        <v>520</v>
+      </c>
+      <c r="E8">
+        <v>650</v>
+      </c>
+      <c r="F8">
+        <v>1000</v>
+      </c>
+      <c r="G8">
+        <v>1200</v>
+      </c>
+      <c r="H8">
+        <v>800</v>
+      </c>
+      <c r="I8">
+        <v>5500</v>
+      </c>
+      <c r="J8">
+        <v>1800</v>
+      </c>
+      <c r="K8">
+        <v>800</v>
+      </c>
+      <c r="L8">
+        <v>5000</v>
+      </c>
+      <c r="M8">
+        <v>3050</v>
+      </c>
+      <c r="N8">
+        <v>1600</v>
+      </c>
+      <c r="O8">
+        <v>1600</v>
+      </c>
+      <c r="P8">
+        <v>8500</v>
+      </c>
+      <c r="Q8">
+        <v>110000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B9" s="30" t="s">
+        <v>465</v>
+      </c>
+      <c r="C9">
+        <v>2500</v>
+      </c>
+      <c r="D9">
+        <v>25000</v>
+      </c>
+      <c r="E9">
+        <v>25000</v>
+      </c>
+      <c r="F9">
+        <v>25000</v>
+      </c>
+      <c r="G9">
+        <v>25000</v>
+      </c>
+      <c r="H9">
+        <v>15000</v>
+      </c>
+      <c r="I9">
+        <v>50000</v>
+      </c>
+      <c r="J9">
+        <v>50000</v>
+      </c>
+      <c r="K9">
+        <v>12000</v>
+      </c>
+      <c r="L9">
+        <v>24000</v>
+      </c>
+      <c r="M9">
+        <v>24000</v>
+      </c>
+      <c r="N9">
+        <v>12000</v>
+      </c>
+      <c r="O9">
+        <v>12000</v>
+      </c>
+      <c r="P9">
+        <v>15000</v>
+      </c>
+      <c r="Q9">
+        <v>10000</v>
+      </c>
+      <c r="R9">
+        <v>5000</v>
+      </c>
+      <c r="S9">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B10" s="30" t="s">
+        <v>466</v>
+      </c>
+      <c r="D10">
+        <v>50</v>
+      </c>
+      <c r="E10">
+        <v>65</v>
+      </c>
+      <c r="F10">
+        <v>75</v>
+      </c>
+      <c r="G10">
+        <v>90</v>
+      </c>
+      <c r="H10">
+        <v>60</v>
+      </c>
+      <c r="I10">
+        <v>59</v>
+      </c>
+      <c r="J10" t="s">
+        <v>467</v>
+      </c>
+      <c r="N10">
+        <v>100</v>
+      </c>
+      <c r="O10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="C11">
+        <f>C6/C7</f>
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="D11">
+        <f t="shared" ref="D11:T11" si="0">D6/D7</f>
+        <v>0.79230769230769238</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="0"/>
+        <v>0.9973333333333334</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="0"/>
+        <v>0.69166666666666676</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="0"/>
+        <v>0.78933333333333333</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="0"/>
+        <v>0.32450000000000001</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="0"/>
+        <v>0.31235000000000002</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="0"/>
+        <v>0.62818181818181817</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="0"/>
+        <v>0.40076923076923077</v>
+      </c>
+      <c r="L11">
+        <f t="shared" si="0"/>
+        <v>9.5412037037037045E-2</v>
+      </c>
+      <c r="M11">
+        <f t="shared" si="0"/>
+        <v>0.15026041666666667</v>
+      </c>
+      <c r="N11">
+        <f t="shared" si="0"/>
+        <v>0.2401449275362319</v>
+      </c>
+      <c r="O11">
+        <f t="shared" si="0"/>
+        <v>0.24016908212560392</v>
+      </c>
+      <c r="P11">
+        <f t="shared" si="0"/>
+        <v>0.15990000000000001</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="0"/>
+        <v>2.7949999999999999E-2</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="0"/>
+        <v>3.9949999999999999E-2</v>
+      </c>
+      <c r="S11">
+        <f t="shared" si="0"/>
+        <v>0.24285714285714285</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="0"/>
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="H13" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="C14" t="s">
+        <v>462</v>
+      </c>
+      <c r="D14" t="s">
+        <v>470</v>
+      </c>
+      <c r="E14" t="s">
+        <v>469</v>
+      </c>
+      <c r="F14" t="s">
+        <v>463</v>
+      </c>
+      <c r="H14" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B15" s="30" t="s">
+        <v>434</v>
+      </c>
+      <c r="C15" s="7">
+        <f>AVERAGEIFS($C$6:$T$6,$C$3:$T$3,$B15)</f>
+        <v>1.3</v>
+      </c>
+      <c r="D15" s="23">
+        <f>AVERAGEIFS($C$7:$T$7,$C$3:$T$3,$B15)*$O$19/1000*$O$21</f>
+        <v>377565.42095238098</v>
+      </c>
+      <c r="E15" s="23">
+        <f>AVERAGEIFS($C$9:$T$9,$C$3:$T$3,$B15)</f>
+        <v>2500</v>
+      </c>
+      <c r="F15" s="23">
+        <f>AVERAGEIFS($C$7:$T$7,$C$3:$T$3,$B15)</f>
+        <v>40</v>
+      </c>
+      <c r="G15" s="23"/>
+      <c r="H15" t="s">
+        <v>435</v>
+      </c>
+      <c r="I15" s="31">
+        <v>0.65200000000000002</v>
+      </c>
+      <c r="J15" s="23">
+        <f>I15*E16</f>
+        <v>20025.714285714286</v>
+      </c>
+      <c r="K15" s="23">
+        <f>I15*D16</f>
+        <v>89677.181267918349</v>
+      </c>
+      <c r="L15">
+        <f>C16*I15</f>
+        <v>5.1618839999999997</v>
+      </c>
+      <c r="M15">
+        <f>I15*F16</f>
+        <v>9.500571428571428</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B16" s="30" t="s">
+        <v>435</v>
+      </c>
+      <c r="C16" s="7">
+        <f t="shared" ref="C16:C19" si="1">AVERAGEIFS($C$6:$T$6,$C$3:$T$3,$B16)</f>
+        <v>7.9169999999999998</v>
+      </c>
+      <c r="D16" s="23">
+        <f>AVERAGEIFS($C$7:$T$7,$C$3:$T$3,$B16)*$O$19/1000*$O$21</f>
+        <v>137541.68906122446</v>
+      </c>
+      <c r="E16" s="23">
+        <f t="shared" ref="E16:E19" si="2">AVERAGEIFS($C$9:$T$9,$C$3:$T$3,$B16)</f>
+        <v>30714.285714285714</v>
+      </c>
+      <c r="F16" s="23">
+        <f t="shared" ref="F16:F19" si="3">AVERAGEIFS($C$7:$T$7,$C$3:$T$3,$B16)</f>
+        <v>14.571428571428571</v>
+      </c>
+      <c r="G16" s="23"/>
+      <c r="H16" t="s">
+        <v>472</v>
+      </c>
+      <c r="I16" s="31">
+        <v>0.13650000000000001</v>
+      </c>
+      <c r="J16" s="23">
+        <f>I16*E17</f>
+        <v>2730</v>
+      </c>
+      <c r="K16" s="23">
+        <f>I16*D17</f>
+        <v>42518.585966999999</v>
+      </c>
+      <c r="L16">
+        <f>I16*C17</f>
+        <v>0.69026154166666676</v>
+      </c>
+      <c r="M16">
+        <f>I16*F17</f>
+        <v>4.5045000000000002</v>
+      </c>
+      <c r="O16" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="17" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B17" s="30" t="s">
+        <v>436</v>
+      </c>
+      <c r="C17" s="7">
+        <f t="shared" si="1"/>
+        <v>5.056861111111111</v>
+      </c>
+      <c r="D17" s="23">
+        <f>AVERAGEIFS($C$7:$T$7,$C$3:$T$3,$B17)*$O$19/1000*$O$21</f>
+        <v>311491.47228571423</v>
+      </c>
+      <c r="E17" s="23">
+        <f t="shared" si="2"/>
+        <v>20000</v>
+      </c>
+      <c r="F17" s="23">
+        <f t="shared" si="3"/>
+        <v>33</v>
+      </c>
+      <c r="G17" s="23"/>
+      <c r="H17" t="s">
+        <v>474</v>
+      </c>
+      <c r="I17" s="31">
+        <v>0.20050000000000001</v>
+      </c>
+      <c r="J17" s="23">
+        <f>I17*E19</f>
+        <v>1804.5</v>
+      </c>
+      <c r="K17" s="23">
+        <f>I17*D19</f>
+        <v>859216.18932580936</v>
+      </c>
+      <c r="L17">
+        <f>I17*C19</f>
+        <v>4.5268889999999997</v>
+      </c>
+      <c r="M17">
+        <f>I17*F19</f>
+        <v>91.027000000000001</v>
+      </c>
+      <c r="O17">
+        <v>9</v>
+      </c>
+      <c r="P17" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="18" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B18" s="30" t="s">
+        <v>437</v>
+      </c>
+      <c r="C18" s="7">
+        <f t="shared" si="1"/>
+        <v>5.5236111111111121</v>
+      </c>
+      <c r="D18" s="23">
+        <f>AVERAGEIFS($C$7:$T$7,$C$3:$T$3,$B18)*$O$19/1000*$O$21</f>
+        <v>217100.11704761902</v>
+      </c>
+      <c r="E18" s="23">
+        <f t="shared" si="2"/>
+        <v>12000</v>
+      </c>
+      <c r="F18" s="23">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="G18" s="23"/>
+      <c r="H18" t="s">
+        <v>476</v>
+      </c>
+      <c r="I18" s="31">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="J18" s="23">
+        <f>I18*E16</f>
+        <v>337.85714285714283</v>
+      </c>
+      <c r="K18" s="23">
+        <f>I18*D16</f>
+        <v>1512.9585796734689</v>
+      </c>
+      <c r="L18">
+        <f>I18*C16</f>
+        <v>8.7086999999999998E-2</v>
+      </c>
+      <c r="M18">
+        <f>I18*F16</f>
+        <v>0.16028571428571428</v>
+      </c>
+    </row>
+    <row r="19" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B19" s="30" t="s">
+        <v>438</v>
+      </c>
+      <c r="C19" s="7">
+        <f t="shared" si="1"/>
+        <v>22.577999999999999</v>
+      </c>
+      <c r="D19" s="23">
+        <f>AVERAGEIFS($C$7:$T$7,$C$3:$T$3,$B19)*$O$19/1000*$O$21</f>
+        <v>4285367.527809523</v>
+      </c>
+      <c r="E19" s="23">
+        <f t="shared" si="2"/>
+        <v>9000</v>
+      </c>
+      <c r="F19" s="23">
+        <f t="shared" si="3"/>
+        <v>454</v>
+      </c>
+      <c r="G19" s="23"/>
+      <c r="J19" s="32">
+        <f>SUM(J15:J18)</f>
+        <v>24898.071428571428</v>
+      </c>
+      <c r="K19" s="32">
+        <f>SUM(K15:K18)</f>
+        <v>992924.91514040111</v>
+      </c>
+      <c r="L19" s="33">
+        <f>SUM(L15:L18)</f>
+        <v>10.466121541666666</v>
+      </c>
+      <c r="M19" s="32">
+        <f>SUM(M15:M18)</f>
+        <v>105.19235714285715</v>
+      </c>
+      <c r="O19" s="32">
+        <f>J19/9</f>
+        <v>2766.4523809523807</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="20" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="J20" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="L20" t="s">
+        <v>462</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="21" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="O21">
+        <v>3412</v>
+      </c>
+      <c r="P21" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="23" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="O23" s="34">
+        <f>L19/K19</f>
+        <v>1.0540697873601793E-5</v>
+      </c>
+      <c r="P23" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="24" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="25" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="27" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B27" s="31">
+        <f>0.35</f>
+        <v>0.35</v>
+      </c>
+      <c r="C27" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="28" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B28">
+        <f>O23*B27</f>
+        <v>3.6892442557606274E-6</v>
+      </c>
+      <c r="C28" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="31" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="32" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>486</v>
+      </c>
+      <c r="C32" t="s">
+        <v>487</v>
+      </c>
+      <c r="D32" t="s">
+        <v>488</v>
+      </c>
+      <c r="E32" t="s">
+        <v>489</v>
+      </c>
+      <c r="F32" t="s">
+        <v>490</v>
+      </c>
+      <c r="G32" t="s">
+        <v>491</v>
+      </c>
+      <c r="H32" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>462</v>
+      </c>
+      <c r="B33">
+        <v>3579</v>
+      </c>
+      <c r="C33">
+        <v>649</v>
+      </c>
+      <c r="D33">
+        <v>849</v>
+      </c>
+      <c r="E33">
+        <v>926</v>
+      </c>
+      <c r="F33">
+        <v>399.99</v>
+      </c>
+      <c r="G33">
+        <v>1299</v>
+      </c>
+      <c r="H33">
+        <v>999</v>
+      </c>
+      <c r="I33" s="23">
+        <f>AVERAGE(Lighting!B33:H33)</f>
+        <v>1242.9985714285715</v>
+      </c>
+      <c r="J33" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>463</v>
+      </c>
+      <c r="B34">
+        <v>10000</v>
+      </c>
+      <c r="C34">
+        <v>5300</v>
+      </c>
+      <c r="D34">
+        <v>7500</v>
+      </c>
+      <c r="E34">
+        <v>9500</v>
+      </c>
+      <c r="F34">
+        <v>5600</v>
+      </c>
+      <c r="G34">
+        <v>13000</v>
+      </c>
+      <c r="H34">
+        <f>AVERAGE(10000,8000)</f>
+        <v>9000</v>
+      </c>
+      <c r="I34" s="23">
+        <f>AVERAGE(Lighting!B34:H34)</f>
+        <v>8557.1428571428569</v>
+      </c>
+      <c r="J34" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B35">
+        <f>B33/B34</f>
+        <v>0.3579</v>
+      </c>
+      <c r="C35">
+        <f t="shared" ref="C35:H35" si="4">C33/C34</f>
+        <v>0.12245283018867925</v>
+      </c>
+      <c r="D35">
+        <f t="shared" si="4"/>
+        <v>0.1132</v>
+      </c>
+      <c r="E35">
+        <f t="shared" si="4"/>
+        <v>9.747368421052631E-2</v>
+      </c>
+      <c r="F35">
+        <f t="shared" si="4"/>
+        <v>7.142678571428572E-2</v>
+      </c>
+      <c r="G35">
+        <f t="shared" si="4"/>
+        <v>9.992307692307692E-2</v>
+      </c>
+      <c r="H35">
+        <f t="shared" si="4"/>
+        <v>0.111</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I37" s="23">
+        <f>I33*M19/I34</f>
+        <v>15.280094283412833</v>
+      </c>
+      <c r="J37" t="s">
+        <v>462</v>
+      </c>
+      <c r="K37" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I38">
+        <f>I37/K19*B27</f>
+        <v>5.3861403995872857E-6</v>
+      </c>
+      <c r="K38" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I39" s="34">
+        <f>I38+B28</f>
+        <v>9.0753846553479132E-6</v>
+      </c>
+      <c r="K39" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C42" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D43" t="s">
+        <v>499</v>
+      </c>
+      <c r="E43" t="s">
+        <v>472</v>
+      </c>
+      <c r="F43" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B44" t="s">
+        <v>502</v>
+      </c>
+      <c r="C44" t="s">
+        <v>498</v>
+      </c>
+      <c r="D44">
+        <f>C6</f>
+        <v>1.3</v>
+      </c>
+      <c r="E44">
+        <v>2.99</v>
+      </c>
+      <c r="F44">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C46" t="s">
+        <v>500</v>
+      </c>
+      <c r="D46">
+        <f>AVERAGE(1.3,1.83)</f>
+        <v>1.5649999999999999</v>
+      </c>
+      <c r="E46">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B48" t="s">
+        <v>442</v>
+      </c>
+      <c r="C48" t="s">
+        <v>503</v>
+      </c>
+      <c r="E48">
+        <f>L6</f>
+        <v>5.1522500000000004</v>
+      </c>
+      <c r="F48">
+        <f>I6</f>
+        <v>12.494</v>
+      </c>
+    </row>
+    <row r="50" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C50" t="s">
+        <v>436</v>
+      </c>
+      <c r="D50" t="s">
+        <v>436</v>
+      </c>
+      <c r="E50" t="s">
+        <v>436</v>
+      </c>
+      <c r="F50" t="s">
+        <v>436</v>
+      </c>
+      <c r="G50" t="s">
+        <v>435</v>
+      </c>
+      <c r="H50" t="s">
+        <v>435</v>
+      </c>
+      <c r="I50" t="s">
+        <v>435</v>
+      </c>
+      <c r="J50" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="51" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C51" t="s">
+        <v>504</v>
+      </c>
+      <c r="D51" t="s">
+        <v>506</v>
+      </c>
+      <c r="E51" t="s">
+        <v>508</v>
+      </c>
+      <c r="F51" t="s">
+        <v>509</v>
+      </c>
+      <c r="G51" t="s">
+        <v>511</v>
+      </c>
+      <c r="H51" t="s">
+        <v>514</v>
+      </c>
+      <c r="I51" t="s">
+        <v>516</v>
+      </c>
+      <c r="J51" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="52" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C52">
+        <v>32</v>
+      </c>
+      <c r="D52">
+        <v>32</v>
+      </c>
+      <c r="E52">
+        <v>32</v>
+      </c>
+      <c r="F52">
+        <v>25</v>
+      </c>
+      <c r="G52">
+        <v>18</v>
+      </c>
+      <c r="H52">
+        <v>15</v>
+      </c>
+      <c r="I52">
+        <v>22</v>
+      </c>
+      <c r="J52">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="53" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C53">
+        <v>2600</v>
+      </c>
+      <c r="D53">
+        <v>2800</v>
+      </c>
+      <c r="E53">
+        <v>2800</v>
+      </c>
+      <c r="F53">
+        <v>2225</v>
+      </c>
+      <c r="G53">
+        <v>2300</v>
+      </c>
+      <c r="H53">
+        <v>2100</v>
+      </c>
+      <c r="I53">
+        <v>2860</v>
+      </c>
+      <c r="J53">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="54" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C54">
+        <v>3.17</v>
+      </c>
+      <c r="D54">
+        <v>6.29</v>
+      </c>
+      <c r="E54">
+        <v>5.33</v>
+      </c>
+      <c r="F54">
+        <v>6.9</v>
+      </c>
+      <c r="G54">
+        <f>224.99/25</f>
+        <v>8.9996000000000009</v>
+      </c>
+      <c r="H54">
+        <v>14.58</v>
+      </c>
+      <c r="I54">
+        <f>224.99/30</f>
+        <v>7.4996666666666671</v>
+      </c>
+      <c r="J54">
+        <f>193.99/25</f>
+        <v>7.7596000000000007</v>
+      </c>
+    </row>
+    <row r="55" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C55" t="s">
+        <v>505</v>
+      </c>
+      <c r="D55" t="s">
+        <v>507</v>
+      </c>
+      <c r="E55" t="s">
+        <v>501</v>
+      </c>
+      <c r="F55" t="s">
+        <v>510</v>
+      </c>
+      <c r="G55" t="s">
+        <v>513</v>
+      </c>
+      <c r="H55" t="s">
+        <v>513</v>
+      </c>
+      <c r="I55" t="s">
+        <v>513</v>
+      </c>
+      <c r="J55" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="56" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="F56" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="58" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="F58" t="s">
+        <v>517</v>
+      </c>
+      <c r="G58" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="59" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="F59">
+        <f>AVERAGE(C52:F52)</f>
+        <v>30.25</v>
+      </c>
+      <c r="G59">
+        <f>AVERAGE(G52:J52)</f>
+        <v>18</v>
+      </c>
+      <c r="H59" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="60" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="F60">
+        <f t="shared" ref="F60:F61" si="5">AVERAGE(C53:F53)</f>
+        <v>2606.25</v>
+      </c>
+      <c r="G60">
+        <f t="shared" ref="G60:G61" si="6">AVERAGE(G53:J53)</f>
+        <v>2440</v>
+      </c>
+      <c r="H60" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="61" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="F61">
+        <f t="shared" si="5"/>
+        <v>5.4225000000000003</v>
+      </c>
+      <c r="G61">
+        <f t="shared" si="6"/>
+        <v>9.709716666666667</v>
+      </c>
+      <c r="H61" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="63" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="G63">
+        <f>((G61-F61)/F61)/((1/G59-1/F59)/(1/F59))</f>
+        <v>1.1617489485420724</v>
+      </c>
+      <c r="H63" t="s">
+        <v>318</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1D5271D-8741-40B6-92F2-97D4F5B6382F}">
+  <dimension ref="A1:K13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="33.5703125" customWidth="1"/>
+    <col min="2" max="8" width="13.5703125" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>13</v>
       </c>
@@ -7557,30 +10153,36 @@
         <v>345</v>
       </c>
       <c r="I1" s="25" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+        <v>429</v>
+      </c>
+      <c r="J1" s="25" t="s">
+        <v>430</v>
+      </c>
+      <c r="K1" s="25" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="27">
+      <c r="B2" s="26">
         <f>AVERAGE('indst heat pumps'!E92,'indst heat pumps'!B63)</f>
         <v>1.4326814351134223</v>
       </c>
-      <c r="C2" s="27">
+      <c r="C2" s="26">
         <f>AVERAGE('indst heat pumps'!E92,'indst heat pumps'!B63)</f>
         <v>1.4326814351134223</v>
       </c>
-      <c r="D2" s="27">
+      <c r="D2" s="26">
         <f>AVERAGE(C4,C6)</f>
         <v>4.0277954796628537</v>
       </c>
-      <c r="E2" s="28">
+      <c r="E2" s="27">
         <f>D2</f>
         <v>4.0277954796628537</v>
       </c>
-      <c r="F2" s="27">
+      <c r="F2" s="26">
         <f>'process chillers'!$K$15</f>
         <v>0.84489777592279791</v>
       </c>
@@ -7588,419 +10190,515 @@
         <f>AVERAGE('fans-blowers'!D36,'indst motors'!H49,pumps!W47)</f>
         <v>2.5525704426134292</v>
       </c>
-      <c r="H2" s="28">
-        <f>AVERAGE($B$2:$G$13)</f>
+      <c r="H2" s="27">
+        <f t="shared" ref="H2:H13" si="0">AVERAGE($B$2:$G$13)</f>
         <v>3.1863586362595919</v>
       </c>
-      <c r="I2" s="28">
-        <f t="shared" ref="I2:I13" si="0">AVERAGE($B$2:$G$13)</f>
+      <c r="I2" s="27">
+        <f>AVERAGE(B2:C2)</f>
+        <v>1.4326814351134223</v>
+      </c>
+      <c r="J2" s="26">
+        <f>Lighting!G63</f>
+        <v>1.1617489485420724</v>
+      </c>
+      <c r="K2" s="27">
+        <f>H2</f>
         <v>3.1863586362595919</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="27">
+      <c r="B3" s="26">
         <f>'solid fuel boilers'!$J$19</f>
         <v>2.6579492384232659</v>
       </c>
-      <c r="C3" s="28">
+      <c r="C3" s="27">
         <f>$C$6</f>
         <v>2.1980839095148221</v>
       </c>
-      <c r="D3" s="28">
+      <c r="D3" s="27">
         <f>C3</f>
         <v>2.1980839095148221</v>
       </c>
-      <c r="E3" s="28">
+      <c r="E3" s="27">
         <f t="shared" ref="E3:E13" si="1">D3</f>
         <v>2.1980839095148221</v>
       </c>
-      <c r="F3" s="28">
+      <c r="F3" s="27">
         <f>$F$2</f>
         <v>0.84489777592279791</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="27">
         <f>$G$2</f>
         <v>2.5525704426134292</v>
       </c>
-      <c r="H3" s="28">
-        <f t="shared" ref="H3:H13" si="2">AVERAGE($B$2:$G$13)</f>
-        <v>3.1863586362595919</v>
-      </c>
-      <c r="I3" s="28">
+      <c r="H3" s="27">
         <f t="shared" si="0"/>
         <v>3.1863586362595919</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I3" s="27">
+        <f t="shared" ref="I3:I13" si="2">AVERAGE(B3:C3)</f>
+        <v>2.4280165739690442</v>
+      </c>
+      <c r="J3" s="27">
+        <f>$J$2</f>
+        <v>1.1617489485420724</v>
+      </c>
+      <c r="K3" s="27">
+        <f t="shared" ref="K3:K13" si="3">H3</f>
+        <v>3.1863586362595919</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="27">
+      <c r="B4" s="26">
         <f>AVERAGE('comm boilers'!M4:M5,'comm boilers'!M8:M9,'indst boilers'!O26)</f>
         <v>8.9979161894765802</v>
       </c>
-      <c r="C4" s="27">
+      <c r="C4" s="26">
         <f>AVERAGE(furnaces!H5,furnaces!H12,furnaces!H19)</f>
         <v>5.8575070498108852</v>
       </c>
-      <c r="D4" s="28">
-        <f t="shared" ref="D4:D13" si="3">C4</f>
+      <c r="D4" s="27">
+        <f t="shared" ref="D4:D13" si="4">C4</f>
         <v>5.8575070498108852</v>
       </c>
-      <c r="E4" s="28">
+      <c r="E4" s="27">
         <f t="shared" si="1"/>
         <v>5.8575070498108852</v>
       </c>
-      <c r="F4" s="28">
-        <f t="shared" ref="F4:F13" si="4">$F$2</f>
+      <c r="F4" s="27">
+        <f t="shared" ref="F4:F13" si="5">$F$2</f>
         <v>0.84489777592279791</v>
       </c>
-      <c r="G4" s="7">
-        <f t="shared" ref="G4:G13" si="5">$G$2</f>
+      <c r="G4" s="27">
+        <f t="shared" ref="G4:G13" si="6">$G$2</f>
         <v>2.5525704426134292</v>
       </c>
-      <c r="H4" s="28">
-        <f t="shared" si="2"/>
-        <v>3.1863586362595919</v>
-      </c>
-      <c r="I4" s="28">
+      <c r="H4" s="27">
         <f t="shared" si="0"/>
         <v>3.1863586362595919</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I4" s="27">
+        <f t="shared" si="2"/>
+        <v>7.4277116196437323</v>
+      </c>
+      <c r="J4" s="27">
+        <f t="shared" ref="J4:J13" si="7">$J$2</f>
+        <v>1.1617489485420724</v>
+      </c>
+      <c r="K4" s="27">
+        <f t="shared" si="3"/>
+        <v>3.1863586362595919</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="28">
+      <c r="B5" s="27">
         <f>$B$3</f>
         <v>2.6579492384232659</v>
       </c>
-      <c r="C5" s="28">
+      <c r="C5" s="27">
         <f>$C$6</f>
         <v>2.1980839095148221</v>
       </c>
-      <c r="D5" s="28">
-        <f t="shared" si="3"/>
+      <c r="D5" s="27">
+        <f t="shared" si="4"/>
         <v>2.1980839095148221</v>
       </c>
-      <c r="E5" s="28">
+      <c r="E5" s="27">
         <f t="shared" si="1"/>
         <v>2.1980839095148221</v>
       </c>
-      <c r="F5" s="28">
-        <f t="shared" si="4"/>
+      <c r="F5" s="27">
+        <f t="shared" si="5"/>
         <v>0.84489777592279791</v>
       </c>
-      <c r="G5" s="7">
-        <f t="shared" si="5"/>
+      <c r="G5" s="27">
+        <f t="shared" si="6"/>
         <v>2.5525704426134292</v>
       </c>
-      <c r="H5" s="28">
-        <f t="shared" si="2"/>
-        <v>3.1863586362595919</v>
-      </c>
-      <c r="I5" s="28">
+      <c r="H5" s="27">
         <f t="shared" si="0"/>
         <v>3.1863586362595919</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I5" s="27">
+        <f t="shared" si="2"/>
+        <v>2.4280165739690442</v>
+      </c>
+      <c r="J5" s="27">
+        <f t="shared" si="7"/>
+        <v>1.1617489485420724</v>
+      </c>
+      <c r="K5" s="27">
+        <f t="shared" si="3"/>
+        <v>3.1863586362595919</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="26">
         <f>AVERAGE('comm boilers'!M6:M7,'comm boilers'!M10:M11,'indst boilers'!O26)</f>
         <v>10.741730678741742</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="26">
         <f>furnaces!H26</f>
         <v>2.1980839095148221</v>
       </c>
-      <c r="D6" s="28">
-        <f t="shared" si="3"/>
+      <c r="D6" s="27">
+        <f t="shared" si="4"/>
         <v>2.1980839095148221</v>
       </c>
-      <c r="E6" s="28">
+      <c r="E6" s="27">
         <f t="shared" si="1"/>
         <v>2.1980839095148221</v>
       </c>
-      <c r="F6" s="28">
-        <f t="shared" si="4"/>
+      <c r="F6" s="27">
+        <f t="shared" si="5"/>
         <v>0.84489777592279791</v>
       </c>
-      <c r="G6" s="7">
-        <f t="shared" si="5"/>
+      <c r="G6" s="27">
+        <f t="shared" si="6"/>
         <v>2.5525704426134292</v>
       </c>
-      <c r="H6" s="28">
-        <f t="shared" si="2"/>
-        <v>3.1863586362595919</v>
-      </c>
-      <c r="I6" s="28">
+      <c r="H6" s="27">
         <f t="shared" si="0"/>
         <v>3.1863586362595919</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I6" s="27">
+        <f t="shared" si="2"/>
+        <v>6.4699072941282818</v>
+      </c>
+      <c r="J6" s="27">
+        <f t="shared" si="7"/>
+        <v>1.1617489485420724</v>
+      </c>
+      <c r="K6" s="27">
+        <f t="shared" si="3"/>
+        <v>3.1863586362595919</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="26">
         <f>AVERAGE(B2,B4,B6)</f>
         <v>7.0574427677772489</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="26">
         <f>AVERAGE(C2,C4,C6)</f>
         <v>3.1627574648130428</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="26">
         <f>AVERAGE(D2,D4,D6)</f>
         <v>4.0277954796628537</v>
       </c>
-      <c r="E7" s="28">
+      <c r="E7" s="27">
         <f t="shared" si="1"/>
         <v>4.0277954796628537</v>
       </c>
-      <c r="F7" s="28">
-        <f t="shared" si="4"/>
+      <c r="F7" s="27">
+        <f t="shared" si="5"/>
         <v>0.84489777592279791</v>
       </c>
-      <c r="G7" s="7">
-        <f t="shared" si="5"/>
+      <c r="G7" s="27">
+        <f t="shared" si="6"/>
         <v>2.5525704426134292</v>
       </c>
-      <c r="H7" s="28">
-        <f t="shared" si="2"/>
-        <v>3.1863586362595919</v>
-      </c>
-      <c r="I7" s="28">
+      <c r="H7" s="27">
         <f t="shared" si="0"/>
         <v>3.1863586362595919</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I7" s="27">
+        <f t="shared" si="2"/>
+        <v>5.110100116295146</v>
+      </c>
+      <c r="J7" s="27">
+        <f t="shared" si="7"/>
+        <v>1.1617489485420724</v>
+      </c>
+      <c r="K7" s="27">
+        <f t="shared" si="3"/>
+        <v>3.1863586362595919</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="28">
-        <f t="shared" ref="B8:B9" si="6">$B$6</f>
+      <c r="B8" s="27">
+        <f t="shared" ref="B8:B9" si="8">$B$6</f>
         <v>10.741730678741742</v>
       </c>
-      <c r="C8" s="28">
-        <f t="shared" ref="C8:C9" si="7">$C$6</f>
+      <c r="C8" s="27">
+        <f t="shared" ref="C8:C9" si="9">$C$6</f>
         <v>2.1980839095148221</v>
       </c>
-      <c r="D8" s="28">
-        <f t="shared" si="3"/>
+      <c r="D8" s="27">
+        <f t="shared" si="4"/>
         <v>2.1980839095148221</v>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="27">
         <f t="shared" si="1"/>
         <v>2.1980839095148221</v>
       </c>
-      <c r="F8" s="28">
-        <f t="shared" si="4"/>
+      <c r="F8" s="27">
+        <f t="shared" si="5"/>
         <v>0.84489777592279791</v>
       </c>
-      <c r="G8" s="7">
-        <f t="shared" si="5"/>
+      <c r="G8" s="27">
+        <f t="shared" si="6"/>
         <v>2.5525704426134292</v>
       </c>
-      <c r="H8" s="28">
-        <f t="shared" si="2"/>
-        <v>3.1863586362595919</v>
-      </c>
-      <c r="I8" s="28">
+      <c r="H8" s="27">
         <f t="shared" si="0"/>
         <v>3.1863586362595919</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I8" s="27">
+        <f t="shared" si="2"/>
+        <v>6.4699072941282818</v>
+      </c>
+      <c r="J8" s="27">
+        <f t="shared" si="7"/>
+        <v>1.1617489485420724</v>
+      </c>
+      <c r="K8" s="27">
+        <f t="shared" si="3"/>
+        <v>3.1863586362595919</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="28">
-        <f t="shared" si="6"/>
+      <c r="B9" s="27">
+        <f t="shared" si="8"/>
         <v>10.741730678741742</v>
       </c>
-      <c r="C9" s="28">
-        <f t="shared" si="7"/>
+      <c r="C9" s="27">
+        <f t="shared" si="9"/>
         <v>2.1980839095148221</v>
       </c>
-      <c r="D9" s="28">
-        <f t="shared" si="3"/>
+      <c r="D9" s="27">
+        <f t="shared" si="4"/>
         <v>2.1980839095148221</v>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="27">
         <f t="shared" si="1"/>
         <v>2.1980839095148221</v>
       </c>
-      <c r="F9" s="28">
-        <f t="shared" si="4"/>
+      <c r="F9" s="27">
+        <f t="shared" si="5"/>
         <v>0.84489777592279791</v>
       </c>
-      <c r="G9" s="7">
-        <f t="shared" si="5"/>
+      <c r="G9" s="27">
+        <f t="shared" si="6"/>
         <v>2.5525704426134292</v>
       </c>
-      <c r="H9" s="28">
-        <f t="shared" si="2"/>
-        <v>3.1863586362595919</v>
-      </c>
-      <c r="I9" s="28">
+      <c r="H9" s="27">
         <f t="shared" si="0"/>
         <v>3.1863586362595919</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I9" s="27">
+        <f t="shared" si="2"/>
+        <v>6.4699072941282818</v>
+      </c>
+      <c r="J9" s="27">
+        <f t="shared" si="7"/>
+        <v>1.1617489485420724</v>
+      </c>
+      <c r="K9" s="27">
+        <f t="shared" si="3"/>
+        <v>3.1863586362595919</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="28">
+      <c r="B10" s="27">
         <f>$B$4</f>
         <v>8.9979161894765802</v>
       </c>
-      <c r="C10" s="28">
+      <c r="C10" s="27">
         <f>$C$6</f>
         <v>2.1980839095148221</v>
       </c>
-      <c r="D10" s="28">
-        <f t="shared" si="3"/>
+      <c r="D10" s="27">
+        <f t="shared" si="4"/>
         <v>2.1980839095148221</v>
       </c>
-      <c r="E10" s="28">
+      <c r="E10" s="27">
         <f t="shared" si="1"/>
         <v>2.1980839095148221</v>
       </c>
-      <c r="F10" s="28">
-        <f t="shared" si="4"/>
+      <c r="F10" s="27">
+        <f t="shared" si="5"/>
         <v>0.84489777592279791</v>
       </c>
-      <c r="G10" s="7">
-        <f t="shared" si="5"/>
+      <c r="G10" s="27">
+        <f t="shared" si="6"/>
         <v>2.5525704426134292</v>
       </c>
-      <c r="H10" s="28">
-        <f t="shared" si="2"/>
-        <v>3.1863586362595919</v>
-      </c>
-      <c r="I10" s="28">
+      <c r="H10" s="27">
         <f t="shared" si="0"/>
         <v>3.1863586362595919</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I10" s="27">
+        <f t="shared" si="2"/>
+        <v>5.5980000494957007</v>
+      </c>
+      <c r="J10" s="27">
+        <f t="shared" si="7"/>
+        <v>1.1617489485420724</v>
+      </c>
+      <c r="K10" s="27">
+        <f t="shared" si="3"/>
+        <v>3.1863586362595919</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="28">
+      <c r="B11" s="27">
         <f>$B$4</f>
         <v>8.9979161894765802</v>
       </c>
-      <c r="C11" s="28">
-        <f t="shared" ref="C11:C13" si="8">$C$6</f>
+      <c r="C11" s="27">
+        <f t="shared" ref="C11:C13" si="10">$C$6</f>
         <v>2.1980839095148221</v>
       </c>
-      <c r="D11" s="28">
-        <f t="shared" si="3"/>
+      <c r="D11" s="27">
+        <f t="shared" si="4"/>
         <v>2.1980839095148221</v>
       </c>
-      <c r="E11" s="28">
+      <c r="E11" s="27">
         <f t="shared" si="1"/>
         <v>2.1980839095148221</v>
       </c>
-      <c r="F11" s="28">
-        <f t="shared" si="4"/>
+      <c r="F11" s="27">
+        <f t="shared" si="5"/>
         <v>0.84489777592279791</v>
       </c>
-      <c r="G11" s="7">
-        <f t="shared" si="5"/>
+      <c r="G11" s="27">
+        <f t="shared" si="6"/>
         <v>2.5525704426134292</v>
       </c>
-      <c r="H11" s="28">
-        <f t="shared" si="2"/>
-        <v>3.1863586362595919</v>
-      </c>
-      <c r="I11" s="28">
+      <c r="H11" s="27">
         <f t="shared" si="0"/>
         <v>3.1863586362595919</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I11" s="27">
+        <f t="shared" si="2"/>
+        <v>5.5980000494957007</v>
+      </c>
+      <c r="J11" s="27">
+        <f t="shared" si="7"/>
+        <v>1.1617489485420724</v>
+      </c>
+      <c r="K11" s="27">
+        <f t="shared" si="3"/>
+        <v>3.1863586362595919</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="28">
-        <f t="shared" ref="B12:B13" si="9">$B$4</f>
+      <c r="B12" s="27">
+        <f t="shared" ref="B12:B13" si="11">$B$4</f>
         <v>8.9979161894765802</v>
       </c>
-      <c r="C12" s="28">
-        <f t="shared" si="8"/>
+      <c r="C12" s="27">
+        <f t="shared" si="10"/>
         <v>2.1980839095148221</v>
       </c>
-      <c r="D12" s="28">
-        <f t="shared" si="3"/>
+      <c r="D12" s="27">
+        <f t="shared" si="4"/>
         <v>2.1980839095148221</v>
       </c>
-      <c r="E12" s="28">
+      <c r="E12" s="27">
         <f t="shared" si="1"/>
         <v>2.1980839095148221</v>
       </c>
-      <c r="F12" s="28">
-        <f t="shared" si="4"/>
+      <c r="F12" s="27">
+        <f t="shared" si="5"/>
         <v>0.84489777592279791</v>
       </c>
-      <c r="G12" s="7">
-        <f t="shared" si="5"/>
+      <c r="G12" s="27">
+        <f t="shared" si="6"/>
         <v>2.5525704426134292</v>
       </c>
-      <c r="H12" s="28">
-        <f t="shared" si="2"/>
-        <v>3.1863586362595919</v>
-      </c>
-      <c r="I12" s="28">
+      <c r="H12" s="27">
         <f t="shared" si="0"/>
         <v>3.1863586362595919</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I12" s="27">
+        <f t="shared" si="2"/>
+        <v>5.5980000494957007</v>
+      </c>
+      <c r="J12" s="27">
+        <f t="shared" si="7"/>
+        <v>1.1617489485420724</v>
+      </c>
+      <c r="K12" s="27">
+        <f t="shared" si="3"/>
+        <v>3.1863586362595919</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="28">
-        <f t="shared" si="9"/>
+      <c r="B13" s="27">
+        <f t="shared" si="11"/>
         <v>8.9979161894765802</v>
       </c>
-      <c r="C13" s="28">
-        <f t="shared" si="8"/>
+      <c r="C13" s="27">
+        <f t="shared" si="10"/>
         <v>2.1980839095148221</v>
       </c>
-      <c r="D13" s="28">
-        <f t="shared" si="3"/>
+      <c r="D13" s="27">
+        <f t="shared" si="4"/>
         <v>2.1980839095148221</v>
       </c>
-      <c r="E13" s="28">
+      <c r="E13" s="27">
         <f t="shared" si="1"/>
         <v>2.1980839095148221</v>
       </c>
-      <c r="F13" s="28">
-        <f t="shared" si="4"/>
+      <c r="F13" s="27">
+        <f t="shared" si="5"/>
         <v>0.84489777592279791</v>
       </c>
-      <c r="G13" s="7">
-        <f t="shared" si="5"/>
+      <c r="G13" s="27">
+        <f t="shared" si="6"/>
         <v>2.5525704426134292</v>
       </c>
-      <c r="H13" s="28">
+      <c r="H13" s="27">
+        <f t="shared" si="0"/>
+        <v>3.1863586362595919</v>
+      </c>
+      <c r="I13" s="27">
         <f t="shared" si="2"/>
-        <v>3.1863586362595919</v>
-      </c>
-      <c r="I13" s="28">
-        <f t="shared" si="0"/>
+        <v>5.5980000494957007</v>
+      </c>
+      <c r="J13" s="27">
+        <f t="shared" si="7"/>
+        <v>1.1617489485420724</v>
+      </c>
+      <c r="K13" s="27">
+        <f t="shared" si="3"/>
         <v>3.1863586362595919</v>
       </c>
     </row>
@@ -8009,19 +10707,20 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BB977EF-DFFE-4EEF-A0E1-DBBDDDFA9996}">
   <sheetPr>
     <tabColor theme="3" tint="9.9978637043366805E-2"/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:K13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.54296875" customWidth="1"/>
-    <col min="2" max="9" width="13.54296875" customWidth="1"/>
+    <col min="1" max="1" width="33.5703125" customWidth="1"/>
+    <col min="2" max="7" width="13.5703125" customWidth="1"/>
+    <col min="8" max="11" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>13</v>
       </c>
@@ -8047,456 +10746,558 @@
         <v>345</v>
       </c>
       <c r="I1" s="25" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+        <v>429</v>
+      </c>
+      <c r="J1" s="25" t="s">
+        <v>430</v>
+      </c>
+      <c r="K1" s="25" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="28">
+      <c r="B2" s="27">
         <f>calcs!B2</f>
         <v>1.4326814351134223</v>
       </c>
-      <c r="C2" s="28">
+      <c r="C2" s="27">
         <f>calcs!C2</f>
         <v>1.4326814351134223</v>
       </c>
-      <c r="D2" s="28">
+      <c r="D2" s="27">
         <f>calcs!D2</f>
         <v>4.0277954796628537</v>
       </c>
-      <c r="E2" s="28">
+      <c r="E2" s="27">
         <f>calcs!E2</f>
         <v>4.0277954796628537</v>
       </c>
-      <c r="F2" s="28">
+      <c r="F2" s="27">
         <f>calcs!F2</f>
         <v>0.84489777592279791</v>
       </c>
-      <c r="G2" s="28">
+      <c r="G2" s="27">
         <f>calcs!G2</f>
         <v>2.5525704426134292</v>
       </c>
-      <c r="H2" s="28">
+      <c r="H2" s="27">
         <f>calcs!H2</f>
         <v>3.1863586362595919</v>
       </c>
-      <c r="I2" s="28">
+      <c r="I2" s="27">
         <f>calcs!I2</f>
+        <v>1.4326814351134223</v>
+      </c>
+      <c r="J2" s="27">
+        <f>calcs!J2</f>
+        <v>1.1617489485420724</v>
+      </c>
+      <c r="K2" s="27">
+        <f>calcs!K2</f>
         <v>3.1863586362595919</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="28">
+      <c r="B3" s="27">
         <f>calcs!B3</f>
         <v>2.6579492384232659</v>
       </c>
-      <c r="C3" s="28">
+      <c r="C3" s="27">
         <f>calcs!C3</f>
         <v>2.1980839095148221</v>
       </c>
-      <c r="D3" s="28">
+      <c r="D3" s="27">
         <f>calcs!D3</f>
         <v>2.1980839095148221</v>
       </c>
-      <c r="E3" s="28">
+      <c r="E3" s="27">
         <f>calcs!E3</f>
         <v>2.1980839095148221</v>
       </c>
-      <c r="F3" s="28">
+      <c r="F3" s="27">
         <f>calcs!F3</f>
         <v>0.84489777592279791</v>
       </c>
-      <c r="G3" s="28">
+      <c r="G3" s="27">
         <f>calcs!G3</f>
         <v>2.5525704426134292</v>
       </c>
-      <c r="H3" s="28">
+      <c r="H3" s="27">
         <f>calcs!H3</f>
         <v>3.1863586362595919</v>
       </c>
-      <c r="I3" s="28">
+      <c r="I3" s="27">
         <f>calcs!I3</f>
+        <v>2.4280165739690442</v>
+      </c>
+      <c r="J3" s="27">
+        <f>calcs!J3</f>
+        <v>1.1617489485420724</v>
+      </c>
+      <c r="K3" s="27">
+        <f>calcs!K3</f>
         <v>3.1863586362595919</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="28">
+      <c r="B4" s="27">
         <f>calcs!B4</f>
         <v>8.9979161894765802</v>
       </c>
-      <c r="C4" s="28">
+      <c r="C4" s="27">
         <f>calcs!C4</f>
         <v>5.8575070498108852</v>
       </c>
-      <c r="D4" s="28">
+      <c r="D4" s="27">
         <f>calcs!D4</f>
         <v>5.8575070498108852</v>
       </c>
-      <c r="E4" s="28">
+      <c r="E4" s="27">
         <f>calcs!E4</f>
         <v>5.8575070498108852</v>
       </c>
-      <c r="F4" s="28">
+      <c r="F4" s="27">
         <f>calcs!F4</f>
         <v>0.84489777592279791</v>
       </c>
-      <c r="G4" s="28">
+      <c r="G4" s="27">
         <f>calcs!G4</f>
         <v>2.5525704426134292</v>
       </c>
-      <c r="H4" s="28">
+      <c r="H4" s="27">
         <f>calcs!H4</f>
         <v>3.1863586362595919</v>
       </c>
-      <c r="I4" s="28">
+      <c r="I4" s="27">
         <f>calcs!I4</f>
+        <v>7.4277116196437323</v>
+      </c>
+      <c r="J4" s="27">
+        <f>calcs!J4</f>
+        <v>1.1617489485420724</v>
+      </c>
+      <c r="K4" s="27">
+        <f>calcs!K4</f>
         <v>3.1863586362595919</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="28">
+      <c r="B5" s="27">
         <f>calcs!B5</f>
         <v>2.6579492384232659</v>
       </c>
-      <c r="C5" s="28">
+      <c r="C5" s="27">
         <f>calcs!C5</f>
         <v>2.1980839095148221</v>
       </c>
-      <c r="D5" s="28">
+      <c r="D5" s="27">
         <f>calcs!D5</f>
         <v>2.1980839095148221</v>
       </c>
-      <c r="E5" s="28">
+      <c r="E5" s="27">
         <f>calcs!E5</f>
         <v>2.1980839095148221</v>
       </c>
-      <c r="F5" s="28">
+      <c r="F5" s="27">
         <f>calcs!F5</f>
         <v>0.84489777592279791</v>
       </c>
-      <c r="G5" s="28">
+      <c r="G5" s="27">
         <f>calcs!G5</f>
         <v>2.5525704426134292</v>
       </c>
-      <c r="H5" s="28">
+      <c r="H5" s="27">
         <f>calcs!H5</f>
         <v>3.1863586362595919</v>
       </c>
-      <c r="I5" s="28">
+      <c r="I5" s="27">
         <f>calcs!I5</f>
+        <v>2.4280165739690442</v>
+      </c>
+      <c r="J5" s="27">
+        <f>calcs!J5</f>
+        <v>1.1617489485420724</v>
+      </c>
+      <c r="K5" s="27">
+        <f>calcs!K5</f>
         <v>3.1863586362595919</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="28">
+      <c r="B6" s="27">
         <f>calcs!B6</f>
         <v>10.741730678741742</v>
       </c>
-      <c r="C6" s="28">
+      <c r="C6" s="27">
         <f>calcs!C6</f>
         <v>2.1980839095148221</v>
       </c>
-      <c r="D6" s="28">
+      <c r="D6" s="27">
         <f>calcs!D6</f>
         <v>2.1980839095148221</v>
       </c>
-      <c r="E6" s="28">
+      <c r="E6" s="27">
         <f>calcs!E6</f>
         <v>2.1980839095148221</v>
       </c>
-      <c r="F6" s="28">
+      <c r="F6" s="27">
         <f>calcs!F6</f>
         <v>0.84489777592279791</v>
       </c>
-      <c r="G6" s="28">
+      <c r="G6" s="27">
         <f>calcs!G6</f>
         <v>2.5525704426134292</v>
       </c>
-      <c r="H6" s="28">
+      <c r="H6" s="27">
         <f>calcs!H6</f>
         <v>3.1863586362595919</v>
       </c>
-      <c r="I6" s="28">
+      <c r="I6" s="27">
         <f>calcs!I6</f>
+        <v>6.4699072941282818</v>
+      </c>
+      <c r="J6" s="27">
+        <f>calcs!J6</f>
+        <v>1.1617489485420724</v>
+      </c>
+      <c r="K6" s="27">
+        <f>calcs!K6</f>
         <v>3.1863586362595919</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="28">
+      <c r="B7" s="27">
         <f>calcs!B7</f>
         <v>7.0574427677772489</v>
       </c>
-      <c r="C7" s="28">
+      <c r="C7" s="27">
         <f>calcs!C7</f>
         <v>3.1627574648130428</v>
       </c>
-      <c r="D7" s="28">
+      <c r="D7" s="27">
         <f>calcs!D7</f>
         <v>4.0277954796628537</v>
       </c>
-      <c r="E7" s="28">
+      <c r="E7" s="27">
         <f>calcs!E7</f>
         <v>4.0277954796628537</v>
       </c>
-      <c r="F7" s="28">
+      <c r="F7" s="27">
         <f>calcs!F7</f>
         <v>0.84489777592279791</v>
       </c>
-      <c r="G7" s="28">
+      <c r="G7" s="27">
         <f>calcs!G7</f>
         <v>2.5525704426134292</v>
       </c>
-      <c r="H7" s="28">
+      <c r="H7" s="27">
         <f>calcs!H7</f>
         <v>3.1863586362595919</v>
       </c>
-      <c r="I7" s="28">
+      <c r="I7" s="27">
         <f>calcs!I7</f>
+        <v>5.110100116295146</v>
+      </c>
+      <c r="J7" s="27">
+        <f>calcs!J7</f>
+        <v>1.1617489485420724</v>
+      </c>
+      <c r="K7" s="27">
+        <f>calcs!K7</f>
         <v>3.1863586362595919</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="28">
+      <c r="B8" s="27">
         <f>calcs!B8</f>
         <v>10.741730678741742</v>
       </c>
-      <c r="C8" s="28">
+      <c r="C8" s="27">
         <f>calcs!C8</f>
         <v>2.1980839095148221</v>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="27">
         <f>calcs!D8</f>
         <v>2.1980839095148221</v>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="27">
         <f>calcs!E8</f>
         <v>2.1980839095148221</v>
       </c>
-      <c r="F8" s="28">
+      <c r="F8" s="27">
         <f>calcs!F8</f>
         <v>0.84489777592279791</v>
       </c>
-      <c r="G8" s="28">
+      <c r="G8" s="27">
         <f>calcs!G8</f>
         <v>2.5525704426134292</v>
       </c>
-      <c r="H8" s="28">
+      <c r="H8" s="27">
         <f>calcs!H8</f>
         <v>3.1863586362595919</v>
       </c>
-      <c r="I8" s="28">
+      <c r="I8" s="27">
         <f>calcs!I8</f>
+        <v>6.4699072941282818</v>
+      </c>
+      <c r="J8" s="27">
+        <f>calcs!J8</f>
+        <v>1.1617489485420724</v>
+      </c>
+      <c r="K8" s="27">
+        <f>calcs!K8</f>
         <v>3.1863586362595919</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="28">
+      <c r="B9" s="27">
         <f>calcs!B9</f>
         <v>10.741730678741742</v>
       </c>
-      <c r="C9" s="28">
+      <c r="C9" s="27">
         <f>calcs!C9</f>
         <v>2.1980839095148221</v>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="27">
         <f>calcs!D9</f>
         <v>2.1980839095148221</v>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="27">
         <f>calcs!E9</f>
         <v>2.1980839095148221</v>
       </c>
-      <c r="F9" s="28">
+      <c r="F9" s="27">
         <f>calcs!F9</f>
         <v>0.84489777592279791</v>
       </c>
-      <c r="G9" s="28">
+      <c r="G9" s="27">
         <f>calcs!G9</f>
         <v>2.5525704426134292</v>
       </c>
-      <c r="H9" s="28">
+      <c r="H9" s="27">
         <f>calcs!H9</f>
         <v>3.1863586362595919</v>
       </c>
-      <c r="I9" s="28">
+      <c r="I9" s="27">
         <f>calcs!I9</f>
+        <v>6.4699072941282818</v>
+      </c>
+      <c r="J9" s="27">
+        <f>calcs!J9</f>
+        <v>1.1617489485420724</v>
+      </c>
+      <c r="K9" s="27">
+        <f>calcs!K9</f>
         <v>3.1863586362595919</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="28">
+      <c r="B10" s="27">
         <f>calcs!B10</f>
         <v>8.9979161894765802</v>
       </c>
-      <c r="C10" s="28">
+      <c r="C10" s="27">
         <f>calcs!C10</f>
         <v>2.1980839095148221</v>
       </c>
-      <c r="D10" s="28">
+      <c r="D10" s="27">
         <f>calcs!D10</f>
         <v>2.1980839095148221</v>
       </c>
-      <c r="E10" s="28">
+      <c r="E10" s="27">
         <f>calcs!E10</f>
         <v>2.1980839095148221</v>
       </c>
-      <c r="F10" s="28">
+      <c r="F10" s="27">
         <f>calcs!F10</f>
         <v>0.84489777592279791</v>
       </c>
-      <c r="G10" s="28">
+      <c r="G10" s="27">
         <f>calcs!G10</f>
         <v>2.5525704426134292</v>
       </c>
-      <c r="H10" s="28">
+      <c r="H10" s="27">
         <f>calcs!H10</f>
         <v>3.1863586362595919</v>
       </c>
-      <c r="I10" s="28">
+      <c r="I10" s="27">
         <f>calcs!I10</f>
+        <v>5.5980000494957007</v>
+      </c>
+      <c r="J10" s="27">
+        <f>calcs!J10</f>
+        <v>1.1617489485420724</v>
+      </c>
+      <c r="K10" s="27">
+        <f>calcs!K10</f>
         <v>3.1863586362595919</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="28">
+      <c r="B11" s="27">
         <f>calcs!B11</f>
         <v>8.9979161894765802</v>
       </c>
-      <c r="C11" s="28">
+      <c r="C11" s="27">
         <f>calcs!C11</f>
         <v>2.1980839095148221</v>
       </c>
-      <c r="D11" s="28">
+      <c r="D11" s="27">
         <f>calcs!D11</f>
         <v>2.1980839095148221</v>
       </c>
-      <c r="E11" s="28">
+      <c r="E11" s="27">
         <f>calcs!E11</f>
         <v>2.1980839095148221</v>
       </c>
-      <c r="F11" s="28">
+      <c r="F11" s="27">
         <f>calcs!F11</f>
         <v>0.84489777592279791</v>
       </c>
-      <c r="G11" s="28">
+      <c r="G11" s="27">
         <f>calcs!G11</f>
         <v>2.5525704426134292</v>
       </c>
-      <c r="H11" s="28">
+      <c r="H11" s="27">
         <f>calcs!H11</f>
         <v>3.1863586362595919</v>
       </c>
-      <c r="I11" s="28">
+      <c r="I11" s="27">
         <f>calcs!I11</f>
+        <v>5.5980000494957007</v>
+      </c>
+      <c r="J11" s="27">
+        <f>calcs!J11</f>
+        <v>1.1617489485420724</v>
+      </c>
+      <c r="K11" s="27">
+        <f>calcs!K11</f>
         <v>3.1863586362595919</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="28">
+      <c r="B12" s="27">
         <f>calcs!B12</f>
         <v>8.9979161894765802</v>
       </c>
-      <c r="C12" s="28">
+      <c r="C12" s="27">
         <f>calcs!C12</f>
         <v>2.1980839095148221</v>
       </c>
-      <c r="D12" s="28">
+      <c r="D12" s="27">
         <f>calcs!D12</f>
         <v>2.1980839095148221</v>
       </c>
-      <c r="E12" s="28">
+      <c r="E12" s="27">
         <f>calcs!E12</f>
         <v>2.1980839095148221</v>
       </c>
-      <c r="F12" s="28">
+      <c r="F12" s="27">
         <f>calcs!F12</f>
         <v>0.84489777592279791</v>
       </c>
-      <c r="G12" s="28">
+      <c r="G12" s="27">
         <f>calcs!G12</f>
         <v>2.5525704426134292</v>
       </c>
-      <c r="H12" s="28">
+      <c r="H12" s="27">
         <f>calcs!H12</f>
         <v>3.1863586362595919</v>
       </c>
-      <c r="I12" s="28">
+      <c r="I12" s="27">
         <f>calcs!I12</f>
+        <v>5.5980000494957007</v>
+      </c>
+      <c r="J12" s="27">
+        <f>calcs!J12</f>
+        <v>1.1617489485420724</v>
+      </c>
+      <c r="K12" s="27">
+        <f>calcs!K12</f>
         <v>3.1863586362595919</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="28">
+      <c r="B13" s="27">
         <f>calcs!B13</f>
         <v>8.9979161894765802</v>
       </c>
-      <c r="C13" s="28">
+      <c r="C13" s="27">
         <f>calcs!C13</f>
         <v>2.1980839095148221</v>
       </c>
-      <c r="D13" s="28">
+      <c r="D13" s="27">
         <f>calcs!D13</f>
         <v>2.1980839095148221</v>
       </c>
-      <c r="E13" s="28">
+      <c r="E13" s="27">
         <f>calcs!E13</f>
         <v>2.1980839095148221</v>
       </c>
-      <c r="F13" s="28">
+      <c r="F13" s="27">
         <f>calcs!F13</f>
         <v>0.84489777592279791</v>
       </c>
-      <c r="G13" s="28">
+      <c r="G13" s="27">
         <f>calcs!G13</f>
         <v>2.5525704426134292</v>
       </c>
-      <c r="H13" s="28">
+      <c r="H13" s="27">
         <f>calcs!H13</f>
         <v>3.1863586362595919</v>
       </c>
-      <c r="I13" s="28">
+      <c r="I13" s="27">
         <f>calcs!I13</f>
+        <v>5.5980000494957007</v>
+      </c>
+      <c r="J13" s="27">
+        <f>calcs!J13</f>
+        <v>1.1617489485420724</v>
+      </c>
+      <c r="K13" s="27">
+        <f>calcs!K13</f>
         <v>3.1863586362595919</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:I13">
-    <cfRule type="colorScale" priority="1">
+  <conditionalFormatting sqref="B2:K13">
+    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -8514,54 +11315,54 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A366C323-AEA8-47A1-8400-4A398ED6DC8A}">
   <dimension ref="A1:H49"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.36328125" customWidth="1"/>
-    <col min="2" max="2" width="10.54296875" customWidth="1"/>
+    <col min="1" max="1" width="15.42578125" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" s="13" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
+        <v>381</v>
+      </c>
+      <c r="C8" t="s">
         <v>382</v>
       </c>
-      <c r="C8" t="s">
-        <v>383</v>
-      </c>
       <c r="D8" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C9" s="9">
         <v>0.59199999999999997</v>
@@ -8570,9 +11371,9 @@
         <v>112.5</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C10" s="12">
         <v>0.66</v>
@@ -8581,12 +11382,12 @@
         <v>150</v>
       </c>
       <c r="H10" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C11" s="9">
         <v>0.72699999999999998</v>
@@ -8603,9 +11404,9 @@
         <v>2.0029850746268671</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C13" s="9">
         <v>0.59199999999999997</v>
@@ -8614,9 +11415,9 @@
         <v>127.5</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C14" s="12">
         <v>0.66</v>
@@ -8625,9 +11426,9 @@
         <v>150</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C15" s="9">
         <v>0.72699999999999998</v>
@@ -8640,28 +11441,28 @@
         <v>1.510447761194031</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>381</v>
+      </c>
+      <c r="C18" t="s">
+        <v>382</v>
+      </c>
+      <c r="D18" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>392</v>
+      </c>
+      <c r="B19" t="s">
         <v>388</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B18" t="s">
-        <v>382</v>
-      </c>
-      <c r="C18" t="s">
-        <v>383</v>
-      </c>
-      <c r="D18" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>393</v>
-      </c>
-      <c r="B19" t="s">
-        <v>389</v>
       </c>
       <c r="C19" s="9">
         <v>0.59799999999999998</v>
@@ -8670,12 +11471,12 @@
         <v>192</v>
       </c>
       <c r="H19" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C20" s="12">
         <v>0.66500000000000004</v>
@@ -8688,9 +11489,9 @@
         <v>6.4942922385873603</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C21" s="9">
         <v>0.70799999999999996</v>
@@ -8703,9 +11504,9 @@
         <v>1.9512062595088053</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C22" s="9">
         <v>0.77700000000000002</v>
@@ -8718,12 +11519,12 @@
         <v>2.8577686915887854</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B24" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C24" s="9">
         <v>0.82</v>
@@ -8732,9 +11533,9 @@
         <v>762</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C25" s="12">
         <v>0.85</v>
@@ -8743,9 +11544,9 @@
         <v>853</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C26" s="9">
         <v>0.86899999999999999</v>
@@ -8758,9 +11559,9 @@
         <v>5.9264515332880796</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C27" s="9">
         <v>0.88600000000000001</v>
@@ -8773,12 +11574,12 @@
         <v>7.0030610915722225</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B29" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C29" s="9">
         <v>0.89300000000000002</v>
@@ -8787,9 +11588,9 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C30" s="12">
         <v>0.91100000000000003</v>
@@ -8798,9 +11599,9 @@
         <v>7802</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C31" s="9">
         <v>0.92300000000000004</v>
@@ -8813,9 +11614,9 @@
         <v>10.431000598137221</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C32" s="9">
         <v>0.93700000000000006</v>
@@ -8828,28 +11629,28 @@
         <v>10.796265257429052</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>402</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
+      <c r="B35" t="s">
+        <v>381</v>
+      </c>
+      <c r="C35" t="s">
+        <v>400</v>
+      </c>
+      <c r="D35" t="s">
         <v>403</v>
       </c>
-      <c r="B35" t="s">
-        <v>382</v>
-      </c>
-      <c r="C35" t="s">
-        <v>401</v>
-      </c>
-      <c r="D35" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C36">
         <v>24595</v>
@@ -8858,9 +11659,9 @@
         <v>683</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C37">
         <v>16135</v>
@@ -8873,12 +11674,12 @@
         <v>-6.8955795769602197</v>
       </c>
       <c r="H37" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C38">
         <v>15922</v>
@@ -8895,9 +11696,9 @@
         <v>6.9105031031053334</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C39">
         <v>15709</v>
@@ -8910,9 +11711,9 @@
         <v>-7.4362825495152691</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C40">
         <v>15497</v>
@@ -8925,23 +11726,23 @@
         <v>-7.7577586115333697</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B42" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C42" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D42" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C43">
         <v>23805</v>
@@ -8950,9 +11751,9 @@
         <v>761</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C44">
         <v>15593</v>
@@ -8965,9 +11766,9 @@
         <v>-6.1709155474537125</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C45">
         <v>15381</v>
@@ -8980,9 +11781,9 @@
         <v>-6.3498180531689075</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C46">
         <v>15168</v>
@@ -8995,9 +11796,9 @@
         <v>-6.6459440079710843</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C47">
         <v>14955</v>
@@ -9010,12 +11811,12 @@
         <v>-6.9278157642709193</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="H48" s="13" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="49" spans="8:8" x14ac:dyDescent="0.35">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="49" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H49" s="13">
         <f>AVERAGE(H38,H20,H11)</f>
         <v>5.1359268054398539</v>
@@ -9030,18 +11831,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79CA3ECE-CC46-4C9C-9910-1D3FD99A313F}">
   <dimension ref="B2:H29"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="15.81640625" customWidth="1"/>
-    <col min="7" max="7" width="8.7265625" customWidth="1"/>
+    <col min="2" max="2" width="15.85546875" customWidth="1"/>
+    <col min="7" max="7" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>170</v>
       </c>
@@ -9052,7 +11853,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>138</v>
       </c>
@@ -9063,7 +11864,7 @@
         <v>441.74</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>172</v>
       </c>
@@ -9082,7 +11883,7 @@
         <v>6.9143739655805581</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>90</v>
       </c>
@@ -9097,7 +11898,7 @@
         <v>2.3977905555304151</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>173</v>
       </c>
@@ -9112,12 +11913,12 @@
         <v>15.214077662576777</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>170</v>
       </c>
@@ -9128,7 +11929,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>138</v>
       </c>
@@ -9139,7 +11940,7 @@
         <v>585.58000000000004</v>
       </c>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>172</v>
       </c>
@@ -9158,7 +11959,7 @@
         <v>5.766666287175866</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>90</v>
       </c>
@@ -9173,7 +11974,7 @@
         <v>3.4550360326513991</v>
       </c>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>173</v>
       </c>
@@ -9188,12 +11989,12 @@
         <v>9.8393615446793472</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>170</v>
       </c>
@@ -9204,7 +12005,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>138</v>
       </c>
@@ -9215,7 +12016,7 @@
         <v>785.32</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>172</v>
       </c>
@@ -9234,7 +12035,7 @@
         <v>4.8914808966762324</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>90</v>
       </c>
@@ -9249,7 +12050,7 @@
         <v>4.3116181938572993</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>173</v>
       </c>
@@ -9264,12 +12065,12 @@
         <v>5.6411823630282338</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>170</v>
       </c>
@@ -9280,7 +12081,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>138</v>
       </c>
@@ -9291,7 +12092,7 @@
         <v>2065.19</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>172</v>
       </c>
@@ -9310,7 +12111,7 @@
         <v>2.1980839095148221</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>173</v>
       </c>
@@ -9325,7 +12126,7 @@
         <v>3.1528439602079317</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
       <c r="H29" s="1">
         <f>AVERAGE(H5:H26)</f>
         <v>4.9426512647368694</v>
@@ -9339,22 +12140,22 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44C2550C-391B-4AED-8625-12FCF8A24E5E}">
   <dimension ref="A1:M90"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.54296875" customWidth="1"/>
-    <col min="4" max="4" width="20.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="49.453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20.7265625" customWidth="1"/>
-    <col min="12" max="12" width="12.81640625" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="49.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>137</v>
       </c>
@@ -9362,7 +12163,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>140</v>
       </c>
@@ -9379,7 +12180,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>139</v>
       </c>
@@ -9406,7 +12207,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>139</v>
       </c>
@@ -9436,7 +12237,7 @@
         <v>1.177</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>139</v>
       </c>
@@ -9466,7 +12267,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="K7" t="s">
         <v>315</v>
       </c>
@@ -9477,7 +12278,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>144</v>
       </c>
@@ -9491,7 +12292,7 @@
         <v>1.073</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>139</v>
       </c>
@@ -9521,7 +12322,7 @@
         <v>1.2629999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>139</v>
       </c>
@@ -9541,7 +12342,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>139</v>
       </c>
@@ -9561,12 +12362,12 @@
         <v>145</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>139</v>
       </c>
@@ -9590,7 +12391,7 @@
         <v>4773.2519400000001</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>139</v>
       </c>
@@ -9614,7 +12415,7 @@
         <v>4818.5178599999999</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>139</v>
       </c>
@@ -9645,7 +12446,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>139</v>
       </c>
@@ -9676,7 +12477,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>139</v>
       </c>
@@ -9704,7 +12505,7 @@
         <v>-0.37515893987856253</v>
       </c>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>139</v>
       </c>
@@ -9728,12 +12529,12 @@
         <v>5202.8487600000008</v>
       </c>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>139</v>
       </c>
@@ -9754,7 +12555,7 @@
       </c>
       <c r="H22" s="5"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>139</v>
       </c>
@@ -9774,7 +12575,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>139</v>
       </c>
@@ -9791,7 +12592,7 @@
         <v>4534.6499999999996</v>
       </c>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>139</v>
       </c>
@@ -9808,7 +12609,7 @@
         <v>4689.2299999999996</v>
       </c>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>139</v>
       </c>
@@ -9825,12 +12626,12 @@
         <v>6537.7</v>
       </c>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>139</v>
       </c>
@@ -9851,7 +12652,7 @@
       </c>
       <c r="H29" s="5"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>139</v>
       </c>
@@ -9868,7 +12669,7 @@
         <v>4536.04</v>
       </c>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>139</v>
       </c>
@@ -9885,7 +12686,7 @@
         <v>4690.62</v>
       </c>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>139</v>
       </c>
@@ -9902,12 +12703,12 @@
         <v>6539.09</v>
       </c>
     </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>139</v>
       </c>
@@ -9931,7 +12732,7 @@
         <v>3285.0679200000004</v>
       </c>
     </row>
-    <row r="36" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>139</v>
       </c>
@@ -9959,7 +12760,7 @@
         <v>-7.1767170419329271E-2</v>
       </c>
     </row>
-    <row r="37" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>139</v>
       </c>
@@ -9987,7 +12788,7 @@
         <v>-0.1350437702275796</v>
       </c>
     </row>
-    <row r="38" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
         <v>139</v>
       </c>
@@ -10015,7 +12816,7 @@
         <v>-0.29795758890834489</v>
       </c>
     </row>
-    <row r="39" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
         <v>139</v>
       </c>
@@ -10039,7 +12840,7 @@
         <v>3466.8262500000001</v>
       </c>
     </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>139</v>
       </c>
@@ -10063,7 +12864,7 @@
         <v>3548.9212500000003</v>
       </c>
     </row>
-    <row r="41" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>139</v>
       </c>
@@ -10087,7 +12888,7 @@
         <v>3627.0125400000002</v>
       </c>
     </row>
-    <row r="42" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>139</v>
       </c>
@@ -10111,12 +12912,12 @@
         <v>4560.86211</v>
       </c>
     </row>
-    <row r="44" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="45" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
         <v>139</v>
       </c>
@@ -10137,7 +12938,7 @@
       </c>
       <c r="H45" s="5"/>
     </row>
-    <row r="46" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
         <v>139</v>
       </c>
@@ -10158,7 +12959,7 @@
       </c>
       <c r="H46" s="5"/>
     </row>
-    <row r="47" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
         <v>139</v>
       </c>
@@ -10179,7 +12980,7 @@
       </c>
       <c r="H47" s="5"/>
     </row>
-    <row r="48" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>139</v>
       </c>
@@ -10200,12 +13001,12 @@
       </c>
       <c r="H48" s="5"/>
     </row>
-    <row r="50" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="51" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
         <v>139</v>
       </c>
@@ -10229,7 +13030,7 @@
         <v>2987.6178599999998</v>
       </c>
     </row>
-    <row r="52" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
         <v>139</v>
       </c>
@@ -10257,7 +13058,7 @@
         <v>-5.2885797094647621E-2</v>
       </c>
     </row>
-    <row r="53" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
         <v>139</v>
       </c>
@@ -10285,7 +13086,7 @@
         <v>-9.8355927104850596E-2</v>
       </c>
     </row>
-    <row r="54" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>139</v>
       </c>
@@ -10313,12 +13114,12 @@
         <v>-0.27634900468231655</v>
       </c>
     </row>
-    <row r="56" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="57" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
         <v>139</v>
       </c>
@@ -10342,7 +13143,7 @@
         <v>2992.4973</v>
       </c>
     </row>
-    <row r="58" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
         <v>139</v>
       </c>
@@ -10370,7 +13171,7 @@
         <v>-9.4194441382049326E-2</v>
       </c>
     </row>
-    <row r="59" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
         <v>139</v>
       </c>
@@ -10398,12 +13199,12 @@
         <v>-0.44375415947561242</v>
       </c>
     </row>
-    <row r="61" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="62" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
         <v>139</v>
       </c>
@@ -10427,7 +13228,7 @@
         <v>3147.6303600000001</v>
       </c>
     </row>
-    <row r="63" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
         <v>139</v>
       </c>
@@ -10455,7 +13256,7 @@
         <v>-0.127860669353144</v>
       </c>
     </row>
-    <row r="64" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
         <v>139</v>
       </c>
@@ -10483,7 +13284,7 @@
         <v>-0.2426177784692137</v>
       </c>
     </row>
-    <row r="65" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
         <v>139</v>
       </c>
@@ -10511,12 +13312,12 @@
         <v>-0.28422695397249625</v>
       </c>
     </row>
-    <row r="67" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="68" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
         <v>139</v>
       </c>
@@ -10540,7 +13341,7 @@
         <v>3454.4326800000003</v>
       </c>
     </row>
-    <row r="69" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
         <v>139</v>
       </c>
@@ -10568,7 +13369,7 @@
         <v>-0.16607521209530268</v>
       </c>
     </row>
-    <row r="70" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
         <v>139</v>
       </c>
@@ -10596,7 +13397,7 @@
         <v>-0.3160522249319408</v>
       </c>
     </row>
-    <row r="71" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
         <v>139</v>
       </c>
@@ -10624,12 +13425,12 @@
         <v>-0.54936977454017333</v>
       </c>
     </row>
-    <row r="73" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="74" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
         <v>139</v>
       </c>
@@ -10650,7 +13451,7 @@
       </c>
       <c r="H74" s="5"/>
     </row>
-    <row r="75" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
         <v>139</v>
       </c>
@@ -10670,7 +13471,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="76" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B76" t="s">
         <v>139</v>
       </c>
@@ -10690,12 +13491,12 @@
         <v>145</v>
       </c>
     </row>
-    <row r="78" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B78" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="79" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
         <v>139</v>
       </c>
@@ -10716,7 +13517,7 @@
       </c>
       <c r="H79" s="5"/>
     </row>
-    <row r="80" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B80" t="s">
         <v>139</v>
       </c>
@@ -10736,7 +13537,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
         <v>139</v>
       </c>
@@ -10756,7 +13557,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
         <v>139</v>
       </c>
@@ -10776,7 +13577,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
         <v>139</v>
       </c>
@@ -10796,12 +13597,12 @@
         <v>159</v>
       </c>
     </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B86" t="s">
         <v>139</v>
       </c>
@@ -10825,7 +13626,7 @@
         <v>1676.1177600000001</v>
       </c>
     </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
         <v>139</v>
       </c>
@@ -10853,7 +13654,7 @@
         <v>-0.50450778819706843</v>
       </c>
     </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B88" t="s">
         <v>139</v>
       </c>
@@ -10881,7 +13682,7 @@
         <v>-0.68827016087660164</v>
       </c>
     </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:10" x14ac:dyDescent="0.25">
       <c r="I90" s="1">
         <f>AVERAGE(I16:I88)</f>
         <v>-0.27364729366829971</v>
@@ -10898,25 +13699,25 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AB4F1A2-F703-4C6F-AA45-D27647AF57D3}">
   <dimension ref="A1:L15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="7.453125" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="7.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D4" t="s">
         <v>335</v>
       </c>
@@ -10927,7 +13728,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D5" t="s">
         <v>332</v>
       </c>
@@ -10953,7 +13754,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
         <v>324</v>
       </c>
@@ -10984,7 +13785,7 @@
         <v>1.2041041072488405</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
         <v>325</v>
       </c>
@@ -11015,7 +13816,7 @@
         <v>1.0661290303038382</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
         <v>326</v>
       </c>
@@ -11046,7 +13847,7 @@
         <v>1.2493007531597848</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
         <v>327</v>
       </c>
@@ -11077,7 +13878,7 @@
         <v>1.0749978945004353</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
         <v>328</v>
       </c>
@@ -11108,7 +13909,7 @@
         <v>1.2040660259396516</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
         <v>329</v>
       </c>
@@ -11139,7 +13940,7 @@
         <v>1.0749936470910193</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
         <v>330</v>
       </c>
@@ -11170,7 +13971,7 @@
         <v>1.2222135812044317</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
         <v>331</v>
       </c>
@@ -11201,12 +14002,12 @@
         <v>1.063195759659757</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C14" s="17" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="K15" s="13">
         <f>AVERAGE(K6:L13)</f>
         <v>0.84489777592279791</v>
@@ -11231,20 +14032,20 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2293F3F-9A88-4413-B145-B7568F539BC4}">
   <dimension ref="B2:J20"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="24.81640625" customWidth="1"/>
-    <col min="3" max="3" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.85546875" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>126</v>
       </c>
@@ -11258,7 +14059,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>130</v>
       </c>
@@ -11273,7 +14074,7 @@
       </c>
       <c r="J4" s="7"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>131</v>
       </c>
@@ -11291,7 +14092,7 @@
         <v>0.48457468495615924</v>
       </c>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>132</v>
       </c>
@@ -11309,7 +14110,7 @@
         <v>0.40812137036870288</v>
       </c>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>133</v>
       </c>
@@ -11327,7 +14128,7 @@
         <v>0.37971125362275093</v>
       </c>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>134</v>
       </c>
@@ -11345,7 +14146,7 @@
         <v>0.36318061551316005</v>
       </c>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>135</v>
       </c>
@@ -11363,21 +14164,21 @@
         <v>0.3699587517672609</v>
       </c>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="G10" s="8">
         <f>AVERAGE(G5:G9)</f>
         <v>0.40110933524560688</v>
       </c>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="G11" s="8"/>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>126</v>
       </c>
@@ -11391,7 +14192,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>130</v>
       </c>
@@ -11405,7 +14206,7 @@
         <v>1801.36</v>
       </c>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>131</v>
       </c>
@@ -11423,7 +14224,7 @@
         <v>0.17795856107792277</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>132</v>
       </c>
@@ -11441,7 +14242,7 @@
         <v>0.73483880282556446</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>133</v>
       </c>
@@ -11459,7 +14260,7 @@
         <v>2.8548635478975006</v>
       </c>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>134</v>
       </c>
@@ -11477,7 +14278,7 @@
         <v>2.577075205511751</v>
       </c>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>135</v>
       </c>
@@ -11495,7 +14296,7 @@
         <v>2.3600219245858747</v>
       </c>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="G20" s="8">
         <f>AVERAGE(G15:G19)</f>
         <v>1.7409516083797225</v>
@@ -11510,25 +14311,25 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5F4C270-6BF9-4D0D-85CD-90AE6754A5FB}">
   <dimension ref="A2:W114"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.81640625" customWidth="1"/>
-    <col min="2" max="2" width="8.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="7.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.453125" customWidth="1"/>
-    <col min="11" max="11" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.85546875" customWidth="1"/>
+    <col min="2" max="2" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.42578125" customWidth="1"/>
+    <col min="11" max="11" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>64</v>
       </c>
@@ -11536,7 +14337,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>46</v>
       </c>
@@ -11577,7 +14378,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="4" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>52</v>
       </c>
@@ -11600,7 +14401,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="5" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:20" x14ac:dyDescent="0.25">
       <c r="C5">
         <v>50</v>
       </c>
@@ -11644,7 +14445,7 @@
         <v>-1.7351479979551212</v>
       </c>
     </row>
-    <row r="6" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>55</v>
       </c>
@@ -11694,7 +14495,7 @@
         <v>-1.4282628303383635</v>
       </c>
     </row>
-    <row r="7" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:20" x14ac:dyDescent="0.25">
       <c r="C7">
         <v>85</v>
       </c>
@@ -11738,7 +14539,7 @@
         <v>-2.6308996997545302</v>
       </c>
     </row>
-    <row r="8" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:20" x14ac:dyDescent="0.25">
       <c r="C8">
         <v>100</v>
       </c>
@@ -11782,7 +14583,7 @@
         <v>-1.9383909355489866</v>
       </c>
     </row>
-    <row r="9" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>56</v>
       </c>
@@ -11832,7 +14633,7 @@
         <v>-3.0545656735773874</v>
       </c>
     </row>
-    <row r="10" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:20" x14ac:dyDescent="0.25">
       <c r="C10">
         <v>160</v>
       </c>
@@ -11876,7 +14677,7 @@
         <v>-2.048071931367609</v>
       </c>
     </row>
-    <row r="11" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:20" x14ac:dyDescent="0.25">
       <c r="C11">
         <v>40</v>
       </c>
@@ -11920,7 +14721,7 @@
         <v>-1.4990616006765836</v>
       </c>
     </row>
-    <row r="12" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>57</v>
       </c>
@@ -11970,7 +14771,7 @@
         <v>-1.6713835530873047</v>
       </c>
     </row>
-    <row r="13" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:20" x14ac:dyDescent="0.25">
       <c r="C13">
         <v>150</v>
       </c>
@@ -12014,7 +14815,7 @@
         <v>-3.3781383833324585</v>
       </c>
     </row>
-    <row r="14" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:20" x14ac:dyDescent="0.25">
       <c r="C14">
         <v>200</v>
       </c>
@@ -12058,7 +14859,7 @@
         <v>-2.7309768589762058</v>
       </c>
     </row>
-    <row r="15" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>58</v>
       </c>
@@ -12108,7 +14909,7 @@
         <v>-1.524739602891763</v>
       </c>
     </row>
-    <row r="16" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:20" x14ac:dyDescent="0.25">
       <c r="C16">
         <v>130</v>
       </c>
@@ -12152,7 +14953,7 @@
         <v>-2.0804560907263778</v>
       </c>
     </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:20" x14ac:dyDescent="0.25">
       <c r="C17">
         <v>125</v>
       </c>
@@ -12199,7 +15000,7 @@
         <v>-8.7788419549361105</v>
       </c>
     </row>
-    <row r="18" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>59</v>
       </c>
@@ -12246,7 +15047,7 @@
         <v>-4.0839676960070426</v>
       </c>
     </row>
-    <row r="19" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:20" x14ac:dyDescent="0.25">
       <c r="C19">
         <v>210</v>
       </c>
@@ -12290,7 +15091,7 @@
         <v>-7.3240504827306534</v>
       </c>
     </row>
-    <row r="20" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:20" x14ac:dyDescent="0.25">
       <c r="C20">
         <v>330</v>
       </c>
@@ -12334,7 +15135,7 @@
         <v>-5.7233550165204115</v>
       </c>
     </row>
-    <row r="21" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>60</v>
       </c>
@@ -12381,7 +15182,7 @@
         <v>-7.8965628791014373</v>
       </c>
     </row>
-    <row r="22" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:20" x14ac:dyDescent="0.25">
       <c r="C22">
         <v>320</v>
       </c>
@@ -12425,7 +15226,7 @@
         <v>-9.2910932144654694</v>
       </c>
     </row>
-    <row r="23" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:20" x14ac:dyDescent="0.25">
       <c r="C23">
         <v>40</v>
       </c>
@@ -12470,7 +15271,7 @@
         <v>-1.0459028355712656</v>
       </c>
     </row>
-    <row r="24" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>61</v>
       </c>
@@ -12518,7 +15319,7 @@
         <v>-1.4904111981491879</v>
       </c>
     </row>
-    <row r="25" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:20" x14ac:dyDescent="0.25">
       <c r="C25">
         <v>100</v>
       </c>
@@ -12563,7 +15364,7 @@
         <v>-2.352471148542254</v>
       </c>
     </row>
-    <row r="26" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:20" x14ac:dyDescent="0.25">
       <c r="C26">
         <v>75</v>
       </c>
@@ -12607,7 +15408,7 @@
         <v>-1.7201851350734794</v>
       </c>
     </row>
-    <row r="27" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>62</v>
       </c>
@@ -12654,7 +15455,7 @@
         <v>-1.8485348460732218</v>
       </c>
     </row>
-    <row r="28" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:20" x14ac:dyDescent="0.25">
       <c r="C28">
         <v>175</v>
       </c>
@@ -12699,7 +15500,7 @@
         <v>-2.5791807128461923</v>
       </c>
     </row>
-    <row r="29" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:20" x14ac:dyDescent="0.25">
       <c r="C29">
         <v>175</v>
       </c>
@@ -12744,7 +15545,7 @@
         <v>-3.1681673641753672</v>
       </c>
     </row>
-    <row r="30" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>63</v>
       </c>
@@ -12792,7 +15593,7 @@
         <v>-1.6221373794905105</v>
       </c>
     </row>
-    <row r="31" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:20" x14ac:dyDescent="0.25">
       <c r="C31">
         <v>350</v>
       </c>
@@ -12836,7 +15637,7 @@
         <v>-1.9210829904512492</v>
       </c>
     </row>
-    <row r="32" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:20" x14ac:dyDescent="0.25">
       <c r="C32">
         <v>40</v>
       </c>
@@ -12880,7 +15681,7 @@
         <v>-1.2580101987707004</v>
       </c>
     </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>65</v>
       </c>
@@ -12928,7 +15729,7 @@
         <v>-0.96847955658773233</v>
       </c>
     </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C34">
         <v>150</v>
       </c>
@@ -12973,7 +15774,7 @@
         <v>-1.0603982778636305</v>
       </c>
     </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C35">
         <v>200</v>
       </c>
@@ -13018,7 +15819,7 @@
         <v>-1.2553540020904954</v>
       </c>
     </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>66</v>
       </c>
@@ -13065,7 +15866,7 @@
         <v>-1.2781215385125198</v>
       </c>
     </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C37">
         <v>130</v>
       </c>
@@ -13109,7 +15910,7 @@
         <v>-1.1125028404475994</v>
       </c>
     </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
       <c r="R38" s="8"/>
       <c r="S38" s="8"/>
       <c r="T38" s="8">
@@ -13117,7 +15918,7 @@
         <v>2.8333001947466441</v>
       </c>
     </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>67</v>
       </c>
@@ -13126,7 +15927,7 @@
       </c>
       <c r="R39" s="5"/>
     </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>46</v>
       </c>
@@ -13171,7 +15972,7 @@
       </c>
       <c r="R40" s="5"/>
     </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>52</v>
       </c>
@@ -13228,7 +16029,7 @@
         <v>9.2409419078576693E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C42">
         <v>25</v>
       </c>
@@ -13285,7 +16086,7 @@
         <v>0.42969045833316616</v>
       </c>
     </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>70</v>
       </c>
@@ -13343,7 +16144,7 @@
         <v>0.34619983213284949</v>
       </c>
     </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C44">
         <v>20</v>
       </c>
@@ -13398,7 +16199,7 @@
         <v>0.31494739568434177</v>
       </c>
     </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C45">
         <v>35</v>
       </c>
@@ -13455,7 +16256,7 @@
         <v>0.37622266697512413</v>
       </c>
     </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
         <v>71</v>
       </c>
@@ -13512,7 +16313,7 @@
         <v>0.53473243236803913</v>
       </c>
     </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
       <c r="R47" s="8"/>
       <c r="S47" s="8"/>
       <c r="T47" s="8"/>
@@ -13525,225 +16326,225 @@
         <v>1.5911669477543302</v>
       </c>
     </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
       <c r="J48" s="5"/>
       <c r="R48" s="5"/>
     </row>
-    <row r="49" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="49" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J49" s="5"/>
       <c r="R49" s="5"/>
     </row>
-    <row r="50" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="50" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J50" s="5"/>
       <c r="R50" s="5"/>
     </row>
-    <row r="51" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="51" spans="10:18" x14ac:dyDescent="0.25">
       <c r="R51" s="5"/>
     </row>
-    <row r="52" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="52" spans="10:18" x14ac:dyDescent="0.25">
       <c r="R52" s="5"/>
     </row>
-    <row r="53" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="53" spans="10:18" x14ac:dyDescent="0.25">
       <c r="R53" s="5"/>
     </row>
-    <row r="54" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="54" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J54" s="5"/>
       <c r="R54" s="5"/>
     </row>
-    <row r="55" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="55" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J55" s="5"/>
       <c r="R55" s="5"/>
     </row>
-    <row r="56" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="56" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J56" s="5"/>
       <c r="R56" s="5"/>
     </row>
-    <row r="57" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="57" spans="10:18" x14ac:dyDescent="0.25">
       <c r="R57" s="5"/>
     </row>
-    <row r="58" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="58" spans="10:18" x14ac:dyDescent="0.25">
       <c r="R58" s="5"/>
     </row>
-    <row r="59" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="59" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J59" s="5"/>
       <c r="R59" s="5"/>
     </row>
-    <row r="60" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="60" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J60" s="5"/>
       <c r="R60" s="5"/>
     </row>
-    <row r="61" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="61" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J61" s="5"/>
       <c r="R61" s="5"/>
     </row>
-    <row r="62" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="62" spans="10:18" x14ac:dyDescent="0.25">
       <c r="R62" s="5"/>
     </row>
-    <row r="63" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="63" spans="10:18" x14ac:dyDescent="0.25">
       <c r="R63" s="5"/>
     </row>
-    <row r="64" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="64" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J64" s="5"/>
       <c r="R64" s="5"/>
     </row>
-    <row r="65" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="65" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J65" s="5"/>
       <c r="R65" s="5"/>
     </row>
-    <row r="66" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="66" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J66" s="5"/>
       <c r="R66" s="5"/>
     </row>
-    <row r="67" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="67" spans="10:18" x14ac:dyDescent="0.25">
       <c r="R67" s="5"/>
     </row>
-    <row r="68" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="68" spans="10:18" x14ac:dyDescent="0.25">
       <c r="R68" s="5"/>
     </row>
-    <row r="69" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="69" spans="10:18" x14ac:dyDescent="0.25">
       <c r="R69" s="5"/>
     </row>
-    <row r="70" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="70" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J70" s="5"/>
       <c r="R70" s="5"/>
     </row>
-    <row r="71" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="71" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J71" s="5"/>
       <c r="R71" s="5"/>
     </row>
-    <row r="72" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="72" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J72" s="5"/>
       <c r="R72" s="5"/>
     </row>
-    <row r="73" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="73" spans="10:18" x14ac:dyDescent="0.25">
       <c r="R73" s="5"/>
     </row>
-    <row r="74" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="74" spans="10:18" x14ac:dyDescent="0.25">
       <c r="R74" s="5"/>
     </row>
-    <row r="75" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="75" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J75" s="5"/>
       <c r="R75" s="5"/>
     </row>
-    <row r="76" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="76" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J76" s="5"/>
       <c r="R76" s="5"/>
     </row>
-    <row r="77" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="77" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J77" s="5"/>
       <c r="R77" s="5"/>
     </row>
-    <row r="78" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="78" spans="10:18" x14ac:dyDescent="0.25">
       <c r="R78" s="5"/>
     </row>
-    <row r="79" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="79" spans="10:18" x14ac:dyDescent="0.25">
       <c r="R79" s="5"/>
     </row>
-    <row r="80" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="80" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J80" s="5"/>
       <c r="R80" s="5"/>
     </row>
-    <row r="81" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="81" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J81" s="5"/>
       <c r="R81" s="5"/>
     </row>
-    <row r="82" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="82" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J82" s="5"/>
       <c r="R82" s="5"/>
     </row>
-    <row r="83" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="83" spans="10:18" x14ac:dyDescent="0.25">
       <c r="R83" s="5"/>
     </row>
-    <row r="84" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="84" spans="10:18" x14ac:dyDescent="0.25">
       <c r="R84" s="5"/>
     </row>
-    <row r="85" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="85" spans="10:18" x14ac:dyDescent="0.25">
       <c r="R85" s="5"/>
     </row>
-    <row r="86" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="86" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J86" s="5"/>
       <c r="R86" s="5"/>
     </row>
-    <row r="87" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="87" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J87" s="5"/>
       <c r="R87" s="5"/>
     </row>
-    <row r="88" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="88" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J88" s="5"/>
       <c r="R88" s="5"/>
     </row>
-    <row r="89" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="89" spans="10:18" x14ac:dyDescent="0.25">
       <c r="R89" s="5"/>
     </row>
-    <row r="90" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="90" spans="10:18" x14ac:dyDescent="0.25">
       <c r="R90" s="5"/>
     </row>
-    <row r="91" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="91" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J91" s="5"/>
       <c r="R91" s="5"/>
     </row>
-    <row r="92" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="92" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J92" s="5"/>
       <c r="R92" s="5"/>
     </row>
-    <row r="93" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="93" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J93" s="5"/>
       <c r="R93" s="5"/>
     </row>
-    <row r="94" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="94" spans="10:18" x14ac:dyDescent="0.25">
       <c r="R94" s="5"/>
     </row>
-    <row r="95" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="95" spans="10:18" x14ac:dyDescent="0.25">
       <c r="R95" s="5"/>
     </row>
-    <row r="96" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="96" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J96" s="5"/>
       <c r="R96" s="5"/>
     </row>
-    <row r="97" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="97" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J97" s="5"/>
       <c r="R97" s="5"/>
     </row>
-    <row r="98" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="98" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J98" s="5"/>
       <c r="R98" s="5"/>
     </row>
-    <row r="99" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="99" spans="10:18" x14ac:dyDescent="0.25">
       <c r="R99" s="5"/>
     </row>
-    <row r="100" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="100" spans="10:18" x14ac:dyDescent="0.25">
       <c r="R100" s="5"/>
     </row>
-    <row r="101" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="101" spans="10:18" x14ac:dyDescent="0.25">
       <c r="R101" s="5"/>
     </row>
-    <row r="102" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="102" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J102" s="5"/>
       <c r="R102" s="5"/>
     </row>
-    <row r="103" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="103" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J103" s="5"/>
       <c r="R103" s="5"/>
     </row>
-    <row r="104" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="104" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J104" s="5"/>
     </row>
-    <row r="107" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="107" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J107" s="5"/>
     </row>
-    <row r="108" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="108" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J108" s="5"/>
     </row>
-    <row r="109" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="109" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J109" s="5"/>
     </row>
-    <row r="112" spans="10:18" x14ac:dyDescent="0.35">
+    <row r="112" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J112" s="5"/>
     </row>
-    <row r="113" spans="10:10" x14ac:dyDescent="0.35">
+    <row r="113" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J113" s="5"/>
     </row>
-    <row r="114" spans="10:10" x14ac:dyDescent="0.35">
+    <row r="114" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J114" s="5"/>
     </row>
   </sheetData>
@@ -13766,22 +16567,22 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC1B79DA-1807-4980-8716-C48017AC8EE8}">
   <dimension ref="B2:X23"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="5.453125" customWidth="1"/>
-    <col min="3" max="3" width="3.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="51.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="9" width="6.81640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.54296875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="49.1796875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.42578125" customWidth="1"/>
+    <col min="3" max="3" width="3.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="51.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="9" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="49.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>86</v>
       </c>
@@ -13792,7 +16593,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="3" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>87</v>
       </c>
@@ -13824,7 +16625,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="4" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:24" x14ac:dyDescent="0.25">
       <c r="D4" t="s">
         <v>93</v>
       </c>
@@ -13847,7 +16648,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="5" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:24" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
         <v>95</v>
       </c>
@@ -13855,7 +16656,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="6" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:24" x14ac:dyDescent="0.25">
       <c r="C6">
         <v>1</v>
       </c>
@@ -13919,7 +16720,7 @@
         <v>17.050585761126278</v>
       </c>
     </row>
-    <row r="7" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:24" x14ac:dyDescent="0.25">
       <c r="C7">
         <v>2</v>
       </c>
@@ -13983,7 +16784,7 @@
         <v>32.018403828408623</v>
       </c>
     </row>
-    <row r="8" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>1</v>
       </c>
@@ -14053,7 +16854,7 @@
         <v>40.434465954096879</v>
       </c>
     </row>
-    <row r="9" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:24" x14ac:dyDescent="0.25">
       <c r="C9">
         <v>4</v>
       </c>
@@ -14117,7 +16918,7 @@
         <v>31.718830696496546</v>
       </c>
     </row>
-    <row r="10" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:24" x14ac:dyDescent="0.25">
       <c r="C10">
         <v>5</v>
       </c>
@@ -14181,7 +16982,7 @@
         <v>35.554034251412403</v>
       </c>
     </row>
-    <row r="11" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>2</v>
       </c>
@@ -14251,7 +17052,7 @@
         <v>22.174484326487942</v>
       </c>
     </row>
-    <row r="12" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:24" x14ac:dyDescent="0.25">
       <c r="C12">
         <v>7</v>
       </c>
@@ -14315,7 +17116,7 @@
         <v>9.1935719796635222</v>
       </c>
     </row>
-    <row r="13" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:24" x14ac:dyDescent="0.25">
       <c r="C13">
         <v>8</v>
       </c>
@@ -14379,7 +17180,7 @@
         <v>13.481354636376457</v>
       </c>
     </row>
-    <row r="14" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:24" x14ac:dyDescent="0.25">
       <c r="C14">
         <v>9</v>
       </c>
@@ -14443,7 +17244,7 @@
         <v>23.374268398037174</v>
       </c>
     </row>
-    <row r="15" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B15">
         <v>3</v>
       </c>
@@ -14507,7 +17308,7 @@
         <v>24.111708919500494</v>
       </c>
     </row>
-    <row r="16" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:24" x14ac:dyDescent="0.25">
       <c r="C16">
         <v>11</v>
       </c>
@@ -14571,7 +17372,7 @@
         <v>9.2997636166650182</v>
       </c>
     </row>
-    <row r="17" spans="14:24" x14ac:dyDescent="0.35">
+    <row r="17" spans="14:24" x14ac:dyDescent="0.25">
       <c r="Q17" s="5"/>
       <c r="R17" s="5"/>
       <c r="T17" s="8"/>
@@ -14583,31 +17384,31 @@
         <v>23.491952033479212</v>
       </c>
     </row>
-    <row r="18" spans="14:24" x14ac:dyDescent="0.35">
+    <row r="18" spans="14:24" x14ac:dyDescent="0.25">
       <c r="N18" s="5"/>
       <c r="O18" s="5"/>
       <c r="P18" s="5"/>
     </row>
-    <row r="19" spans="14:24" x14ac:dyDescent="0.35">
+    <row r="19" spans="14:24" x14ac:dyDescent="0.25">
       <c r="O19" s="5"/>
       <c r="P19" s="10"/>
       <c r="Q19" s="10"/>
       <c r="R19" s="10"/>
     </row>
-    <row r="20" spans="14:24" x14ac:dyDescent="0.35">
+    <row r="20" spans="14:24" x14ac:dyDescent="0.25">
       <c r="N20" s="10"/>
       <c r="O20" s="5"/>
       <c r="Q20" s="10"/>
       <c r="R20" s="10"/>
     </row>
-    <row r="22" spans="14:24" x14ac:dyDescent="0.35">
+    <row r="22" spans="14:24" x14ac:dyDescent="0.25">
       <c r="N22" s="10"/>
       <c r="O22" s="5"/>
       <c r="P22" s="10"/>
       <c r="Q22" s="10"/>
       <c r="R22" s="10"/>
     </row>
-    <row r="23" spans="14:24" x14ac:dyDescent="0.35">
+    <row r="23" spans="14:24" x14ac:dyDescent="0.25">
       <c r="N23" s="5"/>
       <c r="O23" s="5"/>
       <c r="P23" s="5"/>
@@ -14622,25 +17423,25 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1873BFA-BFB8-479B-8580-77E23D72D642}">
   <dimension ref="B1:M51"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:13" x14ac:dyDescent="0.25">
       <c r="I1" s="1"/>
     </row>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>112</v>
       </c>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>113</v>
       </c>
@@ -14655,7 +17456,7 @@
       </c>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="C4" s="12">
         <v>0.8</v>
       </c>
@@ -14674,7 +17475,7 @@
         <v>7.5361437213570515</v>
       </c>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
       <c r="C5" s="12">
         <v>0.81</v>
       </c>
@@ -14698,7 +17499,7 @@
         <v>10.236696165191734</v>
       </c>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>117</v>
       </c>
@@ -14728,7 +17529,7 @@
         <v>7.5709278650378069</v>
       </c>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
       <c r="C7" s="12">
         <v>0.84</v>
       </c>
@@ -14752,7 +17553,7 @@
         <v>13.093142804855722</v>
       </c>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
       <c r="C8" s="12">
         <v>0.85</v>
       </c>
@@ -14776,7 +17577,7 @@
         <v>6.8445086849877326</v>
       </c>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
       <c r="C9" s="12">
         <v>0.93</v>
       </c>
@@ -14800,7 +17601,7 @@
         <v>4.7753002649653098</v>
       </c>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
       <c r="C10" s="12">
         <v>0.95</v>
       </c>
@@ -14824,7 +17625,7 @@
         <v>10.329147244310422</v>
       </c>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
       <c r="C11" s="12">
         <v>0.99</v>
       </c>
@@ -14848,7 +17649,7 @@
         <v>7.1185033686236947</v>
       </c>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
       <c r="C12" s="12">
         <v>0.82</v>
       </c>
@@ -14860,7 +17661,7 @@
         <v>21244</v>
       </c>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
       <c r="C13" s="12">
         <v>0.83</v>
       </c>
@@ -14877,7 +17678,7 @@
       </c>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>118</v>
       </c>
@@ -14900,7 +17701,7 @@
       </c>
       <c r="I14" s="1"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
       <c r="C15" s="12">
         <v>0.85</v>
       </c>
@@ -14917,7 +17718,7 @@
       </c>
       <c r="I15" s="1"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
       <c r="C16" s="12">
         <v>0.94</v>
       </c>
@@ -14934,7 +17735,7 @@
       </c>
       <c r="I16" s="1"/>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C17" s="12">
         <v>0.97</v>
       </c>
@@ -14951,7 +17752,7 @@
       </c>
       <c r="I17" s="1"/>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C18" s="12">
         <v>0.82</v>
       </c>
@@ -14963,7 +17764,7 @@
         <v>8404</v>
       </c>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C19" s="12">
         <v>0.83</v>
       </c>
@@ -14980,7 +17781,7 @@
       </c>
       <c r="I19" s="1"/>
     </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C20" s="12">
         <v>0.84</v>
       </c>
@@ -14997,7 +17798,7 @@
       </c>
       <c r="I20" s="1"/>
     </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>119</v>
       </c>
@@ -15020,7 +17821,7 @@
       </c>
       <c r="I21" s="1"/>
     </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C22" s="12">
         <v>0.87</v>
       </c>
@@ -15037,7 +17838,7 @@
       </c>
       <c r="I22" s="1"/>
     </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C23" s="12">
         <v>0.88</v>
       </c>
@@ -15054,7 +17855,7 @@
       </c>
       <c r="I23" s="1"/>
     </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C24" s="12">
         <v>0.97</v>
       </c>
@@ -15071,7 +17872,7 @@
       </c>
       <c r="I24" s="1"/>
     </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C25" s="12">
         <v>0.84</v>
       </c>
@@ -15083,7 +17884,7 @@
         <v>18915</v>
       </c>
     </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C26" s="12">
         <v>0.86</v>
       </c>
@@ -15100,7 +17901,7 @@
       </c>
       <c r="I26" s="1"/>
     </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>120</v>
       </c>
@@ -15123,7 +17924,7 @@
       </c>
       <c r="I27" s="1"/>
     </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C28" s="12">
         <v>0.89</v>
       </c>
@@ -15140,7 +17941,7 @@
       </c>
       <c r="I28" s="1"/>
     </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C29" s="12">
         <v>0.97</v>
       </c>
@@ -15157,7 +17958,7 @@
       </c>
       <c r="I29" s="1"/>
     </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C30" s="12">
         <v>0.77</v>
       </c>
@@ -15169,7 +17970,7 @@
         <v>6659</v>
       </c>
     </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C31" s="12">
         <v>0.78</v>
       </c>
@@ -15186,7 +17987,7 @@
       </c>
       <c r="I31" s="1"/>
     </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>121</v>
       </c>
@@ -15209,7 +18010,7 @@
       </c>
       <c r="I32" s="1"/>
     </row>
-    <row r="33" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C33" s="12">
         <v>0.8</v>
       </c>
@@ -15226,7 +18027,7 @@
       </c>
       <c r="I33" s="1"/>
     </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C34" s="12">
         <v>0.81</v>
       </c>
@@ -15243,7 +18044,7 @@
       </c>
       <c r="I34" s="1"/>
     </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C35" s="12">
         <v>0.83</v>
       </c>
@@ -15260,7 +18061,7 @@
       </c>
       <c r="I35" s="1"/>
     </row>
-    <row r="36" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C36" s="12">
         <v>0.77</v>
       </c>
@@ -15272,7 +18073,7 @@
         <v>19122</v>
       </c>
     </row>
-    <row r="37" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C37" s="12">
         <v>0.78</v>
       </c>
@@ -15289,7 +18090,7 @@
       </c>
       <c r="I37" s="1"/>
     </row>
-    <row r="38" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C38" s="12">
         <v>0.79</v>
       </c>
@@ -15306,7 +18107,7 @@
       </c>
       <c r="I38" s="1"/>
     </row>
-    <row r="39" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
         <v>122</v>
       </c>
@@ -15329,7 +18130,7 @@
       </c>
       <c r="I39" s="1"/>
     </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C40" s="12">
         <v>0.81</v>
       </c>
@@ -15346,7 +18147,7 @@
       </c>
       <c r="I40" s="1"/>
     </row>
-    <row r="41" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C41" s="12">
         <v>0.82</v>
       </c>
@@ -15363,7 +18164,7 @@
       </c>
       <c r="I41" s="1"/>
     </row>
-    <row r="42" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C42" s="12">
         <v>0.84</v>
       </c>
@@ -15380,7 +18181,7 @@
       </c>
       <c r="I42" s="1"/>
     </row>
-    <row r="43" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C43" s="12">
         <v>0.81</v>
       </c>
@@ -15392,7 +18193,7 @@
         <v>7294</v>
       </c>
     </row>
-    <row r="44" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
         <v>123</v>
       </c>
@@ -15415,7 +18216,7 @@
       </c>
       <c r="I44" s="1"/>
     </row>
-    <row r="45" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C45" s="12">
         <v>0.84</v>
       </c>
@@ -15432,7 +18233,7 @@
       </c>
       <c r="I45" s="1"/>
     </row>
-    <row r="46" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C46" s="12">
         <v>0.86</v>
       </c>
@@ -15449,7 +18250,7 @@
       </c>
       <c r="I46" s="1"/>
     </row>
-    <row r="47" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C47" s="12">
         <v>0.81</v>
       </c>
@@ -15461,7 +18262,7 @@
         <v>18702</v>
       </c>
     </row>
-    <row r="48" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>124</v>
       </c>
@@ -15484,7 +18285,7 @@
       </c>
       <c r="I48" s="1"/>
     </row>
-    <row r="49" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="49" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C49" s="12">
         <v>0.85</v>
       </c>
@@ -15501,7 +18302,7 @@
       </c>
       <c r="I49" s="1"/>
     </row>
-    <row r="50" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="50" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C50" s="12">
         <v>0.87</v>
       </c>
@@ -15518,7 +18319,7 @@
       </c>
       <c r="I50" s="1"/>
     </row>
-    <row r="51" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="51" spans="3:9" x14ac:dyDescent="0.25">
       <c r="I51" s="13">
         <f>AVERAGE(H1:H50)</f>
         <v>8.126972362529246</v>

--- a/InputData/indst/EoIEPwEEI/Elasticity of Ind Eqpt Price wrt E Eff Improvements.xlsx
+++ b/InputData/indst/EoIEPwEEI/Elasticity of Ind Eqpt Price wrt E Eff Improvements.xlsx
@@ -1,34 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanO'Brien\Models\EPS\US\eps-us\InputData\indst\EoIEPwEEI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\indst\EoIEPwEEI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{138C8715-36E6-4D76-B3E3-4B17A9E8069F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E3217B7-465B-4D4E-B5F5-63CD0C08DA2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="763" firstSheet="4" activeTab="15" xr2:uid="{05F795DA-2DEA-4188-AD09-B14B246EEF5D}"/>
+    <workbookView xWindow="1545" yWindow="1200" windowWidth="24345" windowHeight="14850" tabRatio="763" firstSheet="7" activeTab="17" xr2:uid="{05F795DA-2DEA-4188-AD09-B14B246EEF5D}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="indst motors" sheetId="15" r:id="rId2"/>
-    <sheet name="furnaces" sheetId="8" r:id="rId3"/>
-    <sheet name="comm refrigerators" sheetId="7" r:id="rId4"/>
-    <sheet name="process chillers" sheetId="12" r:id="rId5"/>
-    <sheet name="water heaters" sheetId="6" r:id="rId6"/>
-    <sheet name="pumps" sheetId="2" r:id="rId7"/>
-    <sheet name="motors" sheetId="4" r:id="rId8"/>
-    <sheet name="comm boilers" sheetId="5" r:id="rId9"/>
-    <sheet name="indst boilers" sheetId="9" r:id="rId10"/>
-    <sheet name="indst heat pumps" sheetId="11" r:id="rId11"/>
-    <sheet name="fans-blowers" sheetId="14" r:id="rId12"/>
-    <sheet name="solid fuel boilers" sheetId="16" r:id="rId13"/>
-    <sheet name="Lighting" sheetId="17" r:id="rId14"/>
-    <sheet name="calcs" sheetId="13" r:id="rId15"/>
-    <sheet name="EoIEPwEEI" sheetId="3" r:id="rId16"/>
+    <sheet name="cpi" sheetId="19" r:id="rId2"/>
+    <sheet name="indst motors" sheetId="15" r:id="rId3"/>
+    <sheet name="furnaces" sheetId="8" r:id="rId4"/>
+    <sheet name="comm refrigerators" sheetId="7" r:id="rId5"/>
+    <sheet name="process chillers" sheetId="12" r:id="rId6"/>
+    <sheet name="water heaters" sheetId="6" r:id="rId7"/>
+    <sheet name="pumps" sheetId="2" r:id="rId8"/>
+    <sheet name="motors" sheetId="4" r:id="rId9"/>
+    <sheet name="comm boilers" sheetId="5" r:id="rId10"/>
+    <sheet name="indst boilers" sheetId="9" r:id="rId11"/>
+    <sheet name="indst heat pumps" sheetId="11" r:id="rId12"/>
+    <sheet name="fans-blowers" sheetId="14" r:id="rId13"/>
+    <sheet name="solid fuel boilers" sheetId="16" r:id="rId14"/>
+    <sheet name="Lighting" sheetId="17" r:id="rId15"/>
+    <sheet name="mobile" sheetId="18" r:id="rId16"/>
+    <sheet name="calcs" sheetId="13" r:id="rId17"/>
+    <sheet name="EoIEPwEEI" sheetId="3" r:id="rId18"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -51,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1106" uniqueCount="610">
   <si>
     <t>Source:</t>
   </si>
@@ -1672,19 +1674,291 @@
   <si>
     <t>lumens</t>
   </si>
+  <si>
+    <t>Cal Poly &amp; University of Nebraska, Lincoln</t>
+  </si>
+  <si>
+    <t>Assessing the Cost and Fuel Consumption of Off-Road Agricultural Equipment</t>
+  </si>
+  <si>
+    <t>https://digitalcommons.calpoly.edu/agb_fac/161/?utm_source=chatgpt.com</t>
+  </si>
+  <si>
+    <t>Table 5</t>
+  </si>
+  <si>
+    <t>Historical Consumer Price Index for All Urban Consumers (CPI-U): U.S. city average, all items, index</t>
+  </si>
+  <si>
+    <t>averages — Continued</t>
+  </si>
+  <si>
+    <t>[1982-84=100, unless otherwise noted]</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Semiannual averages</t>
+  </si>
+  <si>
+    <t>Annual avg.</t>
+  </si>
+  <si>
+    <t>Percent change from previous</t>
+  </si>
+  <si>
+    <t>Multiply by to get 2012 Dollars</t>
+  </si>
+  <si>
+    <t>1st half</t>
+  </si>
+  <si>
+    <t>2nd half</t>
+  </si>
+  <si>
+    <t>Dec.</t>
+  </si>
+  <si>
+    <t>1968............................................................................. .</t>
+  </si>
+  <si>
+    <t>–</t>
+  </si>
+  <si>
+    <t>1969............................................................................. .</t>
+  </si>
+  <si>
+    <t>1970............................................................................. .</t>
+  </si>
+  <si>
+    <t>1971............................................................................. .</t>
+  </si>
+  <si>
+    <t>1972............................................................................. .</t>
+  </si>
+  <si>
+    <t>1973............................................................................. .</t>
+  </si>
+  <si>
+    <t>1974............................................................................. .</t>
+  </si>
+  <si>
+    <t>1975............................................................................. .</t>
+  </si>
+  <si>
+    <t>1976............................................................................. .</t>
+  </si>
+  <si>
+    <t>1977............................................................................. .</t>
+  </si>
+  <si>
+    <t>1978............................................................................. .</t>
+  </si>
+  <si>
+    <t>1979............................................................................. .</t>
+  </si>
+  <si>
+    <t>1980............................................................................. .</t>
+  </si>
+  <si>
+    <t>1981............................................................................. .</t>
+  </si>
+  <si>
+    <t>1982............................................................................. .</t>
+  </si>
+  <si>
+    <t>1983............................................................................. .</t>
+  </si>
+  <si>
+    <t>1984............................................................................. .</t>
+  </si>
+  <si>
+    <t>1985............................................................................. .</t>
+  </si>
+  <si>
+    <t>1986............................................................................. .</t>
+  </si>
+  <si>
+    <t>1987............................................................................. .</t>
+  </si>
+  <si>
+    <t>1988............................................................................. .</t>
+  </si>
+  <si>
+    <t>1989............................................................................. .</t>
+  </si>
+  <si>
+    <t>1990............................................................................. .</t>
+  </si>
+  <si>
+    <t>1991............................................................................. .</t>
+  </si>
+  <si>
+    <t>1992............................................................................. .</t>
+  </si>
+  <si>
+    <t>1993............................................................................. .</t>
+  </si>
+  <si>
+    <t>1994............................................................................. .</t>
+  </si>
+  <si>
+    <t>1995............................................................................. .</t>
+  </si>
+  <si>
+    <t>1996............................................................................. .</t>
+  </si>
+  <si>
+    <t>1997............................................................................. .</t>
+  </si>
+  <si>
+    <t>1998............................................................................. .</t>
+  </si>
+  <si>
+    <t>1999............................................................................. .</t>
+  </si>
+  <si>
+    <t>2000............................................................................. .</t>
+  </si>
+  <si>
+    <t>2001............................................................................. .</t>
+  </si>
+  <si>
+    <t>2002............................................................................. .</t>
+  </si>
+  <si>
+    <t>2003............................................................................. .</t>
+  </si>
+  <si>
+    <t>2004............................................................................. .</t>
+  </si>
+  <si>
+    <t>2005............................................................................. .</t>
+  </si>
+  <si>
+    <t>2006............................................................................. .</t>
+  </si>
+  <si>
+    <t>2007............................................................................. .</t>
+  </si>
+  <si>
+    <t>2008............................................................................. .</t>
+  </si>
+  <si>
+    <t>2009............................................................................. .</t>
+  </si>
+  <si>
+    <t>2010............................................................................. .</t>
+  </si>
+  <si>
+    <t>2011............................................................................. .</t>
+  </si>
+  <si>
+    <t>2012............................................................................. .</t>
+  </si>
+  <si>
+    <t>2013............................................................................. .</t>
+  </si>
+  <si>
+    <t>2014............................................................................. .</t>
+  </si>
+  <si>
+    <t>2015............................................................................. .</t>
+  </si>
+  <si>
+    <t>2016............................................................................. .</t>
+  </si>
+  <si>
+    <t>2017............................................................................. .</t>
+  </si>
+  <si>
+    <t>2018............................................................................. .</t>
+  </si>
+  <si>
+    <t>2019............................................................................. .</t>
+  </si>
+  <si>
+    <t>2020............................................................................. .</t>
+  </si>
+  <si>
+    <t>2021............................................................................. .</t>
+  </si>
+  <si>
+    <t>2022............................................................................. .</t>
+  </si>
+  <si>
+    <t>2023............................................................................. .</t>
+  </si>
+  <si>
+    <t>2024............................................................................. .</t>
+  </si>
+  <si>
+    <t>https://farmdocdaily.illinois.edu/2025/10/large-increase-in-machinery-costs-suggests-need-to-reconsider-machinery-purchase-decisions.html?utm_source=chatgpt.com</t>
+  </si>
+  <si>
+    <t>CPI</t>
+  </si>
+  <si>
+    <t>CPI indexed to 2000</t>
+  </si>
+  <si>
+    <t>Nominal tractor price index</t>
+  </si>
+  <si>
+    <t>Real tractor price index</t>
+  </si>
+  <si>
+    <t>Real annual price growth:</t>
+  </si>
+  <si>
+    <t>per year</t>
+  </si>
+  <si>
+    <t>Table 5. Regression model comparison</t>
+  </si>
+  <si>
+    <t>Average hp.hr/gal</t>
+  </si>
+  <si>
+    <t>tested tractors</t>
+  </si>
+  <si>
+    <t>year coefficient</t>
+  </si>
+  <si>
+    <t>avg %chg in hp.hr/gal per year</t>
+  </si>
+  <si>
+    <t>Model 1: 1987-2021</t>
+  </si>
+  <si>
+    <t>Model 2</t>
+  </si>
+  <si>
+    <t>Model 3: Tier 4 only (2015-21)</t>
+  </si>
+  <si>
+    <t>Elasticity: Δprice/Δeff</t>
+  </si>
+  <si>
+    <t>Average elasticity:</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="7">
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="171" formatCode="#0.0"/>
+    <numFmt numFmtId="172" formatCode="#0.000"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1756,6 +2030,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -1808,7 +2088,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1854,6 +2134,19 @@
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="171" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="172" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5126,6 +5419,72 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>573315</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2" descr="Line graph showing U.S. Tractor Prices Paid Index from 2000 to 2024. The index starts at 68 in 2000 and rises to 70 in 2002, 76 in 2005, 82 in 2007, 91 in 2009, 100 in 2011, 106 in 2013, 110 in 2015, and 113 in 2017. The index dips slightly to 112 in 2018, then rises to 123 in 2021, followed by sharp increases to 138 in 2023 and 139 in 2024. The trend shows generally steady growth with a notable dip in 2018 and particularly steep increases after 2020. Source: USDA, NASS.">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51158697-A946-42D5-B1A2-8CA2048C4379}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="3048000"/>
+          <a:ext cx="8315779" cy="4657725"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -5443,7 +5802,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6F6B216-0153-49F1-A327-FA35702ED267}">
-  <dimension ref="A1:B68"/>
+  <dimension ref="A1:B74"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="60.42578125" customWidth="1"/>
@@ -5689,52 +6048,77 @@
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
+      <c r="B57" s="15" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B58" s="2">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B59" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B60" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B61" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
         <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>22</v>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
         <v>25</v>
       </c>
     </row>
@@ -5745,6 +6129,916 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1873BFA-BFB8-479B-8580-77E23D72D642}">
+  <dimension ref="B1:M51"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>112</v>
+      </c>
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E3" t="s">
+        <v>116</v>
+      </c>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C4" s="12">
+        <v>0.8</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="F4" s="11">
+        <f>D4+$E$6</f>
+        <v>6928</v>
+      </c>
+      <c r="L4" t="s">
+        <v>117</v>
+      </c>
+      <c r="M4" s="1">
+        <f>AVERAGE(H5:H11)</f>
+        <v>7.5361437213570515</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C5" s="12">
+        <v>0.81</v>
+      </c>
+      <c r="D5" s="11">
+        <v>472</v>
+      </c>
+      <c r="F5" s="11">
+        <f t="shared" ref="F5:F11" si="0">D5+$E$6</f>
+        <v>7400</v>
+      </c>
+      <c r="H5">
+        <f>((F5-$F$4)/($F$4))/((C5-$C$4)/($C$4))</f>
+        <v>5.4503464203233207</v>
+      </c>
+      <c r="I5" s="1"/>
+      <c r="L5" t="s">
+        <v>118</v>
+      </c>
+      <c r="M5" s="1">
+        <f>AVERAGE(H13:H17)</f>
+        <v>10.236696165191734</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" s="12">
+        <v>0.82</v>
+      </c>
+      <c r="D6">
+        <v>977</v>
+      </c>
+      <c r="E6" s="11">
+        <v>6928</v>
+      </c>
+      <c r="F6" s="11">
+        <f t="shared" si="0"/>
+        <v>7905</v>
+      </c>
+      <c r="H6">
+        <f t="shared" ref="H6:H11" si="1">((F6-$F$4)/($F$4))/((C6-$C$4)/($C$4))</f>
+        <v>5.6408775981524517</v>
+      </c>
+      <c r="I6" s="1"/>
+      <c r="L6" t="s">
+        <v>119</v>
+      </c>
+      <c r="M6" s="1">
+        <f>AVERAGE(H19:H24)</f>
+        <v>7.5709278650378069</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C7" s="12">
+        <v>0.84</v>
+      </c>
+      <c r="D7" s="11">
+        <v>2759</v>
+      </c>
+      <c r="F7" s="11">
+        <f t="shared" si="0"/>
+        <v>9687</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="1"/>
+        <v>7.9647806004619088</v>
+      </c>
+      <c r="I7" s="1"/>
+      <c r="L7" t="s">
+        <v>120</v>
+      </c>
+      <c r="M7" s="1">
+        <f>AVERAGE(H26:H29)</f>
+        <v>13.093142804855722</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C8" s="12">
+        <v>0.85</v>
+      </c>
+      <c r="D8">
+        <v>3561</v>
+      </c>
+      <c r="F8" s="11">
+        <f t="shared" si="0"/>
+        <v>10489</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="1"/>
+        <v>8.2240184757505883</v>
+      </c>
+      <c r="I8" s="1"/>
+      <c r="L8" t="s">
+        <v>121</v>
+      </c>
+      <c r="M8" s="1">
+        <f>AVERAGE(H31:H35)</f>
+        <v>6.8445086849877326</v>
+      </c>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C9" s="12">
+        <v>0.93</v>
+      </c>
+      <c r="D9" s="11">
+        <v>10027</v>
+      </c>
+      <c r="F9" s="11">
+        <f t="shared" si="0"/>
+        <v>16955</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="1"/>
+        <v>8.9065553384260081</v>
+      </c>
+      <c r="I9" s="1"/>
+      <c r="L9" t="s">
+        <v>122</v>
+      </c>
+      <c r="M9" s="1">
+        <f>AVERAGE(H37:H42)</f>
+        <v>4.7753002649653098</v>
+      </c>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C10" s="12">
+        <v>0.95</v>
+      </c>
+      <c r="D10" s="11">
+        <v>10494</v>
+      </c>
+      <c r="F10" s="11">
+        <f t="shared" si="0"/>
+        <v>17422</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="1"/>
+        <v>8.0785219399538146</v>
+      </c>
+      <c r="I10" s="1"/>
+      <c r="L10" t="s">
+        <v>123</v>
+      </c>
+      <c r="M10" s="1">
+        <f>AVERAGE(H44:H46)</f>
+        <v>10.329147244310422</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C11" s="12">
+        <v>0.99</v>
+      </c>
+      <c r="D11" s="11">
+        <v>13966</v>
+      </c>
+      <c r="F11" s="11">
+        <f t="shared" si="0"/>
+        <v>20894</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="1"/>
+        <v>8.4879056764312661</v>
+      </c>
+      <c r="I11" s="1"/>
+      <c r="L11" t="s">
+        <v>124</v>
+      </c>
+      <c r="M11" s="1">
+        <f>AVERAGE(H48:H50)</f>
+        <v>7.1185033686236947</v>
+      </c>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C12" s="12">
+        <v>0.82</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="F12" s="11">
+        <f>D12+$E$14</f>
+        <v>21244</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C13" s="12">
+        <v>0.83</v>
+      </c>
+      <c r="D13" s="11">
+        <v>2534</v>
+      </c>
+      <c r="F13" s="11">
+        <f t="shared" ref="F13:F17" si="2">D13+$E$14</f>
+        <v>23778</v>
+      </c>
+      <c r="H13">
+        <f>((F13-$F$12)/($F$12))/((C13-$C$12)/($C$12))</f>
+        <v>9.7810205234419048</v>
+      </c>
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>118</v>
+      </c>
+      <c r="C14" s="12">
+        <v>0.84</v>
+      </c>
+      <c r="D14" s="5">
+        <v>5370</v>
+      </c>
+      <c r="E14" s="11">
+        <v>21244</v>
+      </c>
+      <c r="F14" s="11">
+        <f t="shared" si="2"/>
+        <v>26614</v>
+      </c>
+      <c r="H14">
+        <f t="shared" ref="H14:H17" si="3">((F14-$F$12)/($F$12))/((C14-$C$12)/($C$12))</f>
+        <v>10.363867444925617</v>
+      </c>
+      <c r="I14" s="1"/>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C15" s="12">
+        <v>0.85</v>
+      </c>
+      <c r="D15" s="11">
+        <v>8544</v>
+      </c>
+      <c r="F15" s="11">
+        <f t="shared" si="2"/>
+        <v>29788</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="3"/>
+        <v>10.993033327057042</v>
+      </c>
+      <c r="I15" s="1"/>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C16" s="12">
+        <v>0.94</v>
+      </c>
+      <c r="D16" s="11">
+        <v>32796</v>
+      </c>
+      <c r="F16" s="11">
+        <f t="shared" si="2"/>
+        <v>54040</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="3"/>
+        <v>10.549143287516475</v>
+      </c>
+      <c r="I16" s="1"/>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C17" s="12">
+        <v>0.97</v>
+      </c>
+      <c r="D17" s="11">
+        <v>36904</v>
+      </c>
+      <c r="F17" s="11">
+        <f t="shared" si="2"/>
+        <v>58148</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="3"/>
+        <v>9.4964162430176344</v>
+      </c>
+      <c r="I17" s="1"/>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C18" s="12">
+        <v>0.82</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="F18" s="11">
+        <f>D18+$E$21</f>
+        <v>8404</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C19" s="12">
+        <v>0.83</v>
+      </c>
+      <c r="D19" s="11">
+        <v>634</v>
+      </c>
+      <c r="F19" s="11">
+        <f t="shared" ref="F19:F24" si="4">D19+$E$21</f>
+        <v>9038</v>
+      </c>
+      <c r="H19">
+        <f>((F19-$F$18)/($F$18))/((C19-$C$18)/($C$18))</f>
+        <v>6.1861018562589187</v>
+      </c>
+      <c r="I19" s="1"/>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C20" s="12">
+        <v>0.84</v>
+      </c>
+      <c r="D20">
+        <v>1315</v>
+      </c>
+      <c r="F20" s="11">
+        <f t="shared" si="4"/>
+        <v>9719</v>
+      </c>
+      <c r="H20">
+        <f t="shared" ref="H20:H24" si="5">((F20-$F$18)/($F$18))/((C20-$C$18)/($C$18))</f>
+        <v>6.4153974297953296</v>
+      </c>
+      <c r="I20" s="1"/>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C21" s="12">
+        <v>0.85</v>
+      </c>
+      <c r="D21" s="11">
+        <v>2048</v>
+      </c>
+      <c r="E21" s="11">
+        <v>8404</v>
+      </c>
+      <c r="F21" s="11">
+        <f t="shared" si="4"/>
+        <v>10452</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="5"/>
+        <v>6.6609551007456709</v>
+      </c>
+      <c r="I21" s="1"/>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C22" s="12">
+        <v>0.87</v>
+      </c>
+      <c r="D22">
+        <v>3683</v>
+      </c>
+      <c r="F22" s="11">
+        <f t="shared" si="4"/>
+        <v>12087</v>
+      </c>
+      <c r="H22">
+        <f t="shared" si="5"/>
+        <v>7.1871965730604401</v>
+      </c>
+      <c r="I22" s="1"/>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C23" s="12">
+        <v>0.88</v>
+      </c>
+      <c r="D23" s="11">
+        <v>4594</v>
+      </c>
+      <c r="F23" s="11">
+        <f t="shared" si="4"/>
+        <v>12998</v>
+      </c>
+      <c r="H23">
+        <f t="shared" si="5"/>
+        <v>7.4708075519593775</v>
+      </c>
+      <c r="I23" s="1"/>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C24" s="12">
+        <v>0.97</v>
+      </c>
+      <c r="D24" s="5">
+        <v>17687</v>
+      </c>
+      <c r="F24" s="11">
+        <f t="shared" si="4"/>
+        <v>26091</v>
+      </c>
+      <c r="H24">
+        <f t="shared" si="5"/>
+        <v>11.505108678407106</v>
+      </c>
+      <c r="I24" s="1"/>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C25" s="12">
+        <v>0.84</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="F25" s="11">
+        <f>D25+$E$27</f>
+        <v>18915</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C26" s="12">
+        <v>0.86</v>
+      </c>
+      <c r="D26" s="11">
+        <v>4785</v>
+      </c>
+      <c r="F26" s="11">
+        <f t="shared" ref="F26:F29" si="6">D26+$E$27</f>
+        <v>23700</v>
+      </c>
+      <c r="H26">
+        <f>((F26-$F$25)/($F$25))/((C26-$C$25)/($C$25))</f>
+        <v>10.624900872323542</v>
+      </c>
+      <c r="I26" s="1"/>
+    </row>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>120</v>
+      </c>
+      <c r="C27" s="12">
+        <v>0.88</v>
+      </c>
+      <c r="D27" s="11">
+        <v>10781</v>
+      </c>
+      <c r="E27" s="11">
+        <v>18915</v>
+      </c>
+      <c r="F27" s="11">
+        <f t="shared" si="6"/>
+        <v>29696</v>
+      </c>
+      <c r="H27">
+        <f t="shared" ref="H27:H29" si="7">((F27-$F$25)/($F$25))/((C27-$C$25)/($C$25))</f>
+        <v>11.969389373513073</v>
+      </c>
+      <c r="I27" s="1"/>
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C28" s="12">
+        <v>0.89</v>
+      </c>
+      <c r="D28" s="11">
+        <v>14326</v>
+      </c>
+      <c r="F28" s="11">
+        <f t="shared" si="6"/>
+        <v>33241</v>
+      </c>
+      <c r="H28">
+        <f t="shared" si="7"/>
+        <v>12.724123711340194</v>
+      </c>
+      <c r="I28" s="1"/>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C29" s="12">
+        <v>0.97</v>
+      </c>
+      <c r="D29" s="5">
+        <v>49923</v>
+      </c>
+      <c r="F29" s="11">
+        <f t="shared" si="6"/>
+        <v>68838</v>
+      </c>
+      <c r="H29">
+        <f t="shared" si="7"/>
+        <v>17.054157262246079</v>
+      </c>
+      <c r="I29" s="1"/>
+    </row>
+    <row r="30" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C30" s="12">
+        <v>0.77</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="F30" s="11">
+        <f>D30+$E$32</f>
+        <v>6659</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C31" s="12">
+        <v>0.78</v>
+      </c>
+      <c r="D31" s="11">
+        <v>540</v>
+      </c>
+      <c r="F31" s="11">
+        <f t="shared" ref="F31:F35" si="8">D31+$E$32</f>
+        <v>7199</v>
+      </c>
+      <c r="H31">
+        <f>((F31-$F$30)/($F$30))/((C31-$C$30)/($C$30))</f>
+        <v>6.244180807929113</v>
+      </c>
+      <c r="I31" s="1"/>
+    </row>
+    <row r="32" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>121</v>
+      </c>
+      <c r="C32" s="12">
+        <v>0.79</v>
+      </c>
+      <c r="D32" s="5">
+        <v>1124</v>
+      </c>
+      <c r="E32" s="11">
+        <v>6659</v>
+      </c>
+      <c r="F32" s="11">
+        <f t="shared" si="8"/>
+        <v>7783</v>
+      </c>
+      <c r="H32">
+        <f t="shared" ref="H32:H35" si="9">((F32-$F$30)/($F$30))/((C32-$C$30)/($C$30))</f>
+        <v>6.4985733593632622</v>
+      </c>
+      <c r="I32" s="1"/>
+    </row>
+    <row r="33" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C33" s="12">
+        <v>0.8</v>
+      </c>
+      <c r="D33" s="11">
+        <v>1756</v>
+      </c>
+      <c r="F33" s="11">
+        <f t="shared" si="8"/>
+        <v>8415</v>
+      </c>
+      <c r="H33">
+        <f t="shared" si="9"/>
+        <v>6.7683836411873592</v>
+      </c>
+      <c r="I33" s="1"/>
+    </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C34" s="12">
+        <v>0.81</v>
+      </c>
+      <c r="D34" s="5">
+        <v>2439</v>
+      </c>
+      <c r="F34" s="11">
+        <f t="shared" si="8"/>
+        <v>9098</v>
+      </c>
+      <c r="H34">
+        <f t="shared" si="9"/>
+        <v>7.0507208289532901</v>
+      </c>
+      <c r="I34" s="1"/>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C35" s="12">
+        <v>0.83</v>
+      </c>
+      <c r="D35" s="11">
+        <v>3975</v>
+      </c>
+      <c r="F35" s="11">
+        <f t="shared" si="8"/>
+        <v>10634</v>
+      </c>
+      <c r="H35">
+        <f t="shared" si="9"/>
+        <v>7.6606847875056383</v>
+      </c>
+      <c r="I35" s="1"/>
+    </row>
+    <row r="36" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C36" s="12">
+        <v>0.77</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="F36" s="11">
+        <f>D36+$E$39</f>
+        <v>19122</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C37" s="12">
+        <v>0.78</v>
+      </c>
+      <c r="D37" s="5">
+        <v>1097</v>
+      </c>
+      <c r="F37" s="11">
+        <f t="shared" ref="F37:F42" si="10">D37+$E$39</f>
+        <v>20219</v>
+      </c>
+      <c r="H37">
+        <f>((F37-$F$36)/($F$36))/((C37-$C$36)/($C$36))</f>
+        <v>4.4173726597636191</v>
+      </c>
+      <c r="I37" s="1"/>
+    </row>
+    <row r="38" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C38" s="12">
+        <v>0.79</v>
+      </c>
+      <c r="D38" s="5">
+        <v>2256</v>
+      </c>
+      <c r="F38" s="11">
+        <f t="shared" si="10"/>
+        <v>21378</v>
+      </c>
+      <c r="H38">
+        <f t="shared" ref="H38:H42" si="11">((F38-$F$36)/($F$36))/((C38-$C$36)/($C$36))</f>
+        <v>4.5422026984624999</v>
+      </c>
+      <c r="I38" s="1"/>
+    </row>
+    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
+        <v>122</v>
+      </c>
+      <c r="C39" s="12">
+        <v>0.8</v>
+      </c>
+      <c r="D39" s="5">
+        <v>3483</v>
+      </c>
+      <c r="E39" s="11">
+        <v>19122</v>
+      </c>
+      <c r="F39" s="11">
+        <f t="shared" si="10"/>
+        <v>22605</v>
+      </c>
+      <c r="H39">
+        <f t="shared" si="11"/>
+        <v>4.67508628804518</v>
+      </c>
+      <c r="I39" s="1"/>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C40" s="12">
+        <v>0.81</v>
+      </c>
+      <c r="D40">
+        <v>4779</v>
+      </c>
+      <c r="F40" s="11">
+        <f t="shared" si="10"/>
+        <v>23901</v>
+      </c>
+      <c r="H40">
+        <f t="shared" si="11"/>
+        <v>4.8109899592092837</v>
+      </c>
+      <c r="I40" s="1"/>
+    </row>
+    <row r="41" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C41" s="12">
+        <v>0.82</v>
+      </c>
+      <c r="D41" s="11">
+        <v>6150</v>
+      </c>
+      <c r="F41" s="11">
+        <f t="shared" si="10"/>
+        <v>25272</v>
+      </c>
+      <c r="H41">
+        <f t="shared" si="11"/>
+        <v>4.9529337935362481</v>
+      </c>
+      <c r="I41" s="1"/>
+    </row>
+    <row r="42" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C42" s="12">
+        <v>0.84</v>
+      </c>
+      <c r="D42">
+        <v>9132</v>
+      </c>
+      <c r="F42" s="11">
+        <f t="shared" si="10"/>
+        <v>28254</v>
+      </c>
+      <c r="H42">
+        <f t="shared" si="11"/>
+        <v>5.2532161907750279</v>
+      </c>
+      <c r="I42" s="1"/>
+    </row>
+    <row r="43" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C43" s="12">
+        <v>0.81</v>
+      </c>
+      <c r="D43">
+        <v>0</v>
+      </c>
+      <c r="F43" s="11">
+        <f>D43+$E$44</f>
+        <v>7294</v>
+      </c>
+    </row>
+    <row r="44" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B44" t="s">
+        <v>123</v>
+      </c>
+      <c r="C44" s="12">
+        <v>0.83</v>
+      </c>
+      <c r="D44" s="5">
+        <v>1722</v>
+      </c>
+      <c r="E44" s="11">
+        <v>7294</v>
+      </c>
+      <c r="F44" s="11">
+        <f t="shared" ref="F44:F46" si="12">D44+$E$44</f>
+        <v>9016</v>
+      </c>
+      <c r="H44">
+        <f>((F44-$F$43)/($F$43))/((C44-$C$43)/($C$43))</f>
+        <v>9.5614203454894877</v>
+      </c>
+      <c r="I44" s="1"/>
+    </row>
+    <row r="45" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C45" s="12">
+        <v>0.84</v>
+      </c>
+      <c r="D45">
+        <v>2730</v>
+      </c>
+      <c r="F45" s="11">
+        <f t="shared" si="12"/>
+        <v>10024</v>
+      </c>
+      <c r="H45">
+        <f t="shared" ref="H45:H46" si="13">((F45-$F$43)/($F$43))/((C45-$C$43)/($C$43))</f>
+        <v>10.10556621881001</v>
+      </c>
+      <c r="I45" s="1"/>
+    </row>
+    <row r="46" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C46" s="12">
+        <v>0.86</v>
+      </c>
+      <c r="D46" s="11">
+        <v>5097</v>
+      </c>
+      <c r="F46" s="11">
+        <f t="shared" si="12"/>
+        <v>12391</v>
+      </c>
+      <c r="H46">
+        <f t="shared" si="13"/>
+        <v>11.320455168631767</v>
+      </c>
+      <c r="I46" s="1"/>
+    </row>
+    <row r="47" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C47" s="12">
+        <v>0.81</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="F47" s="11">
+        <f>D47+$E$48</f>
+        <v>18702</v>
+      </c>
+    </row>
+    <row r="48" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B48" t="s">
+        <v>124</v>
+      </c>
+      <c r="C48" s="12">
+        <v>0.83</v>
+      </c>
+      <c r="D48" s="11">
+        <v>3071</v>
+      </c>
+      <c r="E48" s="11">
+        <v>18702</v>
+      </c>
+      <c r="F48" s="11">
+        <f t="shared" ref="F48:F50" si="14">D48+$E$48</f>
+        <v>21773</v>
+      </c>
+      <c r="H48">
+        <f>((F48-$F$47)/($F$47))/((C48-$C$47)/($C$47))</f>
+        <v>6.6503849855630728</v>
+      </c>
+      <c r="I48" s="1"/>
+    </row>
+    <row r="49" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C49" s="12">
+        <v>0.85</v>
+      </c>
+      <c r="D49" s="11">
+        <v>6521</v>
+      </c>
+      <c r="F49" s="11">
+        <f t="shared" si="14"/>
+        <v>25223</v>
+      </c>
+      <c r="H49">
+        <f t="shared" ref="H49:H50" si="15">((F49-$F$47)/($F$47))/((C49-$C$47)/($C$47))</f>
+        <v>7.060755534167483</v>
+      </c>
+      <c r="I49" s="1"/>
+    </row>
+    <row r="50" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C50" s="12">
+        <v>0.87</v>
+      </c>
+      <c r="D50" s="11">
+        <v>10590</v>
+      </c>
+      <c r="F50" s="11">
+        <f t="shared" si="14"/>
+        <v>29292</v>
+      </c>
+      <c r="H50">
+        <f t="shared" si="15"/>
+        <v>7.6443695861405265</v>
+      </c>
+      <c r="I50" s="1"/>
+    </row>
+    <row r="51" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="I51" s="13">
+        <f>AVERAGE(H1:H50)</f>
+        <v>8.126972362529246</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D39F440-FA8D-440E-B9E0-04BD2776E781}">
   <dimension ref="B2:O26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6560,7 +7854,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75FF9701-D73C-4593-9C81-F6045C33961E}">
   <dimension ref="A1:AD94"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7944,7 +9238,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1011C56E-59CC-41D7-BD37-B8D3833EEA91}">
   <dimension ref="B2:G36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8484,7 +9778,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFF80A1E-9380-4D67-8452-F9501E3A0DC6}">
   <dimension ref="A2:J19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8827,7 +10121,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D8718AA-AC7D-4D9E-9BAB-C38A4CE85A96}">
   <dimension ref="A1:W63"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -10117,7 +11411,258 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6BD96FA-EB4C-4695-AB05-D346A69359A2}">
+  <dimension ref="A1:G49"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="28.5703125" customWidth="1"/>
+    <col min="2" max="4" width="10.7109375" customWidth="1"/>
+    <col min="20" max="20" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="B4" s="25" t="s">
+        <v>605</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>606</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>607</v>
+      </c>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>601</v>
+      </c>
+      <c r="B5">
+        <v>17.670000000000002</v>
+      </c>
+      <c r="C5">
+        <v>17.64</v>
+      </c>
+      <c r="D5">
+        <v>18.37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>602</v>
+      </c>
+      <c r="B6">
+        <v>1440</v>
+      </c>
+      <c r="C6">
+        <v>1297</v>
+      </c>
+      <c r="D6">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>603</v>
+      </c>
+      <c r="B7">
+        <v>9.7000000000000003E-2</v>
+      </c>
+      <c r="C7">
+        <v>0.105</v>
+      </c>
+      <c r="D7">
+        <v>0.14099999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>604</v>
+      </c>
+      <c r="B8" s="9">
+        <v>5.4999999999999997E-3</v>
+      </c>
+      <c r="C8" s="9">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="D8" s="9">
+        <v>7.7000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B38">
+        <v>2001</v>
+      </c>
+      <c r="C38">
+        <v>2011</v>
+      </c>
+      <c r="D38">
+        <v>2021</v>
+      </c>
+      <c r="F38">
+        <v>2015</v>
+      </c>
+      <c r="G38">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>596</v>
+      </c>
+      <c r="B39">
+        <v>68</v>
+      </c>
+      <c r="C39">
+        <v>100</v>
+      </c>
+      <c r="D39">
+        <v>123</v>
+      </c>
+      <c r="F39">
+        <v>110</v>
+      </c>
+      <c r="G39">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>594</v>
+      </c>
+      <c r="B40">
+        <f>cpi!D39</f>
+        <v>177.1</v>
+      </c>
+      <c r="C40">
+        <f>cpi!D49</f>
+        <v>224.93899999999999</v>
+      </c>
+      <c r="D40">
+        <f>cpi!D59</f>
+        <v>270.97000000000003</v>
+      </c>
+      <c r="F40">
+        <f>cpi!D53</f>
+        <v>237.017</v>
+      </c>
+      <c r="G40">
+        <f>cpi!D59</f>
+        <v>270.97000000000003</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>595</v>
+      </c>
+      <c r="B41">
+        <v>1</v>
+      </c>
+      <c r="C41">
+        <f>C40/B40</f>
+        <v>1.2701242236024846</v>
+      </c>
+      <c r="D41">
+        <f>D40/B40</f>
+        <v>1.5300395256916999</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
+      </c>
+      <c r="G41">
+        <f>G40/F40</f>
+        <v>1.143251327963817</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>597</v>
+      </c>
+      <c r="B42">
+        <f>B39/B41</f>
+        <v>68</v>
+      </c>
+      <c r="C42">
+        <f>C39/C41</f>
+        <v>78.732456354833971</v>
+      </c>
+      <c r="D42">
+        <f>D39/D41</f>
+        <v>80.390080082665961</v>
+      </c>
+      <c r="F42">
+        <f t="shared" ref="F42:G42" si="0">F39/F41</f>
+        <v>110</v>
+      </c>
+      <c r="G42">
+        <f t="shared" si="0"/>
+        <v>114.58547809720632</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>598</v>
+      </c>
+      <c r="B44" s="39">
+        <f>(D42/B42)^(1/(D38-B38))-1</f>
+        <v>8.4042733414155801E-3</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="F44" s="39">
+        <f>(G42/F42)^(1/(G38-F38))-1</f>
+        <v>6.8300041962665592E-3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>608</v>
+      </c>
+      <c r="B47" s="7">
+        <f>B44/B8</f>
+        <v>1.5280496984391965</v>
+      </c>
+      <c r="F47" s="7">
+        <f>F44/D8</f>
+        <v>0.88701353198266997</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>609</v>
+      </c>
+      <c r="B49" s="7">
+        <f>AVERAGE(B47,F47)</f>
+        <v>1.2075316152109332</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1D5271D-8741-40B6-92F2-97D4F5B6382F}">
   <dimension ref="A1:K13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -10202,9 +11747,9 @@
         <f>Lighting!G63</f>
         <v>1.1617489485420724</v>
       </c>
-      <c r="K2" s="27">
-        <f>H2</f>
-        <v>3.1863586362595919</v>
+      <c r="K2" s="26">
+        <f>mobile!$B$49</f>
+        <v>1.2075316152109332</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -10248,8 +11793,8 @@
         <v>1.1617489485420724</v>
       </c>
       <c r="K3" s="27">
-        <f t="shared" ref="K3:K13" si="3">H3</f>
-        <v>3.1863586362595919</v>
+        <f>$K$2</f>
+        <v>1.2075316152109332</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -10265,7 +11810,7 @@
         <v>5.8575070498108852</v>
       </c>
       <c r="D4" s="27">
-        <f t="shared" ref="D4:D13" si="4">C4</f>
+        <f t="shared" ref="D4:D13" si="3">C4</f>
         <v>5.8575070498108852</v>
       </c>
       <c r="E4" s="27">
@@ -10273,11 +11818,11 @@
         <v>5.8575070498108852</v>
       </c>
       <c r="F4" s="27">
-        <f t="shared" ref="F4:F13" si="5">$F$2</f>
+        <f t="shared" ref="F4:F13" si="4">$F$2</f>
         <v>0.84489777592279791</v>
       </c>
       <c r="G4" s="27">
-        <f t="shared" ref="G4:G13" si="6">$G$2</f>
+        <f t="shared" ref="G4:G13" si="5">$G$2</f>
         <v>2.5525704426134292</v>
       </c>
       <c r="H4" s="27">
@@ -10289,12 +11834,12 @@
         <v>7.4277116196437323</v>
       </c>
       <c r="J4" s="27">
-        <f t="shared" ref="J4:J13" si="7">$J$2</f>
+        <f t="shared" ref="J4:J13" si="6">$J$2</f>
         <v>1.1617489485420724</v>
       </c>
       <c r="K4" s="27">
-        <f t="shared" si="3"/>
-        <v>3.1863586362595919</v>
+        <f t="shared" ref="K4:K13" si="7">$K$2</f>
+        <v>1.2075316152109332</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -10310,7 +11855,7 @@
         <v>2.1980839095148221</v>
       </c>
       <c r="D5" s="27">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.1980839095148221</v>
       </c>
       <c r="E5" s="27">
@@ -10318,11 +11863,11 @@
         <v>2.1980839095148221</v>
       </c>
       <c r="F5" s="27">
+        <f t="shared" si="4"/>
+        <v>0.84489777592279791</v>
+      </c>
+      <c r="G5" s="27">
         <f t="shared" si="5"/>
-        <v>0.84489777592279791</v>
-      </c>
-      <c r="G5" s="27">
-        <f t="shared" si="6"/>
         <v>2.5525704426134292</v>
       </c>
       <c r="H5" s="27">
@@ -10334,12 +11879,12 @@
         <v>2.4280165739690442</v>
       </c>
       <c r="J5" s="27">
+        <f t="shared" si="6"/>
+        <v>1.1617489485420724</v>
+      </c>
+      <c r="K5" s="27">
         <f t="shared" si="7"/>
-        <v>1.1617489485420724</v>
-      </c>
-      <c r="K5" s="27">
-        <f t="shared" si="3"/>
-        <v>3.1863586362595919</v>
+        <v>1.2075316152109332</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -10355,7 +11900,7 @@
         <v>2.1980839095148221</v>
       </c>
       <c r="D6" s="27">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.1980839095148221</v>
       </c>
       <c r="E6" s="27">
@@ -10363,11 +11908,11 @@
         <v>2.1980839095148221</v>
       </c>
       <c r="F6" s="27">
+        <f t="shared" si="4"/>
+        <v>0.84489777592279791</v>
+      </c>
+      <c r="G6" s="27">
         <f t="shared" si="5"/>
-        <v>0.84489777592279791</v>
-      </c>
-      <c r="G6" s="27">
-        <f t="shared" si="6"/>
         <v>2.5525704426134292</v>
       </c>
       <c r="H6" s="27">
@@ -10375,16 +11920,16 @@
         <v>3.1863586362595919</v>
       </c>
       <c r="I6" s="27">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(B6:C6)</f>
         <v>6.4699072941282818</v>
       </c>
       <c r="J6" s="27">
+        <f t="shared" si="6"/>
+        <v>1.1617489485420724</v>
+      </c>
+      <c r="K6" s="27">
         <f t="shared" si="7"/>
-        <v>1.1617489485420724</v>
-      </c>
-      <c r="K6" s="27">
-        <f t="shared" si="3"/>
-        <v>3.1863586362595919</v>
+        <v>1.2075316152109332</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -10408,11 +11953,11 @@
         <v>4.0277954796628537</v>
       </c>
       <c r="F7" s="27">
+        <f t="shared" si="4"/>
+        <v>0.84489777592279791</v>
+      </c>
+      <c r="G7" s="27">
         <f t="shared" si="5"/>
-        <v>0.84489777592279791</v>
-      </c>
-      <c r="G7" s="27">
-        <f t="shared" si="6"/>
         <v>2.5525704426134292</v>
       </c>
       <c r="H7" s="27">
@@ -10424,12 +11969,12 @@
         <v>5.110100116295146</v>
       </c>
       <c r="J7" s="27">
+        <f t="shared" si="6"/>
+        <v>1.1617489485420724</v>
+      </c>
+      <c r="K7" s="27">
         <f t="shared" si="7"/>
-        <v>1.1617489485420724</v>
-      </c>
-      <c r="K7" s="27">
-        <f t="shared" si="3"/>
-        <v>3.1863586362595919</v>
+        <v>1.2075316152109332</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -10445,7 +11990,7 @@
         <v>2.1980839095148221</v>
       </c>
       <c r="D8" s="27">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.1980839095148221</v>
       </c>
       <c r="E8" s="27">
@@ -10453,11 +11998,11 @@
         <v>2.1980839095148221</v>
       </c>
       <c r="F8" s="27">
+        <f t="shared" si="4"/>
+        <v>0.84489777592279791</v>
+      </c>
+      <c r="G8" s="27">
         <f t="shared" si="5"/>
-        <v>0.84489777592279791</v>
-      </c>
-      <c r="G8" s="27">
-        <f t="shared" si="6"/>
         <v>2.5525704426134292</v>
       </c>
       <c r="H8" s="27">
@@ -10469,12 +12014,12 @@
         <v>6.4699072941282818</v>
       </c>
       <c r="J8" s="27">
+        <f t="shared" si="6"/>
+        <v>1.1617489485420724</v>
+      </c>
+      <c r="K8" s="27">
         <f t="shared" si="7"/>
-        <v>1.1617489485420724</v>
-      </c>
-      <c r="K8" s="27">
-        <f t="shared" si="3"/>
-        <v>3.1863586362595919</v>
+        <v>1.2075316152109332</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -10490,7 +12035,7 @@
         <v>2.1980839095148221</v>
       </c>
       <c r="D9" s="27">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.1980839095148221</v>
       </c>
       <c r="E9" s="27">
@@ -10498,11 +12043,11 @@
         <v>2.1980839095148221</v>
       </c>
       <c r="F9" s="27">
+        <f t="shared" si="4"/>
+        <v>0.84489777592279791</v>
+      </c>
+      <c r="G9" s="27">
         <f t="shared" si="5"/>
-        <v>0.84489777592279791</v>
-      </c>
-      <c r="G9" s="27">
-        <f t="shared" si="6"/>
         <v>2.5525704426134292</v>
       </c>
       <c r="H9" s="27">
@@ -10514,12 +12059,12 @@
         <v>6.4699072941282818</v>
       </c>
       <c r="J9" s="27">
+        <f t="shared" si="6"/>
+        <v>1.1617489485420724</v>
+      </c>
+      <c r="K9" s="27">
         <f t="shared" si="7"/>
-        <v>1.1617489485420724</v>
-      </c>
-      <c r="K9" s="27">
-        <f t="shared" si="3"/>
-        <v>3.1863586362595919</v>
+        <v>1.2075316152109332</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -10535,7 +12080,7 @@
         <v>2.1980839095148221</v>
       </c>
       <c r="D10" s="27">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.1980839095148221</v>
       </c>
       <c r="E10" s="27">
@@ -10543,11 +12088,11 @@
         <v>2.1980839095148221</v>
       </c>
       <c r="F10" s="27">
+        <f t="shared" si="4"/>
+        <v>0.84489777592279791</v>
+      </c>
+      <c r="G10" s="27">
         <f t="shared" si="5"/>
-        <v>0.84489777592279791</v>
-      </c>
-      <c r="G10" s="27">
-        <f t="shared" si="6"/>
         <v>2.5525704426134292</v>
       </c>
       <c r="H10" s="27">
@@ -10559,12 +12104,12 @@
         <v>5.5980000494957007</v>
       </c>
       <c r="J10" s="27">
+        <f t="shared" si="6"/>
+        <v>1.1617489485420724</v>
+      </c>
+      <c r="K10" s="27">
         <f t="shared" si="7"/>
-        <v>1.1617489485420724</v>
-      </c>
-      <c r="K10" s="27">
-        <f t="shared" si="3"/>
-        <v>3.1863586362595919</v>
+        <v>1.2075316152109332</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -10580,7 +12125,7 @@
         <v>2.1980839095148221</v>
       </c>
       <c r="D11" s="27">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.1980839095148221</v>
       </c>
       <c r="E11" s="27">
@@ -10588,11 +12133,11 @@
         <v>2.1980839095148221</v>
       </c>
       <c r="F11" s="27">
+        <f t="shared" si="4"/>
+        <v>0.84489777592279791</v>
+      </c>
+      <c r="G11" s="27">
         <f t="shared" si="5"/>
-        <v>0.84489777592279791</v>
-      </c>
-      <c r="G11" s="27">
-        <f t="shared" si="6"/>
         <v>2.5525704426134292</v>
       </c>
       <c r="H11" s="27">
@@ -10604,12 +12149,12 @@
         <v>5.5980000494957007</v>
       </c>
       <c r="J11" s="27">
+        <f t="shared" si="6"/>
+        <v>1.1617489485420724</v>
+      </c>
+      <c r="K11" s="27">
         <f t="shared" si="7"/>
-        <v>1.1617489485420724</v>
-      </c>
-      <c r="K11" s="27">
-        <f t="shared" si="3"/>
-        <v>3.1863586362595919</v>
+        <v>1.2075316152109332</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -10625,7 +12170,7 @@
         <v>2.1980839095148221</v>
       </c>
       <c r="D12" s="27">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.1980839095148221</v>
       </c>
       <c r="E12" s="27">
@@ -10633,11 +12178,11 @@
         <v>2.1980839095148221</v>
       </c>
       <c r="F12" s="27">
+        <f t="shared" si="4"/>
+        <v>0.84489777592279791</v>
+      </c>
+      <c r="G12" s="27">
         <f t="shared" si="5"/>
-        <v>0.84489777592279791</v>
-      </c>
-      <c r="G12" s="27">
-        <f t="shared" si="6"/>
         <v>2.5525704426134292</v>
       </c>
       <c r="H12" s="27">
@@ -10649,12 +12194,12 @@
         <v>5.5980000494957007</v>
       </c>
       <c r="J12" s="27">
+        <f t="shared" si="6"/>
+        <v>1.1617489485420724</v>
+      </c>
+      <c r="K12" s="27">
         <f t="shared" si="7"/>
-        <v>1.1617489485420724</v>
-      </c>
-      <c r="K12" s="27">
-        <f t="shared" si="3"/>
-        <v>3.1863586362595919</v>
+        <v>1.2075316152109332</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -10670,7 +12215,7 @@
         <v>2.1980839095148221</v>
       </c>
       <c r="D13" s="27">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.1980839095148221</v>
       </c>
       <c r="E13" s="27">
@@ -10678,11 +12223,11 @@
         <v>2.1980839095148221</v>
       </c>
       <c r="F13" s="27">
+        <f t="shared" si="4"/>
+        <v>0.84489777592279791</v>
+      </c>
+      <c r="G13" s="27">
         <f t="shared" si="5"/>
-        <v>0.84489777592279791</v>
-      </c>
-      <c r="G13" s="27">
-        <f t="shared" si="6"/>
         <v>2.5525704426134292</v>
       </c>
       <c r="H13" s="27">
@@ -10694,12 +12239,12 @@
         <v>5.5980000494957007</v>
       </c>
       <c r="J13" s="27">
+        <f t="shared" si="6"/>
+        <v>1.1617489485420724</v>
+      </c>
+      <c r="K13" s="27">
         <f t="shared" si="7"/>
-        <v>1.1617489485420724</v>
-      </c>
-      <c r="K13" s="27">
-        <f t="shared" si="3"/>
-        <v>3.1863586362595919</v>
+        <v>1.2075316152109332</v>
       </c>
     </row>
   </sheetData>
@@ -10707,7 +12252,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BB977EF-DFFE-4EEF-A0E1-DBBDDDFA9996}">
   <sheetPr>
     <tabColor theme="3" tint="9.9978637043366805E-2"/>
@@ -10796,8 +12341,8 @@
         <v>1.1617489485420724</v>
       </c>
       <c r="K2" s="27">
-        <f>calcs!K2</f>
-        <v>3.1863586362595919</v>
+        <f>mobile!B49</f>
+        <v>1.2075316152109332</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -10842,7 +12387,7 @@
       </c>
       <c r="K3" s="27">
         <f>calcs!K3</f>
-        <v>3.1863586362595919</v>
+        <v>1.2075316152109332</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -10887,7 +12432,7 @@
       </c>
       <c r="K4" s="27">
         <f>calcs!K4</f>
-        <v>3.1863586362595919</v>
+        <v>1.2075316152109332</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -10932,7 +12477,7 @@
       </c>
       <c r="K5" s="27">
         <f>calcs!K5</f>
-        <v>3.1863586362595919</v>
+        <v>1.2075316152109332</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -10977,7 +12522,7 @@
       </c>
       <c r="K6" s="27">
         <f>calcs!K6</f>
-        <v>3.1863586362595919</v>
+        <v>1.2075316152109332</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -11022,7 +12567,7 @@
       </c>
       <c r="K7" s="27">
         <f>calcs!K7</f>
-        <v>3.1863586362595919</v>
+        <v>1.2075316152109332</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -11067,7 +12612,7 @@
       </c>
       <c r="K8" s="27">
         <f>calcs!K8</f>
-        <v>3.1863586362595919</v>
+        <v>1.2075316152109332</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -11112,7 +12657,7 @@
       </c>
       <c r="K9" s="27">
         <f>calcs!K9</f>
-        <v>3.1863586362595919</v>
+        <v>1.2075316152109332</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -11157,7 +12702,7 @@
       </c>
       <c r="K10" s="27">
         <f>calcs!K10</f>
-        <v>3.1863586362595919</v>
+        <v>1.2075316152109332</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -11202,7 +12747,7 @@
       </c>
       <c r="K11" s="27">
         <f>calcs!K11</f>
-        <v>3.1863586362595919</v>
+        <v>1.2075316152109332</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -11247,7 +12792,7 @@
       </c>
       <c r="K12" s="27">
         <f>calcs!K12</f>
-        <v>3.1863586362595919</v>
+        <v>1.2075316152109332</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -11292,7 +12837,7 @@
       </c>
       <c r="K13" s="27">
         <f>calcs!K13</f>
-        <v>3.1863586362595919</v>
+        <v>1.2075316152109332</v>
       </c>
     </row>
   </sheetData>
@@ -11313,6 +12858,1419 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D47034FE-671A-414C-B645-6D2F26709972}">
+  <dimension ref="A1:O62"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="14" max="14" width="10.5703125" customWidth="1"/>
+    <col min="15" max="15" width="28.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>527</v>
+      </c>
+      <c r="B4" t="s">
+        <v>528</v>
+      </c>
+      <c r="D4" t="s">
+        <v>529</v>
+      </c>
+      <c r="E4" t="s">
+        <v>530</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>532</v>
+      </c>
+      <c r="C5" t="s">
+        <v>533</v>
+      </c>
+      <c r="E5" t="s">
+        <v>534</v>
+      </c>
+      <c r="F5" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>535</v>
+      </c>
+      <c r="B6" t="s">
+        <v>536</v>
+      </c>
+      <c r="C6" t="s">
+        <v>536</v>
+      </c>
+      <c r="D6">
+        <v>34.799999999999997</v>
+      </c>
+      <c r="E6">
+        <v>4.7</v>
+      </c>
+      <c r="F6">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>537</v>
+      </c>
+      <c r="B7" t="s">
+        <v>536</v>
+      </c>
+      <c r="C7" t="s">
+        <v>536</v>
+      </c>
+      <c r="D7">
+        <v>36.700000000000003</v>
+      </c>
+      <c r="E7">
+        <v>6.2</v>
+      </c>
+      <c r="F7">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>538</v>
+      </c>
+      <c r="B8" t="s">
+        <v>536</v>
+      </c>
+      <c r="C8" t="s">
+        <v>536</v>
+      </c>
+      <c r="D8">
+        <v>38.799999999999997</v>
+      </c>
+      <c r="E8">
+        <v>5.6</v>
+      </c>
+      <c r="F8">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>539</v>
+      </c>
+      <c r="B9" t="s">
+        <v>536</v>
+      </c>
+      <c r="C9" t="s">
+        <v>536</v>
+      </c>
+      <c r="D9">
+        <v>40.5</v>
+      </c>
+      <c r="E9">
+        <v>3.3</v>
+      </c>
+      <c r="F9">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>540</v>
+      </c>
+      <c r="B10" t="s">
+        <v>536</v>
+      </c>
+      <c r="C10" t="s">
+        <v>536</v>
+      </c>
+      <c r="D10">
+        <v>41.8</v>
+      </c>
+      <c r="E10">
+        <v>3.4</v>
+      </c>
+      <c r="F10">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>541</v>
+      </c>
+      <c r="B11" t="s">
+        <v>536</v>
+      </c>
+      <c r="C11" t="s">
+        <v>536</v>
+      </c>
+      <c r="D11">
+        <v>44.4</v>
+      </c>
+      <c r="E11">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="F11">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>542</v>
+      </c>
+      <c r="B12" t="s">
+        <v>536</v>
+      </c>
+      <c r="C12" t="s">
+        <v>536</v>
+      </c>
+      <c r="D12">
+        <v>49.3</v>
+      </c>
+      <c r="E12">
+        <v>12.3</v>
+      </c>
+      <c r="F12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>543</v>
+      </c>
+      <c r="B13" t="s">
+        <v>536</v>
+      </c>
+      <c r="C13" t="s">
+        <v>536</v>
+      </c>
+      <c r="D13">
+        <v>53.8</v>
+      </c>
+      <c r="E13">
+        <v>6.9</v>
+      </c>
+      <c r="F13">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>544</v>
+      </c>
+      <c r="B14" t="s">
+        <v>536</v>
+      </c>
+      <c r="C14" t="s">
+        <v>536</v>
+      </c>
+      <c r="D14">
+        <v>56.9</v>
+      </c>
+      <c r="E14">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="F14">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>545</v>
+      </c>
+      <c r="B15" t="s">
+        <v>536</v>
+      </c>
+      <c r="C15" t="s">
+        <v>536</v>
+      </c>
+      <c r="D15">
+        <v>60.6</v>
+      </c>
+      <c r="E15">
+        <v>6.7</v>
+      </c>
+      <c r="F15">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>546</v>
+      </c>
+      <c r="B16" t="s">
+        <v>536</v>
+      </c>
+      <c r="C16" t="s">
+        <v>536</v>
+      </c>
+      <c r="D16">
+        <v>65.2</v>
+      </c>
+      <c r="E16">
+        <v>9</v>
+      </c>
+      <c r="F16">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>547</v>
+      </c>
+      <c r="B17" t="s">
+        <v>536</v>
+      </c>
+      <c r="C17" t="s">
+        <v>536</v>
+      </c>
+      <c r="D17">
+        <v>72.599999999999994</v>
+      </c>
+      <c r="E17">
+        <v>13.3</v>
+      </c>
+      <c r="F17">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>548</v>
+      </c>
+      <c r="B18" t="s">
+        <v>536</v>
+      </c>
+      <c r="C18" t="s">
+        <v>536</v>
+      </c>
+      <c r="D18">
+        <v>82.4</v>
+      </c>
+      <c r="E18">
+        <v>12.5</v>
+      </c>
+      <c r="F18">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>549</v>
+      </c>
+      <c r="B19" t="s">
+        <v>536</v>
+      </c>
+      <c r="C19" t="s">
+        <v>536</v>
+      </c>
+      <c r="D19">
+        <v>90.9</v>
+      </c>
+      <c r="E19">
+        <v>8.9</v>
+      </c>
+      <c r="F19">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>550</v>
+      </c>
+      <c r="B20" t="s">
+        <v>536</v>
+      </c>
+      <c r="C20" t="s">
+        <v>536</v>
+      </c>
+      <c r="D20">
+        <v>96.5</v>
+      </c>
+      <c r="E20">
+        <v>3.8</v>
+      </c>
+      <c r="F20">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>551</v>
+      </c>
+      <c r="B21" t="s">
+        <v>536</v>
+      </c>
+      <c r="C21" t="s">
+        <v>536</v>
+      </c>
+      <c r="D21">
+        <v>99.6</v>
+      </c>
+      <c r="E21">
+        <v>3.8</v>
+      </c>
+      <c r="F21">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>552</v>
+      </c>
+      <c r="B22" s="35">
+        <v>102.9</v>
+      </c>
+      <c r="C22" s="35">
+        <v>104.9</v>
+      </c>
+      <c r="D22" s="35">
+        <v>103.9</v>
+      </c>
+      <c r="E22">
+        <v>3.9</v>
+      </c>
+      <c r="F22">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>553</v>
+      </c>
+      <c r="B23" s="35">
+        <v>106.6</v>
+      </c>
+      <c r="C23" s="35">
+        <v>108.5</v>
+      </c>
+      <c r="D23" s="35">
+        <v>107.6</v>
+      </c>
+      <c r="E23">
+        <v>3.8</v>
+      </c>
+      <c r="F23">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>554</v>
+      </c>
+      <c r="B24" s="35">
+        <v>109.1</v>
+      </c>
+      <c r="C24" s="35">
+        <v>110.1</v>
+      </c>
+      <c r="D24" s="35">
+        <v>109.6</v>
+      </c>
+      <c r="E24">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F24">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>555</v>
+      </c>
+      <c r="B25" s="35">
+        <v>112.4</v>
+      </c>
+      <c r="C25" s="35">
+        <v>114.9</v>
+      </c>
+      <c r="D25" s="35">
+        <v>113.6</v>
+      </c>
+      <c r="E25">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="F25">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>556</v>
+      </c>
+      <c r="B26" s="35">
+        <v>116.8</v>
+      </c>
+      <c r="C26" s="35">
+        <v>119.7</v>
+      </c>
+      <c r="D26" s="35">
+        <v>118.3</v>
+      </c>
+      <c r="E26">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="F26">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>557</v>
+      </c>
+      <c r="B27" s="35">
+        <v>122.7</v>
+      </c>
+      <c r="C27" s="35">
+        <v>125.3</v>
+      </c>
+      <c r="D27" s="35">
+        <v>124</v>
+      </c>
+      <c r="E27">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="F27">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>558</v>
+      </c>
+      <c r="B28" s="35">
+        <v>128.69999999999999</v>
+      </c>
+      <c r="C28" s="35">
+        <v>132.6</v>
+      </c>
+      <c r="D28" s="35">
+        <v>130.69999999999999</v>
+      </c>
+      <c r="E28">
+        <v>6.1</v>
+      </c>
+      <c r="F28">
+        <v>5.4</v>
+      </c>
+      <c r="G28" s="27">
+        <f>$D$50/D28</f>
+        <v>1.7566488140780414</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>559</v>
+      </c>
+      <c r="B29" s="35">
+        <v>135.19999999999999</v>
+      </c>
+      <c r="C29" s="35">
+        <v>137.19999999999999</v>
+      </c>
+      <c r="D29" s="35">
+        <v>136.19999999999999</v>
+      </c>
+      <c r="E29">
+        <v>3.1</v>
+      </c>
+      <c r="F29">
+        <v>4.2</v>
+      </c>
+      <c r="G29" s="27">
+        <f t="shared" ref="G29:G62" si="0">$D$50/D29</f>
+        <v>1.6857121879588841</v>
+      </c>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+      <c r="O29" s="1"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>560</v>
+      </c>
+      <c r="B30" s="35">
+        <v>139.19999999999999</v>
+      </c>
+      <c r="C30" s="35">
+        <v>141.4</v>
+      </c>
+      <c r="D30" s="35">
+        <v>140.30000000000001</v>
+      </c>
+      <c r="E30">
+        <v>2.9</v>
+      </c>
+      <c r="F30">
+        <v>3</v>
+      </c>
+      <c r="G30" s="27">
+        <f t="shared" si="0"/>
+        <v>1.6364504632929435</v>
+      </c>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2"/>
+      <c r="O30" s="36"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>561</v>
+      </c>
+      <c r="B31" s="35">
+        <v>143.69999999999999</v>
+      </c>
+      <c r="C31" s="35">
+        <v>145.30000000000001</v>
+      </c>
+      <c r="D31" s="35">
+        <v>144.5</v>
+      </c>
+      <c r="E31">
+        <v>2.7</v>
+      </c>
+      <c r="F31">
+        <v>3</v>
+      </c>
+      <c r="G31" s="27">
+        <f t="shared" si="0"/>
+        <v>1.5888858131487889</v>
+      </c>
+      <c r="M31" s="2"/>
+      <c r="N31" s="2"/>
+      <c r="O31" s="36"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>562</v>
+      </c>
+      <c r="B32" s="35">
+        <v>147.19999999999999</v>
+      </c>
+      <c r="C32" s="35">
+        <v>149.30000000000001</v>
+      </c>
+      <c r="D32" s="35">
+        <v>148.19999999999999</v>
+      </c>
+      <c r="E32">
+        <v>2.7</v>
+      </c>
+      <c r="F32">
+        <v>2.6</v>
+      </c>
+      <c r="G32" s="27">
+        <f t="shared" si="0"/>
+        <v>1.5492172739541161</v>
+      </c>
+      <c r="M32" s="2"/>
+      <c r="N32" s="2"/>
+      <c r="O32" s="36"/>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>563</v>
+      </c>
+      <c r="B33" s="35">
+        <v>151.5</v>
+      </c>
+      <c r="C33" s="35">
+        <v>153.19999999999999</v>
+      </c>
+      <c r="D33" s="35">
+        <v>152.4</v>
+      </c>
+      <c r="E33">
+        <v>2.5</v>
+      </c>
+      <c r="F33">
+        <v>2.8</v>
+      </c>
+      <c r="G33" s="27">
+        <f t="shared" si="0"/>
+        <v>1.5065223097112861</v>
+      </c>
+      <c r="M33" s="2"/>
+      <c r="N33" s="2"/>
+      <c r="O33" s="36"/>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>564</v>
+      </c>
+      <c r="B34" s="35">
+        <v>155.80000000000001</v>
+      </c>
+      <c r="C34" s="35">
+        <v>157.9</v>
+      </c>
+      <c r="D34" s="35">
+        <v>156.9</v>
+      </c>
+      <c r="E34">
+        <v>3.3</v>
+      </c>
+      <c r="F34">
+        <v>3</v>
+      </c>
+      <c r="G34" s="27">
+        <f t="shared" si="0"/>
+        <v>1.4633142128744423</v>
+      </c>
+      <c r="M34" s="2"/>
+      <c r="N34" s="2"/>
+      <c r="O34" s="36"/>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>565</v>
+      </c>
+      <c r="B35" s="35">
+        <v>159.9</v>
+      </c>
+      <c r="C35" s="35">
+        <v>161.19999999999999</v>
+      </c>
+      <c r="D35" s="35">
+        <v>160.5</v>
+      </c>
+      <c r="E35">
+        <v>1.7</v>
+      </c>
+      <c r="F35">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G35" s="27">
+        <f t="shared" si="0"/>
+        <v>1.4304922118380061</v>
+      </c>
+      <c r="M35" s="2"/>
+      <c r="N35" s="2"/>
+      <c r="O35" s="36"/>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>566</v>
+      </c>
+      <c r="B36" s="35">
+        <v>162.30000000000001</v>
+      </c>
+      <c r="C36" s="35">
+        <v>163.69999999999999</v>
+      </c>
+      <c r="D36" s="35">
+        <v>163</v>
+      </c>
+      <c r="E36">
+        <v>1.6</v>
+      </c>
+      <c r="F36">
+        <v>1.6</v>
+      </c>
+      <c r="G36" s="27">
+        <f t="shared" si="0"/>
+        <v>1.4085521472392637</v>
+      </c>
+      <c r="M36" s="2"/>
+      <c r="N36" s="2"/>
+      <c r="O36" s="36"/>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>567</v>
+      </c>
+      <c r="B37" s="35">
+        <v>165.4</v>
+      </c>
+      <c r="C37" s="35">
+        <v>167.8</v>
+      </c>
+      <c r="D37" s="35">
+        <v>166.6</v>
+      </c>
+      <c r="E37">
+        <v>2.7</v>
+      </c>
+      <c r="F37">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="G37" s="27">
+        <f t="shared" si="0"/>
+        <v>1.3781152460984394</v>
+      </c>
+      <c r="M37" s="2"/>
+      <c r="N37" s="2"/>
+      <c r="O37" s="36"/>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>568</v>
+      </c>
+      <c r="B38" s="35">
+        <v>170.8</v>
+      </c>
+      <c r="C38" s="35">
+        <v>173.6</v>
+      </c>
+      <c r="D38" s="35">
+        <v>172.2</v>
+      </c>
+      <c r="E38">
+        <v>3.4</v>
+      </c>
+      <c r="F38">
+        <v>3.4</v>
+      </c>
+      <c r="G38" s="27">
+        <f t="shared" si="0"/>
+        <v>1.3332984901277585</v>
+      </c>
+      <c r="M38" s="2"/>
+      <c r="N38" s="37"/>
+      <c r="O38" s="36"/>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>569</v>
+      </c>
+      <c r="B39" s="35">
+        <v>176.6</v>
+      </c>
+      <c r="C39" s="35">
+        <v>177.5</v>
+      </c>
+      <c r="D39" s="35">
+        <v>177.1</v>
+      </c>
+      <c r="E39">
+        <v>1.6</v>
+      </c>
+      <c r="F39">
+        <v>2.8</v>
+      </c>
+      <c r="G39" s="27">
+        <f t="shared" si="0"/>
+        <v>1.2964088085827217</v>
+      </c>
+      <c r="M39" s="2"/>
+      <c r="N39" s="2"/>
+      <c r="O39" s="36"/>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>570</v>
+      </c>
+      <c r="B40" s="35">
+        <v>178.9</v>
+      </c>
+      <c r="C40" s="35">
+        <v>180.9</v>
+      </c>
+      <c r="D40" s="35">
+        <v>179.9</v>
+      </c>
+      <c r="E40">
+        <v>2.4</v>
+      </c>
+      <c r="F40">
+        <v>1.6</v>
+      </c>
+      <c r="G40" s="27">
+        <f t="shared" si="0"/>
+        <v>1.276231239577543</v>
+      </c>
+      <c r="M40" s="2"/>
+      <c r="N40" s="2"/>
+      <c r="O40" s="36"/>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>571</v>
+      </c>
+      <c r="B41" s="35">
+        <v>183.3</v>
+      </c>
+      <c r="C41" s="35">
+        <v>184.6</v>
+      </c>
+      <c r="D41" s="35">
+        <v>184</v>
+      </c>
+      <c r="E41">
+        <v>1.9</v>
+      </c>
+      <c r="F41">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G41" s="27">
+        <f t="shared" si="0"/>
+        <v>1.2477934782608695</v>
+      </c>
+      <c r="M41" s="2"/>
+      <c r="N41" s="2"/>
+      <c r="O41" s="36"/>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>572</v>
+      </c>
+      <c r="B42" s="35">
+        <v>187.6</v>
+      </c>
+      <c r="C42" s="35">
+        <v>190.2</v>
+      </c>
+      <c r="D42" s="35">
+        <v>188.9</v>
+      </c>
+      <c r="E42">
+        <v>3.3</v>
+      </c>
+      <c r="F42">
+        <v>2.7</v>
+      </c>
+      <c r="G42" s="27">
+        <f t="shared" si="0"/>
+        <v>1.2154261514028586</v>
+      </c>
+      <c r="M42" s="2"/>
+      <c r="N42" s="2"/>
+      <c r="O42" s="36"/>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>573</v>
+      </c>
+      <c r="B43" s="35">
+        <v>193.2</v>
+      </c>
+      <c r="C43" s="35">
+        <v>197.4</v>
+      </c>
+      <c r="D43" s="35">
+        <v>195.3</v>
+      </c>
+      <c r="E43">
+        <v>3.4</v>
+      </c>
+      <c r="F43">
+        <v>3.4</v>
+      </c>
+      <c r="G43" s="27">
+        <f t="shared" si="0"/>
+        <v>1.1755965181771633</v>
+      </c>
+      <c r="M43" s="2"/>
+      <c r="N43" s="37"/>
+      <c r="O43" s="36"/>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>574</v>
+      </c>
+      <c r="B44" s="35">
+        <v>200.6</v>
+      </c>
+      <c r="C44" s="35">
+        <v>202.6</v>
+      </c>
+      <c r="D44" s="35">
+        <v>201.6</v>
+      </c>
+      <c r="E44">
+        <v>2.5</v>
+      </c>
+      <c r="F44">
+        <v>3.2</v>
+      </c>
+      <c r="G44" s="27">
+        <f t="shared" si="0"/>
+        <v>1.1388591269841271</v>
+      </c>
+      <c r="M44" s="2"/>
+      <c r="N44" s="2"/>
+      <c r="O44" s="36"/>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>575</v>
+      </c>
+      <c r="B45" s="38">
+        <v>205.709</v>
+      </c>
+      <c r="C45" s="38">
+        <v>208.976</v>
+      </c>
+      <c r="D45" s="38">
+        <v>207.34200000000001</v>
+      </c>
+      <c r="E45">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="F45">
+        <v>2.8</v>
+      </c>
+      <c r="G45" s="27">
+        <f t="shared" si="0"/>
+        <v>1.107320272786025</v>
+      </c>
+      <c r="M45" s="2"/>
+      <c r="N45" s="2"/>
+      <c r="O45" s="36"/>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>576</v>
+      </c>
+      <c r="B46" s="38">
+        <v>214.429</v>
+      </c>
+      <c r="C46" s="38">
+        <v>216.17699999999999</v>
+      </c>
+      <c r="D46" s="38">
+        <v>215.303</v>
+      </c>
+      <c r="E46">
+        <v>0.1</v>
+      </c>
+      <c r="F46">
+        <v>3.8</v>
+      </c>
+      <c r="G46" s="27">
+        <f t="shared" si="0"/>
+        <v>1.0663762232760343</v>
+      </c>
+      <c r="M46" s="2"/>
+      <c r="N46" s="2"/>
+      <c r="O46" s="36"/>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>577</v>
+      </c>
+      <c r="B47" s="38">
+        <v>213.13900000000001</v>
+      </c>
+      <c r="C47" s="38">
+        <v>215.935</v>
+      </c>
+      <c r="D47" s="38">
+        <v>214.53700000000001</v>
+      </c>
+      <c r="E47">
+        <v>2.7</v>
+      </c>
+      <c r="F47">
+        <v>-0.4</v>
+      </c>
+      <c r="G47" s="27">
+        <f t="shared" si="0"/>
+        <v>1.0701836979169095</v>
+      </c>
+      <c r="M47" s="2"/>
+      <c r="N47" s="2"/>
+      <c r="O47" s="36"/>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>578</v>
+      </c>
+      <c r="B48" s="38">
+        <v>217.535</v>
+      </c>
+      <c r="C48" s="38">
+        <v>218.57599999999999</v>
+      </c>
+      <c r="D48" s="38">
+        <v>218.05600000000001</v>
+      </c>
+      <c r="E48">
+        <v>1.5</v>
+      </c>
+      <c r="F48">
+        <v>1.6</v>
+      </c>
+      <c r="G48" s="27">
+        <f t="shared" si="0"/>
+        <v>1.0529130131709286</v>
+      </c>
+      <c r="M48" s="2"/>
+      <c r="N48" s="2"/>
+      <c r="O48" s="36"/>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>579</v>
+      </c>
+      <c r="B49" s="38">
+        <v>223.59800000000001</v>
+      </c>
+      <c r="C49" s="38">
+        <v>226.28</v>
+      </c>
+      <c r="D49" s="38">
+        <v>224.93899999999999</v>
+      </c>
+      <c r="E49">
+        <v>3</v>
+      </c>
+      <c r="F49">
+        <v>3.2</v>
+      </c>
+      <c r="G49" s="27">
+        <f t="shared" si="0"/>
+        <v>1.0206944993976144</v>
+      </c>
+      <c r="M49" s="2"/>
+      <c r="N49" s="2"/>
+      <c r="O49" s="36"/>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>580</v>
+      </c>
+      <c r="B50" s="38">
+        <v>228.85</v>
+      </c>
+      <c r="C50" s="38">
+        <v>230.33799999999999</v>
+      </c>
+      <c r="D50" s="38">
+        <v>229.59399999999999</v>
+      </c>
+      <c r="E50">
+        <v>1.7</v>
+      </c>
+      <c r="F50">
+        <v>2.1</v>
+      </c>
+      <c r="G50" s="27">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M50" s="2"/>
+      <c r="N50" s="2"/>
+      <c r="O50" s="36"/>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>581</v>
+      </c>
+      <c r="B51" s="38">
+        <v>232.36600000000001</v>
+      </c>
+      <c r="C51" s="38">
+        <v>233.548</v>
+      </c>
+      <c r="D51" s="38">
+        <v>232.95699999999999</v>
+      </c>
+      <c r="E51">
+        <v>1.5</v>
+      </c>
+      <c r="F51">
+        <v>1.5</v>
+      </c>
+      <c r="G51" s="27">
+        <f t="shared" si="0"/>
+        <v>0.98556385942470071</v>
+      </c>
+      <c r="M51" s="2"/>
+      <c r="N51" s="2"/>
+      <c r="O51" s="36"/>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>582</v>
+      </c>
+      <c r="B52" s="38">
+        <v>236.38399999999999</v>
+      </c>
+      <c r="C52" s="38">
+        <v>237.08799999999999</v>
+      </c>
+      <c r="D52" s="38">
+        <v>236.73599999999999</v>
+      </c>
+      <c r="E52">
+        <v>0.8</v>
+      </c>
+      <c r="F52">
+        <v>1.6</v>
+      </c>
+      <c r="G52" s="27">
+        <f t="shared" si="0"/>
+        <v>0.96983137334414704</v>
+      </c>
+      <c r="M52" s="2"/>
+      <c r="N52" s="2"/>
+      <c r="O52" s="36"/>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>583</v>
+      </c>
+      <c r="B53" s="38">
+        <v>236.26499999999999</v>
+      </c>
+      <c r="C53" s="38">
+        <v>237.76900000000001</v>
+      </c>
+      <c r="D53" s="38">
+        <v>237.017</v>
+      </c>
+      <c r="E53">
+        <v>0.7</v>
+      </c>
+      <c r="F53">
+        <v>0.1</v>
+      </c>
+      <c r="G53" s="27">
+        <f t="shared" si="0"/>
+        <v>0.9686815713640794</v>
+      </c>
+      <c r="M53" s="2"/>
+      <c r="N53" s="2"/>
+      <c r="O53" s="36"/>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>584</v>
+      </c>
+      <c r="B54" s="38">
+        <v>238.77799999999999</v>
+      </c>
+      <c r="C54" s="38">
+        <v>241.23699999999999</v>
+      </c>
+      <c r="D54" s="38">
+        <v>240.00700000000001</v>
+      </c>
+      <c r="E54">
+        <v>2.1</v>
+      </c>
+      <c r="F54">
+        <v>1.3</v>
+      </c>
+      <c r="G54" s="27">
+        <f t="shared" si="0"/>
+        <v>0.95661376543184151</v>
+      </c>
+      <c r="M54" s="2"/>
+      <c r="N54" s="2"/>
+      <c r="O54" s="36"/>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>585</v>
+      </c>
+      <c r="B55" s="38">
+        <v>244.07599999999999</v>
+      </c>
+      <c r="C55" s="38">
+        <v>246.16300000000001</v>
+      </c>
+      <c r="D55" s="38">
+        <v>245.12</v>
+      </c>
+      <c r="E55">
+        <v>2.1</v>
+      </c>
+      <c r="F55">
+        <v>2.1</v>
+      </c>
+      <c r="G55" s="27">
+        <f t="shared" si="0"/>
+        <v>0.93665959530026111</v>
+      </c>
+      <c r="M55" s="2"/>
+      <c r="N55" s="2"/>
+      <c r="O55" s="36"/>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>586</v>
+      </c>
+      <c r="B56" s="38">
+        <v>250.089</v>
+      </c>
+      <c r="C56" s="38">
+        <v>252.125</v>
+      </c>
+      <c r="D56" s="38">
+        <v>251.107</v>
+      </c>
+      <c r="E56">
+        <v>1.9</v>
+      </c>
+      <c r="F56">
+        <v>2.4</v>
+      </c>
+      <c r="G56" s="27">
+        <f t="shared" si="0"/>
+        <v>0.9143273584567535</v>
+      </c>
+      <c r="M56" s="2"/>
+      <c r="N56" s="2"/>
+      <c r="O56" s="36"/>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>587</v>
+      </c>
+      <c r="B57" s="38">
+        <v>254.41200000000001</v>
+      </c>
+      <c r="C57" s="38">
+        <v>256.90300000000002</v>
+      </c>
+      <c r="D57" s="38">
+        <v>255.65700000000001</v>
+      </c>
+      <c r="E57">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="F57">
+        <v>1.8</v>
+      </c>
+      <c r="G57" s="27">
+        <f t="shared" si="0"/>
+        <v>0.89805481563188172</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>588</v>
+      </c>
+      <c r="B58" s="38">
+        <v>257.55700000000002</v>
+      </c>
+      <c r="C58" s="38">
+        <v>260.065</v>
+      </c>
+      <c r="D58" s="38">
+        <v>258.81099999999998</v>
+      </c>
+      <c r="E58">
+        <v>1.4</v>
+      </c>
+      <c r="F58">
+        <v>1.2</v>
+      </c>
+      <c r="G58" s="27">
+        <f t="shared" si="0"/>
+        <v>0.88711067149387013</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>589</v>
+      </c>
+      <c r="B59" s="38">
+        <v>266.23599999999999</v>
+      </c>
+      <c r="C59" s="38">
+        <v>275.70299999999997</v>
+      </c>
+      <c r="D59" s="38">
+        <v>270.97000000000003</v>
+      </c>
+      <c r="E59">
+        <v>7</v>
+      </c>
+      <c r="F59">
+        <v>4.7</v>
+      </c>
+      <c r="G59" s="27">
+        <f t="shared" si="0"/>
+        <v>0.84730412960844359</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>590</v>
+      </c>
+      <c r="B60" s="38">
+        <v>288.34699999999998</v>
+      </c>
+      <c r="C60" s="38">
+        <v>296.96300000000002</v>
+      </c>
+      <c r="D60" s="38">
+        <v>292.65499999999997</v>
+      </c>
+      <c r="E60">
+        <v>6.5</v>
+      </c>
+      <c r="F60">
+        <v>8</v>
+      </c>
+      <c r="G60" s="27">
+        <f t="shared" si="0"/>
+        <v>0.78452102304761584</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>591</v>
+      </c>
+      <c r="B61" s="38">
+        <v>302.40800000000002</v>
+      </c>
+      <c r="C61" s="38">
+        <v>306.99599999999998</v>
+      </c>
+      <c r="D61" s="38">
+        <v>304.702</v>
+      </c>
+      <c r="G61" s="27">
+        <f t="shared" si="0"/>
+        <v>0.75350342301658668</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>592</v>
+      </c>
+      <c r="B62">
+        <v>312.14499999999998</v>
+      </c>
+      <c r="C62">
+        <v>315.233</v>
+      </c>
+      <c r="D62">
+        <v>313.68900000000002</v>
+      </c>
+      <c r="G62" s="27">
+        <f t="shared" si="0"/>
+        <v>0.73191600598044548</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A366C323-AEA8-47A1-8400-4A398ED6DC8A}">
   <dimension ref="A1:H49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -11828,7 +14786,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79CA3ECE-CC46-4C9C-9910-1D3FD99A313F}">
   <dimension ref="B2:H29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -12137,7 +15095,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44C2550C-391B-4AED-8625-12FCF8A24E5E}">
   <dimension ref="A1:M90"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -13696,7 +16654,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AB4F1A2-F703-4C6F-AA45-D27647AF57D3}">
   <dimension ref="A1:L15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -14029,7 +16987,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2293F3F-9A88-4413-B145-B7568F539BC4}">
   <dimension ref="B2:J20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -14308,7 +17266,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5F4C270-6BF9-4D0D-85CD-90AE6754A5FB}">
   <dimension ref="A2:W114"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -16564,7 +19522,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC1B79DA-1807-4980-8716-C48017AC8EE8}">
   <dimension ref="B2:X23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -17418,914 +20376,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1873BFA-BFB8-479B-8580-77E23D72D642}">
-  <dimension ref="B1:M51"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.85546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="I1" s="1"/>
-    </row>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
-        <v>112</v>
-      </c>
-      <c r="I2" s="1"/>
-    </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E3" t="s">
-        <v>116</v>
-      </c>
-      <c r="I3" s="1"/>
-    </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="C4" s="12">
-        <v>0.8</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="F4" s="11">
-        <f>D4+$E$6</f>
-        <v>6928</v>
-      </c>
-      <c r="L4" t="s">
-        <v>117</v>
-      </c>
-      <c r="M4" s="1">
-        <f>AVERAGE(H5:H11)</f>
-        <v>7.5361437213570515</v>
-      </c>
-    </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="C5" s="12">
-        <v>0.81</v>
-      </c>
-      <c r="D5" s="11">
-        <v>472</v>
-      </c>
-      <c r="F5" s="11">
-        <f t="shared" ref="F5:F11" si="0">D5+$E$6</f>
-        <v>7400</v>
-      </c>
-      <c r="H5">
-        <f>((F5-$F$4)/($F$4))/((C5-$C$4)/($C$4))</f>
-        <v>5.4503464203233207</v>
-      </c>
-      <c r="I5" s="1"/>
-      <c r="L5" t="s">
-        <v>118</v>
-      </c>
-      <c r="M5" s="1">
-        <f>AVERAGE(H13:H17)</f>
-        <v>10.236696165191734</v>
-      </c>
-    </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C6" s="12">
-        <v>0.82</v>
-      </c>
-      <c r="D6">
-        <v>977</v>
-      </c>
-      <c r="E6" s="11">
-        <v>6928</v>
-      </c>
-      <c r="F6" s="11">
-        <f t="shared" si="0"/>
-        <v>7905</v>
-      </c>
-      <c r="H6">
-        <f t="shared" ref="H6:H11" si="1">((F6-$F$4)/($F$4))/((C6-$C$4)/($C$4))</f>
-        <v>5.6408775981524517</v>
-      </c>
-      <c r="I6" s="1"/>
-      <c r="L6" t="s">
-        <v>119</v>
-      </c>
-      <c r="M6" s="1">
-        <f>AVERAGE(H19:H24)</f>
-        <v>7.5709278650378069</v>
-      </c>
-    </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="C7" s="12">
-        <v>0.84</v>
-      </c>
-      <c r="D7" s="11">
-        <v>2759</v>
-      </c>
-      <c r="F7" s="11">
-        <f t="shared" si="0"/>
-        <v>9687</v>
-      </c>
-      <c r="H7">
-        <f t="shared" si="1"/>
-        <v>7.9647806004619088</v>
-      </c>
-      <c r="I7" s="1"/>
-      <c r="L7" t="s">
-        <v>120</v>
-      </c>
-      <c r="M7" s="1">
-        <f>AVERAGE(H26:H29)</f>
-        <v>13.093142804855722</v>
-      </c>
-    </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="C8" s="12">
-        <v>0.85</v>
-      </c>
-      <c r="D8">
-        <v>3561</v>
-      </c>
-      <c r="F8" s="11">
-        <f t="shared" si="0"/>
-        <v>10489</v>
-      </c>
-      <c r="H8">
-        <f t="shared" si="1"/>
-        <v>8.2240184757505883</v>
-      </c>
-      <c r="I8" s="1"/>
-      <c r="L8" t="s">
-        <v>121</v>
-      </c>
-      <c r="M8" s="1">
-        <f>AVERAGE(H31:H35)</f>
-        <v>6.8445086849877326</v>
-      </c>
-    </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="C9" s="12">
-        <v>0.93</v>
-      </c>
-      <c r="D9" s="11">
-        <v>10027</v>
-      </c>
-      <c r="F9" s="11">
-        <f t="shared" si="0"/>
-        <v>16955</v>
-      </c>
-      <c r="H9">
-        <f t="shared" si="1"/>
-        <v>8.9065553384260081</v>
-      </c>
-      <c r="I9" s="1"/>
-      <c r="L9" t="s">
-        <v>122</v>
-      </c>
-      <c r="M9" s="1">
-        <f>AVERAGE(H37:H42)</f>
-        <v>4.7753002649653098</v>
-      </c>
-    </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="C10" s="12">
-        <v>0.95</v>
-      </c>
-      <c r="D10" s="11">
-        <v>10494</v>
-      </c>
-      <c r="F10" s="11">
-        <f t="shared" si="0"/>
-        <v>17422</v>
-      </c>
-      <c r="H10">
-        <f t="shared" si="1"/>
-        <v>8.0785219399538146</v>
-      </c>
-      <c r="I10" s="1"/>
-      <c r="L10" t="s">
-        <v>123</v>
-      </c>
-      <c r="M10" s="1">
-        <f>AVERAGE(H44:H46)</f>
-        <v>10.329147244310422</v>
-      </c>
-    </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="C11" s="12">
-        <v>0.99</v>
-      </c>
-      <c r="D11" s="11">
-        <v>13966</v>
-      </c>
-      <c r="F11" s="11">
-        <f t="shared" si="0"/>
-        <v>20894</v>
-      </c>
-      <c r="H11">
-        <f t="shared" si="1"/>
-        <v>8.4879056764312661</v>
-      </c>
-      <c r="I11" s="1"/>
-      <c r="L11" t="s">
-        <v>124</v>
-      </c>
-      <c r="M11" s="1">
-        <f>AVERAGE(H48:H50)</f>
-        <v>7.1185033686236947</v>
-      </c>
-    </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="C12" s="12">
-        <v>0.82</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="F12" s="11">
-        <f>D12+$E$14</f>
-        <v>21244</v>
-      </c>
-    </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="C13" s="12">
-        <v>0.83</v>
-      </c>
-      <c r="D13" s="11">
-        <v>2534</v>
-      </c>
-      <c r="F13" s="11">
-        <f t="shared" ref="F13:F17" si="2">D13+$E$14</f>
-        <v>23778</v>
-      </c>
-      <c r="H13">
-        <f>((F13-$F$12)/($F$12))/((C13-$C$12)/($C$12))</f>
-        <v>9.7810205234419048</v>
-      </c>
-      <c r="I13" s="1"/>
-    </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
-        <v>118</v>
-      </c>
-      <c r="C14" s="12">
-        <v>0.84</v>
-      </c>
-      <c r="D14" s="5">
-        <v>5370</v>
-      </c>
-      <c r="E14" s="11">
-        <v>21244</v>
-      </c>
-      <c r="F14" s="11">
-        <f t="shared" si="2"/>
-        <v>26614</v>
-      </c>
-      <c r="H14">
-        <f t="shared" ref="H14:H17" si="3">((F14-$F$12)/($F$12))/((C14-$C$12)/($C$12))</f>
-        <v>10.363867444925617</v>
-      </c>
-      <c r="I14" s="1"/>
-    </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="C15" s="12">
-        <v>0.85</v>
-      </c>
-      <c r="D15" s="11">
-        <v>8544</v>
-      </c>
-      <c r="F15" s="11">
-        <f t="shared" si="2"/>
-        <v>29788</v>
-      </c>
-      <c r="H15">
-        <f t="shared" si="3"/>
-        <v>10.993033327057042</v>
-      </c>
-      <c r="I15" s="1"/>
-    </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="C16" s="12">
-        <v>0.94</v>
-      </c>
-      <c r="D16" s="11">
-        <v>32796</v>
-      </c>
-      <c r="F16" s="11">
-        <f t="shared" si="2"/>
-        <v>54040</v>
-      </c>
-      <c r="H16">
-        <f t="shared" si="3"/>
-        <v>10.549143287516475</v>
-      </c>
-      <c r="I16" s="1"/>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C17" s="12">
-        <v>0.97</v>
-      </c>
-      <c r="D17" s="11">
-        <v>36904</v>
-      </c>
-      <c r="F17" s="11">
-        <f t="shared" si="2"/>
-        <v>58148</v>
-      </c>
-      <c r="H17">
-        <f t="shared" si="3"/>
-        <v>9.4964162430176344</v>
-      </c>
-      <c r="I17" s="1"/>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C18" s="12">
-        <v>0.82</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="F18" s="11">
-        <f>D18+$E$21</f>
-        <v>8404</v>
-      </c>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C19" s="12">
-        <v>0.83</v>
-      </c>
-      <c r="D19" s="11">
-        <v>634</v>
-      </c>
-      <c r="F19" s="11">
-        <f t="shared" ref="F19:F24" si="4">D19+$E$21</f>
-        <v>9038</v>
-      </c>
-      <c r="H19">
-        <f>((F19-$F$18)/($F$18))/((C19-$C$18)/($C$18))</f>
-        <v>6.1861018562589187</v>
-      </c>
-      <c r="I19" s="1"/>
-    </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C20" s="12">
-        <v>0.84</v>
-      </c>
-      <c r="D20">
-        <v>1315</v>
-      </c>
-      <c r="F20" s="11">
-        <f t="shared" si="4"/>
-        <v>9719</v>
-      </c>
-      <c r="H20">
-        <f t="shared" ref="H20:H24" si="5">((F20-$F$18)/($F$18))/((C20-$C$18)/($C$18))</f>
-        <v>6.4153974297953296</v>
-      </c>
-      <c r="I20" s="1"/>
-    </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B21" t="s">
-        <v>119</v>
-      </c>
-      <c r="C21" s="12">
-        <v>0.85</v>
-      </c>
-      <c r="D21" s="11">
-        <v>2048</v>
-      </c>
-      <c r="E21" s="11">
-        <v>8404</v>
-      </c>
-      <c r="F21" s="11">
-        <f t="shared" si="4"/>
-        <v>10452</v>
-      </c>
-      <c r="H21">
-        <f t="shared" si="5"/>
-        <v>6.6609551007456709</v>
-      </c>
-      <c r="I21" s="1"/>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C22" s="12">
-        <v>0.87</v>
-      </c>
-      <c r="D22">
-        <v>3683</v>
-      </c>
-      <c r="F22" s="11">
-        <f t="shared" si="4"/>
-        <v>12087</v>
-      </c>
-      <c r="H22">
-        <f t="shared" si="5"/>
-        <v>7.1871965730604401</v>
-      </c>
-      <c r="I22" s="1"/>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C23" s="12">
-        <v>0.88</v>
-      </c>
-      <c r="D23" s="11">
-        <v>4594</v>
-      </c>
-      <c r="F23" s="11">
-        <f t="shared" si="4"/>
-        <v>12998</v>
-      </c>
-      <c r="H23">
-        <f t="shared" si="5"/>
-        <v>7.4708075519593775</v>
-      </c>
-      <c r="I23" s="1"/>
-    </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C24" s="12">
-        <v>0.97</v>
-      </c>
-      <c r="D24" s="5">
-        <v>17687</v>
-      </c>
-      <c r="F24" s="11">
-        <f t="shared" si="4"/>
-        <v>26091</v>
-      </c>
-      <c r="H24">
-        <f t="shared" si="5"/>
-        <v>11.505108678407106</v>
-      </c>
-      <c r="I24" s="1"/>
-    </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C25" s="12">
-        <v>0.84</v>
-      </c>
-      <c r="D25">
-        <v>0</v>
-      </c>
-      <c r="F25" s="11">
-        <f>D25+$E$27</f>
-        <v>18915</v>
-      </c>
-    </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C26" s="12">
-        <v>0.86</v>
-      </c>
-      <c r="D26" s="11">
-        <v>4785</v>
-      </c>
-      <c r="F26" s="11">
-        <f t="shared" ref="F26:F29" si="6">D26+$E$27</f>
-        <v>23700</v>
-      </c>
-      <c r="H26">
-        <f>((F26-$F$25)/($F$25))/((C26-$C$25)/($C$25))</f>
-        <v>10.624900872323542</v>
-      </c>
-      <c r="I26" s="1"/>
-    </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B27" t="s">
-        <v>120</v>
-      </c>
-      <c r="C27" s="12">
-        <v>0.88</v>
-      </c>
-      <c r="D27" s="11">
-        <v>10781</v>
-      </c>
-      <c r="E27" s="11">
-        <v>18915</v>
-      </c>
-      <c r="F27" s="11">
-        <f t="shared" si="6"/>
-        <v>29696</v>
-      </c>
-      <c r="H27">
-        <f t="shared" ref="H27:H29" si="7">((F27-$F$25)/($F$25))/((C27-$C$25)/($C$25))</f>
-        <v>11.969389373513073</v>
-      </c>
-      <c r="I27" s="1"/>
-    </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C28" s="12">
-        <v>0.89</v>
-      </c>
-      <c r="D28" s="11">
-        <v>14326</v>
-      </c>
-      <c r="F28" s="11">
-        <f t="shared" si="6"/>
-        <v>33241</v>
-      </c>
-      <c r="H28">
-        <f t="shared" si="7"/>
-        <v>12.724123711340194</v>
-      </c>
-      <c r="I28" s="1"/>
-    </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C29" s="12">
-        <v>0.97</v>
-      </c>
-      <c r="D29" s="5">
-        <v>49923</v>
-      </c>
-      <c r="F29" s="11">
-        <f t="shared" si="6"/>
-        <v>68838</v>
-      </c>
-      <c r="H29">
-        <f t="shared" si="7"/>
-        <v>17.054157262246079</v>
-      </c>
-      <c r="I29" s="1"/>
-    </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C30" s="12">
-        <v>0.77</v>
-      </c>
-      <c r="D30">
-        <v>0</v>
-      </c>
-      <c r="F30" s="11">
-        <f>D30+$E$32</f>
-        <v>6659</v>
-      </c>
-    </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C31" s="12">
-        <v>0.78</v>
-      </c>
-      <c r="D31" s="11">
-        <v>540</v>
-      </c>
-      <c r="F31" s="11">
-        <f t="shared" ref="F31:F35" si="8">D31+$E$32</f>
-        <v>7199</v>
-      </c>
-      <c r="H31">
-        <f>((F31-$F$30)/($F$30))/((C31-$C$30)/($C$30))</f>
-        <v>6.244180807929113</v>
-      </c>
-      <c r="I31" s="1"/>
-    </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B32" t="s">
-        <v>121</v>
-      </c>
-      <c r="C32" s="12">
-        <v>0.79</v>
-      </c>
-      <c r="D32" s="5">
-        <v>1124</v>
-      </c>
-      <c r="E32" s="11">
-        <v>6659</v>
-      </c>
-      <c r="F32" s="11">
-        <f t="shared" si="8"/>
-        <v>7783</v>
-      </c>
-      <c r="H32">
-        <f t="shared" ref="H32:H35" si="9">((F32-$F$30)/($F$30))/((C32-$C$30)/($C$30))</f>
-        <v>6.4985733593632622</v>
-      </c>
-      <c r="I32" s="1"/>
-    </row>
-    <row r="33" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C33" s="12">
-        <v>0.8</v>
-      </c>
-      <c r="D33" s="11">
-        <v>1756</v>
-      </c>
-      <c r="F33" s="11">
-        <f t="shared" si="8"/>
-        <v>8415</v>
-      </c>
-      <c r="H33">
-        <f t="shared" si="9"/>
-        <v>6.7683836411873592</v>
-      </c>
-      <c r="I33" s="1"/>
-    </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C34" s="12">
-        <v>0.81</v>
-      </c>
-      <c r="D34" s="5">
-        <v>2439</v>
-      </c>
-      <c r="F34" s="11">
-        <f t="shared" si="8"/>
-        <v>9098</v>
-      </c>
-      <c r="H34">
-        <f t="shared" si="9"/>
-        <v>7.0507208289532901</v>
-      </c>
-      <c r="I34" s="1"/>
-    </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C35" s="12">
-        <v>0.83</v>
-      </c>
-      <c r="D35" s="11">
-        <v>3975</v>
-      </c>
-      <c r="F35" s="11">
-        <f t="shared" si="8"/>
-        <v>10634</v>
-      </c>
-      <c r="H35">
-        <f t="shared" si="9"/>
-        <v>7.6606847875056383</v>
-      </c>
-      <c r="I35" s="1"/>
-    </row>
-    <row r="36" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C36" s="12">
-        <v>0.77</v>
-      </c>
-      <c r="D36">
-        <v>0</v>
-      </c>
-      <c r="F36" s="11">
-        <f>D36+$E$39</f>
-        <v>19122</v>
-      </c>
-    </row>
-    <row r="37" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C37" s="12">
-        <v>0.78</v>
-      </c>
-      <c r="D37" s="5">
-        <v>1097</v>
-      </c>
-      <c r="F37" s="11">
-        <f t="shared" ref="F37:F42" si="10">D37+$E$39</f>
-        <v>20219</v>
-      </c>
-      <c r="H37">
-        <f>((F37-$F$36)/($F$36))/((C37-$C$36)/($C$36))</f>
-        <v>4.4173726597636191</v>
-      </c>
-      <c r="I37" s="1"/>
-    </row>
-    <row r="38" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C38" s="12">
-        <v>0.79</v>
-      </c>
-      <c r="D38" s="5">
-        <v>2256</v>
-      </c>
-      <c r="F38" s="11">
-        <f t="shared" si="10"/>
-        <v>21378</v>
-      </c>
-      <c r="H38">
-        <f t="shared" ref="H38:H42" si="11">((F38-$F$36)/($F$36))/((C38-$C$36)/($C$36))</f>
-        <v>4.5422026984624999</v>
-      </c>
-      <c r="I38" s="1"/>
-    </row>
-    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B39" t="s">
-        <v>122</v>
-      </c>
-      <c r="C39" s="12">
-        <v>0.8</v>
-      </c>
-      <c r="D39" s="5">
-        <v>3483</v>
-      </c>
-      <c r="E39" s="11">
-        <v>19122</v>
-      </c>
-      <c r="F39" s="11">
-        <f t="shared" si="10"/>
-        <v>22605</v>
-      </c>
-      <c r="H39">
-        <f t="shared" si="11"/>
-        <v>4.67508628804518</v>
-      </c>
-      <c r="I39" s="1"/>
-    </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C40" s="12">
-        <v>0.81</v>
-      </c>
-      <c r="D40">
-        <v>4779</v>
-      </c>
-      <c r="F40" s="11">
-        <f t="shared" si="10"/>
-        <v>23901</v>
-      </c>
-      <c r="H40">
-        <f t="shared" si="11"/>
-        <v>4.8109899592092837</v>
-      </c>
-      <c r="I40" s="1"/>
-    </row>
-    <row r="41" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C41" s="12">
-        <v>0.82</v>
-      </c>
-      <c r="D41" s="11">
-        <v>6150</v>
-      </c>
-      <c r="F41" s="11">
-        <f t="shared" si="10"/>
-        <v>25272</v>
-      </c>
-      <c r="H41">
-        <f t="shared" si="11"/>
-        <v>4.9529337935362481</v>
-      </c>
-      <c r="I41" s="1"/>
-    </row>
-    <row r="42" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C42" s="12">
-        <v>0.84</v>
-      </c>
-      <c r="D42">
-        <v>9132</v>
-      </c>
-      <c r="F42" s="11">
-        <f t="shared" si="10"/>
-        <v>28254</v>
-      </c>
-      <c r="H42">
-        <f t="shared" si="11"/>
-        <v>5.2532161907750279</v>
-      </c>
-      <c r="I42" s="1"/>
-    </row>
-    <row r="43" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C43" s="12">
-        <v>0.81</v>
-      </c>
-      <c r="D43">
-        <v>0</v>
-      </c>
-      <c r="F43" s="11">
-        <f>D43+$E$44</f>
-        <v>7294</v>
-      </c>
-    </row>
-    <row r="44" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B44" t="s">
-        <v>123</v>
-      </c>
-      <c r="C44" s="12">
-        <v>0.83</v>
-      </c>
-      <c r="D44" s="5">
-        <v>1722</v>
-      </c>
-      <c r="E44" s="11">
-        <v>7294</v>
-      </c>
-      <c r="F44" s="11">
-        <f t="shared" ref="F44:F46" si="12">D44+$E$44</f>
-        <v>9016</v>
-      </c>
-      <c r="H44">
-        <f>((F44-$F$43)/($F$43))/((C44-$C$43)/($C$43))</f>
-        <v>9.5614203454894877</v>
-      </c>
-      <c r="I44" s="1"/>
-    </row>
-    <row r="45" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C45" s="12">
-        <v>0.84</v>
-      </c>
-      <c r="D45">
-        <v>2730</v>
-      </c>
-      <c r="F45" s="11">
-        <f t="shared" si="12"/>
-        <v>10024</v>
-      </c>
-      <c r="H45">
-        <f t="shared" ref="H45:H46" si="13">((F45-$F$43)/($F$43))/((C45-$C$43)/($C$43))</f>
-        <v>10.10556621881001</v>
-      </c>
-      <c r="I45" s="1"/>
-    </row>
-    <row r="46" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C46" s="12">
-        <v>0.86</v>
-      </c>
-      <c r="D46" s="11">
-        <v>5097</v>
-      </c>
-      <c r="F46" s="11">
-        <f t="shared" si="12"/>
-        <v>12391</v>
-      </c>
-      <c r="H46">
-        <f t="shared" si="13"/>
-        <v>11.320455168631767</v>
-      </c>
-      <c r="I46" s="1"/>
-    </row>
-    <row r="47" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C47" s="12">
-        <v>0.81</v>
-      </c>
-      <c r="D47">
-        <v>0</v>
-      </c>
-      <c r="F47" s="11">
-        <f>D47+$E$48</f>
-        <v>18702</v>
-      </c>
-    </row>
-    <row r="48" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B48" t="s">
-        <v>124</v>
-      </c>
-      <c r="C48" s="12">
-        <v>0.83</v>
-      </c>
-      <c r="D48" s="11">
-        <v>3071</v>
-      </c>
-      <c r="E48" s="11">
-        <v>18702</v>
-      </c>
-      <c r="F48" s="11">
-        <f t="shared" ref="F48:F50" si="14">D48+$E$48</f>
-        <v>21773</v>
-      </c>
-      <c r="H48">
-        <f>((F48-$F$47)/($F$47))/((C48-$C$47)/($C$47))</f>
-        <v>6.6503849855630728</v>
-      </c>
-      <c r="I48" s="1"/>
-    </row>
-    <row r="49" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C49" s="12">
-        <v>0.85</v>
-      </c>
-      <c r="D49" s="11">
-        <v>6521</v>
-      </c>
-      <c r="F49" s="11">
-        <f t="shared" si="14"/>
-        <v>25223</v>
-      </c>
-      <c r="H49">
-        <f t="shared" ref="H49:H50" si="15">((F49-$F$47)/($F$47))/((C49-$C$47)/($C$47))</f>
-        <v>7.060755534167483</v>
-      </c>
-      <c r="I49" s="1"/>
-    </row>
-    <row r="50" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C50" s="12">
-        <v>0.87</v>
-      </c>
-      <c r="D50" s="11">
-        <v>10590</v>
-      </c>
-      <c r="F50" s="11">
-        <f t="shared" si="14"/>
-        <v>29292</v>
-      </c>
-      <c r="H50">
-        <f t="shared" si="15"/>
-        <v>7.6443695861405265</v>
-      </c>
-      <c r="I50" s="1"/>
-    </row>
-    <row r="51" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="I51" s="13">
-        <f>AVERAGE(H1:H50)</f>
-        <v>8.126972362529246</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>